--- a/IG/AI Native-提案演習_IG.xlsx
+++ b/IG/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FA83E7-2C82-455B-BAD0-2A8A0807F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB9BC81-3836-44AD-9205-3A6007B4BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1950,7 +1950,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2161,6 +2161,84 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2209,6 +2287,51 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2218,51 +2341,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2271,90 +2349,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2738,17 +2732,17 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="70" t="str">
+      <c r="B2" s="96" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案演習_IG」</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
       <c r="J2" s="69"/>
       <c r="K2" s="69"/>
     </row>
@@ -2767,10 +2761,10 @@
     </row>
     <row r="4" spans="1:11" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="72"/>
+      <c r="C4" s="98"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2782,8 +2776,8 @@
     </row>
     <row r="5" spans="1:11" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="74"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="100"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -2800,10 +2794,10 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="16.2">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="75"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -2888,22 +2882,22 @@
       <c r="D11" s="58">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="133"/>
+      <c r="E11" s="94"/>
       <c r="F11" s="58">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="133" t="str">
+      <c r="G11" s="94" t="str">
         <f>master!B39</f>
         <v>チーム演習</v>
       </c>
       <c r="H11" s="58">
         <v>0.40625</v>
       </c>
-      <c r="I11" s="134"/>
+      <c r="I11" s="95"/>
       <c r="J11" s="58">
         <v>0.40625</v>
       </c>
-      <c r="K11" s="114" t="str">
+      <c r="K11" s="83" t="str">
         <f>master!B48</f>
         <v>発表会（ブロック代表の決定）</v>
       </c>
@@ -2912,7 +2906,7 @@
       <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="129">
+      <c r="B12" s="90">
         <v>0.41666666666666669</v>
       </c>
       <c r="C12" s="61" t="str">
@@ -2920,29 +2914,29 @@
         <v>企画提案のステップ</v>
       </c>
       <c r="D12" s="60"/>
-      <c r="E12" s="134"/>
+      <c r="E12" s="95"/>
       <c r="F12" s="60"/>
-      <c r="G12" s="134"/>
+      <c r="G12" s="95"/>
       <c r="H12" s="60"/>
-      <c r="I12" s="134"/>
+      <c r="I12" s="95"/>
       <c r="J12" s="60"/>
-      <c r="K12" s="115"/>
+      <c r="K12" s="84"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="38"/>
-      <c r="B13" s="130"/>
+      <c r="B13" s="91"/>
       <c r="C13" s="62" t="str">
         <f>master!B16</f>
         <v>まとめ</v>
       </c>
       <c r="D13" s="60"/>
-      <c r="E13" s="134"/>
+      <c r="E13" s="95"/>
       <c r="F13" s="60"/>
-      <c r="G13" s="134"/>
+      <c r="G13" s="95"/>
       <c r="H13" s="60"/>
-      <c r="I13" s="134"/>
+      <c r="I13" s="95"/>
       <c r="J13" s="60"/>
-      <c r="K13" s="115"/>
+      <c r="K13" s="84"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="38"/>
@@ -2954,28 +2948,28 @@
         <v>提案書サンプル</v>
       </c>
       <c r="D14" s="60"/>
-      <c r="E14" s="134"/>
+      <c r="E14" s="95"/>
       <c r="F14" s="60"/>
-      <c r="G14" s="134"/>
+      <c r="G14" s="95"/>
       <c r="H14" s="60"/>
-      <c r="I14" s="134"/>
+      <c r="I14" s="95"/>
       <c r="J14" s="60"/>
-      <c r="K14" s="115"/>
+      <c r="K14" s="84"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="39"/>
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="92" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="62"/>
       <c r="D15" s="60"/>
-      <c r="E15" s="134"/>
+      <c r="E15" s="95"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="134"/>
+      <c r="G15" s="95"/>
       <c r="H15" s="60"/>
-      <c r="I15" s="134"/>
+      <c r="I15" s="95"/>
       <c r="J15" s="60"/>
-      <c r="K15" s="115"/>
+      <c r="K15" s="84"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="37">
@@ -2984,85 +2978,85 @@
       <c r="B16" s="58">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="133" t="str">
+      <c r="C16" s="94" t="str">
         <f>master!B31</f>
         <v>個人演習</v>
       </c>
       <c r="D16" s="60"/>
-      <c r="E16" s="134"/>
+      <c r="E16" s="95"/>
       <c r="F16" s="60"/>
-      <c r="G16" s="134"/>
+      <c r="G16" s="95"/>
       <c r="H16" s="60"/>
-      <c r="I16" s="134"/>
+      <c r="I16" s="95"/>
       <c r="J16" s="60"/>
-      <c r="K16" s="115"/>
+      <c r="K16" s="84"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="38"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="134"/>
+      <c r="C17" s="95"/>
       <c r="D17" s="60"/>
-      <c r="E17" s="134"/>
+      <c r="E17" s="95"/>
       <c r="F17" s="60"/>
-      <c r="G17" s="134"/>
+      <c r="G17" s="95"/>
       <c r="H17" s="60"/>
-      <c r="I17" s="134"/>
+      <c r="I17" s="95"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="115"/>
+      <c r="K17" s="84"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="38"/>
       <c r="B18" s="60"/>
-      <c r="C18" s="134"/>
+      <c r="C18" s="95"/>
       <c r="D18" s="60"/>
-      <c r="E18" s="134"/>
+      <c r="E18" s="95"/>
       <c r="F18" s="60"/>
-      <c r="G18" s="134"/>
+      <c r="G18" s="95"/>
       <c r="H18" s="60"/>
-      <c r="I18" s="134"/>
+      <c r="I18" s="95"/>
       <c r="J18" s="60"/>
-      <c r="K18" s="115"/>
+      <c r="K18" s="84"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="39"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="134"/>
+      <c r="C19" s="95"/>
       <c r="D19" s="60"/>
-      <c r="E19" s="134"/>
+      <c r="E19" s="95"/>
       <c r="F19" s="60"/>
-      <c r="G19" s="134"/>
+      <c r="G19" s="95"/>
       <c r="H19" s="60"/>
-      <c r="I19" s="134"/>
+      <c r="I19" s="95"/>
       <c r="J19" s="60"/>
-      <c r="K19" s="115"/>
+      <c r="K19" s="84"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="57">
         <v>0.5</v>
       </c>
       <c r="B20" s="60"/>
-      <c r="C20" s="134"/>
+      <c r="C20" s="95"/>
       <c r="D20" s="60"/>
-      <c r="E20" s="134"/>
+      <c r="E20" s="95"/>
       <c r="F20" s="60"/>
-      <c r="G20" s="134"/>
+      <c r="G20" s="95"/>
       <c r="H20" s="60"/>
-      <c r="I20" s="134"/>
+      <c r="I20" s="95"/>
       <c r="J20" s="60"/>
-      <c r="K20" s="115"/>
+      <c r="K20" s="84"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="52"/>
       <c r="B21" s="54"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="134"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="95"/>
       <c r="J21" s="54"/>
-      <c r="K21" s="116"/>
+      <c r="K21" s="85"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="38"/>
@@ -3173,23 +3167,23 @@
       <c r="B26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="133"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="133"/>
+      <c r="E26" s="94"/>
       <c r="F26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="133"/>
+      <c r="G26" s="94"/>
       <c r="H26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="I26" s="133"/>
+      <c r="I26" s="94"/>
       <c r="J26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="K26" s="114" t="str">
+      <c r="K26" s="83" t="str">
         <f>master!B51</f>
         <v>発表会（最終）</v>
       </c>
@@ -3197,71 +3191,71 @@
     <row r="27" spans="1:12">
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="134"/>
+      <c r="C27" s="95"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="134"/>
+      <c r="E27" s="95"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="134"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="42"/>
-      <c r="I27" s="134"/>
+      <c r="I27" s="95"/>
       <c r="J27" s="42"/>
-      <c r="K27" s="115"/>
+      <c r="K27" s="84"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="37">
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="42"/>
-      <c r="C28" s="134"/>
+      <c r="C28" s="95"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="134"/>
+      <c r="E28" s="95"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="134"/>
+      <c r="G28" s="95"/>
       <c r="H28" s="42"/>
-      <c r="I28" s="134"/>
+      <c r="I28" s="95"/>
       <c r="J28" s="42"/>
-      <c r="K28" s="115"/>
+      <c r="K28" s="84"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="38"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="134"/>
+      <c r="C29" s="95"/>
       <c r="D29" s="42"/>
-      <c r="E29" s="134"/>
+      <c r="E29" s="95"/>
       <c r="F29" s="42"/>
-      <c r="G29" s="134"/>
+      <c r="G29" s="95"/>
       <c r="H29" s="42"/>
-      <c r="I29" s="134"/>
+      <c r="I29" s="95"/>
       <c r="J29" s="42"/>
-      <c r="K29" s="115"/>
+      <c r="K29" s="84"/>
       <c r="L29" s="51"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="38"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="134"/>
+      <c r="C30" s="95"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="134"/>
+      <c r="E30" s="95"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="134"/>
+      <c r="G30" s="95"/>
       <c r="H30" s="42"/>
-      <c r="I30" s="134"/>
+      <c r="I30" s="95"/>
       <c r="J30" s="42"/>
-      <c r="K30" s="115"/>
+      <c r="K30" s="84"/>
       <c r="L30" s="51"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="39"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="134"/>
+      <c r="C31" s="95"/>
       <c r="D31" s="42"/>
-      <c r="E31" s="134"/>
+      <c r="E31" s="95"/>
       <c r="F31" s="42"/>
-      <c r="G31" s="134"/>
+      <c r="G31" s="95"/>
       <c r="H31" s="42"/>
-      <c r="I31" s="134"/>
+      <c r="I31" s="95"/>
       <c r="J31" s="42"/>
-      <c r="K31" s="115"/>
+      <c r="K31" s="84"/>
       <c r="L31" s="51"/>
     </row>
     <row r="32" spans="1:12">
@@ -3269,57 +3263,57 @@
         <v>0.625</v>
       </c>
       <c r="B32" s="42"/>
-      <c r="C32" s="134"/>
+      <c r="C32" s="95"/>
       <c r="D32" s="42"/>
-      <c r="E32" s="134"/>
+      <c r="E32" s="95"/>
       <c r="F32" s="42"/>
-      <c r="G32" s="134"/>
+      <c r="G32" s="95"/>
       <c r="H32" s="42"/>
-      <c r="I32" s="134"/>
+      <c r="I32" s="95"/>
       <c r="J32" s="42"/>
-      <c r="K32" s="115"/>
+      <c r="K32" s="84"/>
       <c r="L32" s="51"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="52"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="134"/>
+      <c r="C33" s="95"/>
       <c r="D33" s="42"/>
-      <c r="E33" s="134"/>
+      <c r="E33" s="95"/>
       <c r="F33" s="42"/>
-      <c r="G33" s="134"/>
+      <c r="G33" s="95"/>
       <c r="H33" s="42"/>
-      <c r="I33" s="134"/>
+      <c r="I33" s="95"/>
       <c r="J33" s="42"/>
-      <c r="K33" s="115"/>
+      <c r="K33" s="84"/>
       <c r="L33" s="51"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="52"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="134"/>
+      <c r="C34" s="95"/>
       <c r="D34" s="42"/>
-      <c r="E34" s="134"/>
+      <c r="E34" s="95"/>
       <c r="F34" s="42"/>
-      <c r="G34" s="134"/>
+      <c r="G34" s="95"/>
       <c r="H34" s="42"/>
-      <c r="I34" s="134"/>
+      <c r="I34" s="95"/>
       <c r="J34" s="42"/>
-      <c r="K34" s="115"/>
+      <c r="K34" s="84"/>
       <c r="L34" s="51"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="39"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="134"/>
+      <c r="C35" s="95"/>
       <c r="D35" s="42"/>
-      <c r="E35" s="134"/>
+      <c r="E35" s="95"/>
       <c r="F35" s="42"/>
-      <c r="G35" s="134"/>
+      <c r="G35" s="95"/>
       <c r="H35" s="42"/>
-      <c r="I35" s="134"/>
+      <c r="I35" s="95"/>
       <c r="J35" s="42"/>
-      <c r="K35" s="115"/>
+      <c r="K35" s="84"/>
       <c r="L35" s="51"/>
     </row>
     <row r="36" spans="1:12">
@@ -3327,57 +3321,57 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="42"/>
-      <c r="C36" s="134"/>
+      <c r="C36" s="95"/>
       <c r="D36" s="42"/>
-      <c r="E36" s="134"/>
+      <c r="E36" s="95"/>
       <c r="F36" s="42"/>
-      <c r="G36" s="134"/>
+      <c r="G36" s="95"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="134"/>
+      <c r="I36" s="95"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="115"/>
+      <c r="K36" s="84"/>
       <c r="L36" s="51"/>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="38"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="134"/>
+      <c r="C37" s="95"/>
       <c r="D37" s="42"/>
-      <c r="E37" s="134"/>
+      <c r="E37" s="95"/>
       <c r="F37" s="42"/>
-      <c r="G37" s="134"/>
+      <c r="G37" s="95"/>
       <c r="H37" s="42"/>
-      <c r="I37" s="134"/>
+      <c r="I37" s="95"/>
       <c r="J37" s="42"/>
-      <c r="K37" s="115"/>
+      <c r="K37" s="84"/>
       <c r="L37" s="51"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="38"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="134"/>
+      <c r="C38" s="95"/>
       <c r="D38" s="42"/>
-      <c r="E38" s="134"/>
+      <c r="E38" s="95"/>
       <c r="F38" s="42"/>
-      <c r="G38" s="134"/>
+      <c r="G38" s="95"/>
       <c r="H38" s="42"/>
-      <c r="I38" s="134"/>
+      <c r="I38" s="95"/>
       <c r="J38" s="42"/>
-      <c r="K38" s="115"/>
+      <c r="K38" s="84"/>
       <c r="L38" s="51"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="38"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="134"/>
+      <c r="C39" s="95"/>
       <c r="D39" s="42"/>
-      <c r="E39" s="134"/>
+      <c r="E39" s="95"/>
       <c r="F39" s="42"/>
-      <c r="G39" s="134"/>
+      <c r="G39" s="95"/>
       <c r="H39" s="42"/>
-      <c r="I39" s="134"/>
+      <c r="I39" s="95"/>
       <c r="J39" s="42"/>
-      <c r="K39" s="115"/>
+      <c r="K39" s="84"/>
       <c r="L39" s="51"/>
     </row>
     <row r="40" spans="1:12">
@@ -3385,75 +3379,75 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="B40" s="42"/>
-      <c r="C40" s="134"/>
+      <c r="C40" s="95"/>
       <c r="D40" s="42"/>
-      <c r="E40" s="134"/>
+      <c r="E40" s="95"/>
       <c r="F40" s="42"/>
-      <c r="G40" s="134"/>
+      <c r="G40" s="95"/>
       <c r="H40" s="42"/>
-      <c r="I40" s="134"/>
+      <c r="I40" s="95"/>
       <c r="J40" s="42"/>
-      <c r="K40" s="115"/>
+      <c r="K40" s="84"/>
       <c r="L40" s="51"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="38"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="134"/>
+      <c r="C41" s="95"/>
       <c r="D41" s="42"/>
-      <c r="E41" s="134"/>
+      <c r="E41" s="95"/>
       <c r="F41" s="42"/>
-      <c r="G41" s="134"/>
+      <c r="G41" s="95"/>
       <c r="H41" s="42"/>
-      <c r="I41" s="134"/>
+      <c r="I41" s="95"/>
       <c r="J41" s="42"/>
-      <c r="K41" s="115"/>
+      <c r="K41" s="84"/>
       <c r="L41" s="53"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="42"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="132"/>
+      <c r="C42" s="93"/>
       <c r="D42" s="42"/>
-      <c r="E42" s="132"/>
+      <c r="E42" s="93"/>
       <c r="F42" s="42"/>
-      <c r="G42" s="132"/>
+      <c r="G42" s="93"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="132"/>
+      <c r="I42" s="93"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="116"/>
+      <c r="K42" s="85"/>
       <c r="L42" s="51"/>
     </row>
     <row r="43" spans="1:12" ht="14.25" customHeight="1">
       <c r="A43" s="41"/>
-      <c r="B43" s="117">
+      <c r="B43" s="86">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="118" t="s">
+      <c r="C43" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="117">
+      <c r="D43" s="86">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="118" t="s">
+      <c r="E43" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="F43" s="117">
+      <c r="F43" s="86">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="118" t="s">
+      <c r="G43" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="H43" s="117">
+      <c r="H43" s="86">
         <v>0.73958333333333337</v>
       </c>
-      <c r="I43" s="118" t="s">
+      <c r="I43" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="J43" s="117">
+      <c r="J43" s="86">
         <v>0.73958333333333337</v>
       </c>
-      <c r="K43" s="118" t="s">
+      <c r="K43" s="87" t="s">
         <v>93</v>
       </c>
       <c r="L43" s="52"/>
@@ -3520,10 +3514,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="81"/>
+      <c r="C4" s="107"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3534,16 +3528,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3556,10 +3550,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="33"/>
-      <c r="D7" s="83" t="s">
+      <c r="D7" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="83"/>
+      <c r="E7" s="109"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -3599,46 +3593,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="77" t="s">
+      <c r="D11" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77" t="s">
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="84" t="s">
+      <c r="H11" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="76" t="s">
+      <c r="I11" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76" t="s">
+      <c r="J11" s="102"/>
+      <c r="K11" s="102" t="s">
         <v>31</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="85"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="111"/>
       <c r="I12" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="77"/>
+      <c r="K12" s="103"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -3647,11 +3641,11 @@
       <c r="C13" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="78" t="s">
+      <c r="D13" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="79"/>
-      <c r="F13" s="80"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="106"/>
       <c r="G13" s="55" t="s">
         <v>45</v>
       </c>
@@ -3750,12 +3744,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3766,30 +3760,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="126"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="126"/>
+      <c r="H6" s="126"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30"/>
     </row>
@@ -3916,28 +3910,28 @@
     </row>
     <row r="14" spans="1:14" ht="24" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77" t="s">
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="89" t="s">
+      <c r="I14" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="90"/>
-      <c r="K14" s="76" t="s">
+      <c r="J14" s="125"/>
+      <c r="K14" s="102" t="s">
         <v>33</v>
       </c>
       <c r="L14" s="6"/>
@@ -3946,27 +3940,27 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="10"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="76"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="102"/>
       <c r="I15" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="77"/>
+      <c r="K15" s="103"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="63">
       <c r="A16" s="10"/>
-      <c r="B16" s="127" t="str">
+      <c r="B16" s="88" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
@@ -3974,11 +3968,11 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="87"/>
-      <c r="F16" s="88"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="129"/>
       <c r="G16" s="50" t="s">
         <v>129</v>
       </c>
@@ -3996,7 +3990,7 @@
     </row>
     <row r="17" spans="1:14" ht="102" customHeight="1">
       <c r="A17" s="10"/>
-      <c r="B17" s="124" t="str">
+      <c r="B17" s="121" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4004,11 +3998,11 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D17" s="86" t="s">
+      <c r="D17" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="87"/>
-      <c r="F17" s="88"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="129"/>
       <c r="G17" s="50" t="s">
         <v>38</v>
       </c>
@@ -4026,16 +4020,16 @@
     </row>
     <row r="18" spans="1:14" ht="176.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="125"/>
+      <c r="B18" s="122"/>
       <c r="C18" s="50" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="D18" s="127" t="s">
         <v>138</v>
       </c>
-      <c r="E18" s="87"/>
-      <c r="F18" s="88"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="129"/>
       <c r="G18" s="50" t="s">
         <v>50</v>
       </c>
@@ -4053,16 +4047,16 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="125"/>
+      <c r="B19" s="122"/>
       <c r="C19" s="50" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D19" s="86" t="s">
+      <c r="D19" s="127" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="87"/>
-      <c r="F19" s="88"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="129"/>
       <c r="G19" s="50" t="s">
         <v>38</v>
       </c>
@@ -4080,16 +4074,16 @@
     </row>
     <row r="20" spans="1:14" ht="151.19999999999999">
       <c r="A20" s="11"/>
-      <c r="B20" s="125"/>
+      <c r="B20" s="122"/>
       <c r="C20" s="50" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D20" s="86" t="s">
+      <c r="D20" s="127" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="87"/>
-      <c r="F20" s="88"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="129"/>
       <c r="G20" s="50" t="s">
         <v>47</v>
       </c>
@@ -4107,16 +4101,16 @@
     </row>
     <row r="21" spans="1:14" ht="252">
       <c r="A21" s="11"/>
-      <c r="B21" s="125"/>
+      <c r="B21" s="122"/>
       <c r="C21" s="50" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D21" s="86" t="s">
+      <c r="D21" s="127" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="87"/>
-      <c r="F21" s="88"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="129"/>
       <c r="G21" s="50" t="s">
         <v>51</v>
       </c>
@@ -4134,16 +4128,16 @@
     </row>
     <row r="22" spans="1:14" ht="126">
       <c r="A22" s="11"/>
-      <c r="B22" s="125"/>
+      <c r="B22" s="122"/>
       <c r="C22" s="50" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D22" s="86" t="s">
+      <c r="D22" s="127" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="87"/>
-      <c r="F22" s="88"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="129"/>
       <c r="G22" s="50" t="s">
         <v>49</v>
       </c>
@@ -4161,16 +4155,16 @@
     </row>
     <row r="23" spans="1:14" ht="63">
       <c r="A23" s="11"/>
-      <c r="B23" s="125"/>
+      <c r="B23" s="122"/>
       <c r="C23" s="50" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D23" s="127" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="87"/>
-      <c r="F23" s="88"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="129"/>
       <c r="G23" s="50" t="s">
         <v>129</v>
       </c>
@@ -4188,16 +4182,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="125"/>
+      <c r="B24" s="122"/>
       <c r="C24" s="50" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D24" s="86" t="s">
+      <c r="D24" s="127" t="s">
         <v>142</v>
       </c>
-      <c r="E24" s="87"/>
-      <c r="F24" s="88"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="129"/>
       <c r="G24" s="50" t="s">
         <v>39</v>
       </c>
@@ -4215,16 +4209,16 @@
     </row>
     <row r="25" spans="1:14" ht="75.599999999999994">
       <c r="A25" s="11"/>
-      <c r="B25" s="125"/>
+      <c r="B25" s="122"/>
       <c r="C25" s="50" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D25" s="86" t="s">
+      <c r="D25" s="127" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="87"/>
-      <c r="F25" s="88"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="129"/>
       <c r="G25" s="50" t="s">
         <v>39</v>
       </c>
@@ -4242,16 +4236,16 @@
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="125"/>
+      <c r="B26" s="122"/>
       <c r="C26" s="50" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D26" s="86" t="s">
+      <c r="D26" s="127" t="s">
         <v>144</v>
       </c>
-      <c r="E26" s="87"/>
-      <c r="F26" s="88"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="129"/>
       <c r="G26" s="50" t="s">
         <v>40</v>
       </c>
@@ -4269,16 +4263,16 @@
     </row>
     <row r="27" spans="1:14" ht="88.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="126"/>
+      <c r="B27" s="123"/>
       <c r="C27" s="50" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D27" s="86" t="s">
+      <c r="D27" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="87"/>
-      <c r="F27" s="88"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="129"/>
       <c r="G27" s="50" t="s">
         <v>41</v>
       </c>
@@ -4296,7 +4290,7 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="127" t="str">
+      <c r="B28" s="88" t="str">
         <f>master!B16</f>
         <v>まとめ</v>
       </c>
@@ -4304,11 +4298,11 @@
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D28" s="86" t="s">
+      <c r="D28" s="127" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="87"/>
-      <c r="F28" s="88"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="129"/>
       <c r="G28" s="50" t="s">
         <v>40</v>
       </c>
@@ -4326,7 +4320,7 @@
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="124" t="str">
+      <c r="B29" s="121" t="str">
         <f>master!B18</f>
         <v>提案書サンプル</v>
       </c>
@@ -4334,11 +4328,11 @@
         <f>master!C18</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D29" s="86" t="s">
+      <c r="D29" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="87"/>
-      <c r="F29" s="88"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="129"/>
       <c r="G29" s="50" t="s">
         <v>98</v>
       </c>
@@ -4356,16 +4350,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="125"/>
+      <c r="B30" s="122"/>
       <c r="C30" s="50" t="str">
         <f>master!C19</f>
         <v>２．背景</v>
       </c>
-      <c r="D30" s="86" t="s">
+      <c r="D30" s="127" t="s">
         <v>148</v>
       </c>
-      <c r="E30" s="87"/>
-      <c r="F30" s="88"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="129"/>
       <c r="G30" s="50" t="s">
         <v>98</v>
       </c>
@@ -4383,16 +4377,16 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="125"/>
+      <c r="B31" s="122"/>
       <c r="C31" s="50" t="str">
         <f>master!C20</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D31" s="86" t="s">
+      <c r="D31" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="E31" s="87"/>
-      <c r="F31" s="88"/>
+      <c r="E31" s="128"/>
+      <c r="F31" s="129"/>
       <c r="G31" s="50" t="s">
         <v>98</v>
       </c>
@@ -4410,16 +4404,16 @@
     </row>
     <row r="32" spans="1:14" ht="63">
       <c r="A32" s="11"/>
-      <c r="B32" s="125"/>
+      <c r="B32" s="122"/>
       <c r="C32" s="50" t="str">
         <f>master!C21</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D32" s="86" t="s">
+      <c r="D32" s="127" t="s">
         <v>158</v>
       </c>
-      <c r="E32" s="87"/>
-      <c r="F32" s="88"/>
+      <c r="E32" s="128"/>
+      <c r="F32" s="129"/>
       <c r="G32" s="50" t="s">
         <v>153</v>
       </c>
@@ -4437,16 +4431,16 @@
     </row>
     <row r="33" spans="1:14" ht="50.4">
       <c r="A33" s="11"/>
-      <c r="B33" s="125"/>
+      <c r="B33" s="122"/>
       <c r="C33" s="50" t="str">
         <f>master!C22</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D33" s="86" t="s">
+      <c r="D33" s="127" t="s">
         <v>161</v>
       </c>
-      <c r="E33" s="87"/>
-      <c r="F33" s="88"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="129"/>
       <c r="G33" s="50" t="s">
         <v>156</v>
       </c>
@@ -4464,16 +4458,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="125"/>
+      <c r="B34" s="122"/>
       <c r="C34" s="50" t="str">
         <f>master!C23</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D34" s="86" t="s">
+      <c r="D34" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="E34" s="87"/>
-      <c r="F34" s="88"/>
+      <c r="E34" s="128"/>
+      <c r="F34" s="129"/>
       <c r="G34" s="50" t="s">
         <v>152</v>
       </c>
@@ -4491,16 +4485,16 @@
     </row>
     <row r="35" spans="1:14" ht="50.4">
       <c r="A35" s="11"/>
-      <c r="B35" s="125"/>
+      <c r="B35" s="122"/>
       <c r="C35" s="50" t="str">
         <f>master!C24</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D35" s="86" t="s">
+      <c r="D35" s="127" t="s">
         <v>157</v>
       </c>
-      <c r="E35" s="87"/>
-      <c r="F35" s="88"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="129"/>
       <c r="G35" s="50" t="s">
         <v>156</v>
       </c>
@@ -4518,16 +4512,16 @@
     </row>
     <row r="36" spans="1:14" ht="25.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="125"/>
+      <c r="B36" s="122"/>
       <c r="C36" s="50" t="str">
         <f>master!C25</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D36" s="86" t="s">
+      <c r="D36" s="127" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="87"/>
-      <c r="F36" s="88"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="129"/>
       <c r="G36" s="50" t="s">
         <v>98</v>
       </c>
@@ -4545,16 +4539,16 @@
     </row>
     <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="125"/>
+      <c r="B37" s="122"/>
       <c r="C37" s="50" t="str">
         <f>master!C26</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D37" s="86" t="s">
+      <c r="D37" s="127" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="87"/>
-      <c r="F37" s="88"/>
+      <c r="E37" s="128"/>
+      <c r="F37" s="129"/>
       <c r="G37" s="50" t="s">
         <v>152</v>
       </c>
@@ -4572,16 +4566,16 @@
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="125"/>
+      <c r="B38" s="122"/>
       <c r="C38" s="50" t="str">
         <f>master!C27</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D38" s="86" t="s">
+      <c r="D38" s="127" t="s">
         <v>155</v>
       </c>
-      <c r="E38" s="87"/>
-      <c r="F38" s="88"/>
+      <c r="E38" s="128"/>
+      <c r="F38" s="129"/>
       <c r="G38" s="50" t="s">
         <v>153</v>
       </c>
@@ -4599,16 +4593,16 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="125"/>
+      <c r="B39" s="122"/>
       <c r="C39" s="50" t="str">
         <f>master!C28</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D39" s="86" t="s">
+      <c r="D39" s="127" t="s">
         <v>154</v>
       </c>
-      <c r="E39" s="87"/>
-      <c r="F39" s="88"/>
+      <c r="E39" s="128"/>
+      <c r="F39" s="129"/>
       <c r="G39" s="50" t="s">
         <v>153</v>
       </c>
@@ -4626,16 +4620,16 @@
     </row>
     <row r="40" spans="1:14" ht="25.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="126"/>
+      <c r="B40" s="123"/>
       <c r="C40" s="50" t="str">
         <f>master!C29</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D40" s="86" t="s">
+      <c r="D40" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="129"/>
       <c r="G40" s="50" t="s">
         <v>98</v>
       </c>
@@ -4653,574 +4647,531 @@
     </row>
     <row r="41" spans="1:14" ht="113.4">
       <c r="A41" s="11"/>
-      <c r="B41" s="121" t="str">
+      <c r="B41" s="118" t="str">
         <f>master!B31</f>
         <v>個人演習</v>
       </c>
-      <c r="C41" s="92" t="str">
+      <c r="C41" s="70" t="str">
         <f>master!C31</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D41" s="93" t="s">
+      <c r="D41" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="E41" s="94"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="92" t="s">
+      <c r="E41" s="113"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="H41" s="96"/>
-      <c r="I41" s="97" t="s">
+      <c r="H41" s="71"/>
+      <c r="I41" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="98">
+      <c r="J41" s="73">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K41" s="99"/>
+      <c r="K41" s="74"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="92" t="str">
+      <c r="B42" s="119"/>
+      <c r="C42" s="70" t="str">
         <f>master!C32</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D42" s="93" t="s">
+      <c r="D42" s="112" t="s">
         <v>118</v>
       </c>
-      <c r="E42" s="94"/>
-      <c r="F42" s="95"/>
-      <c r="G42" s="92" t="s">
+      <c r="E42" s="113"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="H42" s="96"/>
-      <c r="I42" s="97" t="s">
+      <c r="H42" s="71"/>
+      <c r="I42" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="98">
+      <c r="J42" s="73">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K42" s="99"/>
+      <c r="K42" s="74"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
     <row r="43" spans="1:14" ht="176.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="122"/>
-      <c r="C43" s="92" t="str">
+      <c r="B43" s="119"/>
+      <c r="C43" s="70" t="str">
         <f>master!C33</f>
         <v>サービスの検討</v>
       </c>
-      <c r="D43" s="93" t="s">
+      <c r="D43" s="112" t="s">
         <v>115</v>
       </c>
-      <c r="E43" s="94"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="92" t="s">
+      <c r="E43" s="113"/>
+      <c r="F43" s="114"/>
+      <c r="G43" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="H43" s="96"/>
-      <c r="I43" s="97" t="s">
+      <c r="H43" s="71"/>
+      <c r="I43" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="98">
+      <c r="J43" s="73">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K43" s="99"/>
+      <c r="K43" s="74"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
     <row r="44" spans="1:14" ht="138.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="122"/>
-      <c r="C44" s="92" t="str">
+      <c r="B44" s="119"/>
+      <c r="C44" s="70" t="str">
         <f>master!C34</f>
         <v>サービスのブラッシュアップ</v>
       </c>
-      <c r="D44" s="93" t="s">
+      <c r="D44" s="112" t="s">
         <v>114</v>
       </c>
-      <c r="E44" s="94"/>
-      <c r="F44" s="95"/>
-      <c r="G44" s="92" t="s">
+      <c r="E44" s="113"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="H44" s="96"/>
-      <c r="I44" s="97" t="s">
+      <c r="H44" s="71"/>
+      <c r="I44" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="98">
+      <c r="J44" s="73">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K44" s="99"/>
+      <c r="K44" s="74"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" ht="63">
       <c r="A45" s="11"/>
-      <c r="B45" s="122"/>
-      <c r="C45" s="92" t="str">
+      <c r="B45" s="119"/>
+      <c r="C45" s="70" t="str">
         <f>master!C35</f>
         <v>サービスの決定</v>
       </c>
-      <c r="D45" s="93" t="s">
+      <c r="D45" s="112" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="94"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="92" t="s">
+      <c r="E45" s="113"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="H45" s="96"/>
-      <c r="I45" s="97" t="s">
+      <c r="H45" s="71"/>
+      <c r="I45" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="98">
+      <c r="J45" s="73">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K45" s="99"/>
+      <c r="K45" s="74"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" ht="138.6">
       <c r="A46" s="11"/>
-      <c r="B46" s="122"/>
-      <c r="C46" s="92" t="str">
+      <c r="B46" s="119"/>
+      <c r="C46" s="70" t="str">
         <f>master!C36</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D46" s="93" t="s">
+      <c r="D46" s="112" t="s">
         <v>112</v>
       </c>
-      <c r="E46" s="94"/>
-      <c r="F46" s="95"/>
-      <c r="G46" s="92" t="s">
+      <c r="E46" s="113"/>
+      <c r="F46" s="114"/>
+      <c r="G46" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="H46" s="96"/>
-      <c r="I46" s="97" t="s">
+      <c r="H46" s="71"/>
+      <c r="I46" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="98" t="s">
+      <c r="J46" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="K46" s="99"/>
+      <c r="K46" s="74"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="123"/>
-      <c r="C47" s="92" t="str">
+      <c r="B47" s="120"/>
+      <c r="C47" s="70" t="str">
         <f>master!C37</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D47" s="93" t="s">
+      <c r="D47" s="112" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="94"/>
-      <c r="F47" s="95"/>
-      <c r="G47" s="92" t="s">
+      <c r="E47" s="113"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="96"/>
-      <c r="I47" s="97" t="s">
+      <c r="H47" s="71"/>
+      <c r="I47" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="98" t="s">
+      <c r="J47" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="K47" s="99"/>
+      <c r="K47" s="74"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
     <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="121" t="str">
+      <c r="B48" s="118" t="str">
         <f>master!B39</f>
         <v>チーム演習</v>
       </c>
-      <c r="C48" s="92" t="str">
+      <c r="C48" s="70" t="str">
         <f>master!C39</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D48" s="93" t="s">
+      <c r="D48" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="E48" s="94"/>
-      <c r="F48" s="95"/>
-      <c r="G48" s="92" t="s">
+      <c r="E48" s="113"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="H48" s="96"/>
-      <c r="I48" s="97" t="s">
+      <c r="H48" s="71"/>
+      <c r="I48" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="98">
+      <c r="J48" s="73">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K48" s="99"/>
+      <c r="K48" s="74"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="201.6">
       <c r="A49" s="11"/>
-      <c r="B49" s="122"/>
-      <c r="C49" s="92" t="str">
+      <c r="B49" s="119"/>
+      <c r="C49" s="70" t="str">
         <f>master!C40</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D49" s="93" t="s">
+      <c r="D49" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="E49" s="94"/>
-      <c r="F49" s="95"/>
-      <c r="G49" s="92" t="s">
+      <c r="E49" s="113"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="H49" s="96"/>
-      <c r="I49" s="97" t="s">
+      <c r="H49" s="71"/>
+      <c r="I49" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="98">
+      <c r="J49" s="73">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K49" s="99"/>
+      <c r="K49" s="74"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="25.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="122"/>
-      <c r="C50" s="92" t="str">
+      <c r="B50" s="119"/>
+      <c r="C50" s="70" t="str">
         <f>master!C41</f>
         <v>【参考】最終発表時の評価基準</v>
       </c>
-      <c r="D50" s="93" t="s">
+      <c r="D50" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="E50" s="94"/>
-      <c r="F50" s="95"/>
-      <c r="G50" s="92" t="s">
+      <c r="E50" s="113"/>
+      <c r="F50" s="114"/>
+      <c r="G50" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="H50" s="96"/>
-      <c r="I50" s="97" t="s">
+      <c r="H50" s="71"/>
+      <c r="I50" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="98">
+      <c r="J50" s="73">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K50" s="99"/>
+      <c r="K50" s="74"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" ht="113.4">
       <c r="A51" s="11"/>
-      <c r="B51" s="122"/>
-      <c r="C51" s="92" t="str">
+      <c r="B51" s="119"/>
+      <c r="C51" s="70" t="str">
         <f>master!C42</f>
         <v>サービスの提案</v>
       </c>
-      <c r="D51" s="93" t="s">
+      <c r="D51" s="112" t="s">
         <v>124</v>
       </c>
-      <c r="E51" s="94"/>
-      <c r="F51" s="95"/>
-      <c r="G51" s="92" t="s">
+      <c r="E51" s="113"/>
+      <c r="F51" s="114"/>
+      <c r="G51" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="H51" s="96"/>
-      <c r="I51" s="97" t="s">
+      <c r="H51" s="71"/>
+      <c r="I51" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J51" s="98">
+      <c r="J51" s="73">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="K51" s="99"/>
+      <c r="K51" s="74"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" ht="100.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="122"/>
-      <c r="C52" s="92" t="str">
+      <c r="B52" s="119"/>
+      <c r="C52" s="70" t="str">
         <f>master!C43</f>
         <v>サービスの決定（チーム）</v>
       </c>
-      <c r="D52" s="93" t="s">
+      <c r="D52" s="112" t="s">
         <v>125</v>
       </c>
-      <c r="E52" s="94"/>
-      <c r="F52" s="95"/>
-      <c r="G52" s="92" t="s">
+      <c r="E52" s="113"/>
+      <c r="F52" s="114"/>
+      <c r="G52" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="96"/>
-      <c r="I52" s="97" t="s">
+      <c r="H52" s="71"/>
+      <c r="I52" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J52" s="98" t="s">
+      <c r="J52" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="K52" s="99"/>
+      <c r="K52" s="74"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="113.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="122"/>
-      <c r="C53" s="92" t="str">
+      <c r="B53" s="119"/>
+      <c r="C53" s="70" t="str">
         <f>master!C44</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D53" s="93" t="s">
+      <c r="D53" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="E53" s="94"/>
-      <c r="F53" s="95"/>
-      <c r="G53" s="92" t="s">
+      <c r="E53" s="113"/>
+      <c r="F53" s="114"/>
+      <c r="G53" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="H53" s="96"/>
-      <c r="I53" s="97" t="s">
+      <c r="H53" s="71"/>
+      <c r="I53" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J53" s="98" t="s">
+      <c r="J53" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="K53" s="99"/>
+      <c r="K53" s="74"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="122"/>
-      <c r="C54" s="92" t="str">
+      <c r="B54" s="119"/>
+      <c r="C54" s="70" t="str">
         <f>master!C45</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D54" s="93" t="s">
+      <c r="D54" s="112" t="s">
         <v>111</v>
       </c>
-      <c r="E54" s="94"/>
-      <c r="F54" s="95"/>
-      <c r="G54" s="92" t="s">
+      <c r="E54" s="113"/>
+      <c r="F54" s="114"/>
+      <c r="G54" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="H54" s="96"/>
-      <c r="I54" s="97" t="s">
+      <c r="H54" s="71"/>
+      <c r="I54" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="98" t="s">
+      <c r="J54" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="K54" s="99"/>
+      <c r="K54" s="74"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="123"/>
-      <c r="C55" s="92" t="str">
+      <c r="B55" s="120"/>
+      <c r="C55" s="70" t="str">
         <f>master!C46</f>
         <v>発表のリハーサル</v>
       </c>
-      <c r="D55" s="93" t="s">
+      <c r="D55" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="94"/>
-      <c r="F55" s="95"/>
-      <c r="G55" s="92" t="s">
+      <c r="E55" s="113"/>
+      <c r="F55" s="114"/>
+      <c r="G55" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="96"/>
-      <c r="I55" s="97" t="s">
+      <c r="H55" s="71"/>
+      <c r="I55" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="J55" s="98" t="s">
+      <c r="J55" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="K55" s="99"/>
+      <c r="K55" s="74"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="100.8">
       <c r="A56" s="11"/>
-      <c r="B56" s="102" t="str">
+      <c r="B56" s="115" t="str">
         <f>master!B48</f>
         <v>発表会（ブロック代表の決定）</v>
       </c>
-      <c r="C56" s="103" t="str">
+      <c r="C56" s="77" t="str">
         <f>master!C48</f>
         <v>ブロック内発表の説明</v>
       </c>
-      <c r="D56" s="104" t="s">
+      <c r="D56" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="E56" s="105"/>
-      <c r="F56" s="106"/>
-      <c r="G56" s="103" t="s">
+      <c r="E56" s="131"/>
+      <c r="F56" s="132"/>
+      <c r="G56" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="H56" s="107"/>
-      <c r="I56" s="108" t="s">
+      <c r="H56" s="78"/>
+      <c r="I56" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="109">
+      <c r="J56" s="80">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K56" s="110"/>
+      <c r="K56" s="81"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="113.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="111"/>
-      <c r="C57" s="103" t="str">
+      <c r="B57" s="116"/>
+      <c r="C57" s="77" t="str">
         <f>master!C49</f>
         <v>ブロック内発表の実施</v>
       </c>
-      <c r="D57" s="104" t="s">
+      <c r="D57" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="E57" s="105"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="103" t="s">
+      <c r="E57" s="131"/>
+      <c r="F57" s="132"/>
+      <c r="G57" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="H57" s="107"/>
-      <c r="I57" s="108" t="s">
+      <c r="H57" s="78"/>
+      <c r="I57" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="J57" s="109" t="s">
+      <c r="J57" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="K57" s="110"/>
+      <c r="K57" s="81"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="25.2">
       <c r="A58" s="11"/>
-      <c r="B58" s="112"/>
-      <c r="C58" s="103" t="str">
+      <c r="B58" s="117"/>
+      <c r="C58" s="77" t="str">
         <f>master!C50</f>
         <v>ブロック代表（選抜チーム）の決定</v>
       </c>
-      <c r="D58" s="104" t="s">
+      <c r="D58" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E58" s="105"/>
-      <c r="F58" s="106"/>
-      <c r="G58" s="103" t="s">
+      <c r="E58" s="131"/>
+      <c r="F58" s="132"/>
+      <c r="G58" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="H58" s="107"/>
-      <c r="I58" s="108" t="s">
+      <c r="H58" s="78"/>
+      <c r="I58" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="J58" s="109">
+      <c r="J58" s="80">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K58" s="110"/>
+      <c r="K58" s="81"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="138.6">
       <c r="A59" s="11"/>
-      <c r="B59" s="113" t="str">
+      <c r="B59" s="82" t="str">
         <f>master!B51</f>
         <v>発表会（最終）</v>
       </c>
-      <c r="C59" s="103" t="str">
+      <c r="C59" s="77" t="str">
         <f>master!C51</f>
         <v>全体発表</v>
       </c>
-      <c r="D59" s="104"/>
-      <c r="E59" s="105"/>
-      <c r="F59" s="106"/>
-      <c r="G59" s="103" t="s">
+      <c r="D59" s="130"/>
+      <c r="E59" s="131"/>
+      <c r="F59" s="132"/>
+      <c r="G59" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="H59" s="107"/>
-      <c r="I59" s="108" t="s">
+      <c r="H59" s="78"/>
+      <c r="I59" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="J59" s="109" t="s">
+      <c r="J59" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="K59" s="110"/>
+      <c r="K59" s="81"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B41:B47"/>
-    <mergeCell ref="B48:B55"/>
-    <mergeCell ref="B29:B40"/>
-    <mergeCell ref="B17:B27"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
@@ -5232,8 +5183,51 @@
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B17:B27"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="B48:B55"/>
+    <mergeCell ref="B29:B40"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D43:F43"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5363,62 +5357,62 @@
       <c r="B18" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="100" t="s">
+      <c r="C18" s="75" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="75" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="C20" s="100" t="s">
+      <c r="C20" s="75" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="C21" s="100" t="s">
+      <c r="C21" s="75" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="C22" s="100" t="s">
+      <c r="C22" s="75" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="C23" s="100" t="s">
+      <c r="C23" s="75" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="C24" s="101" t="s">
+      <c r="C24" s="76" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="25" spans="2:3">
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="75" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" spans="2:3">
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="75" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="27" spans="2:3">
-      <c r="C27" s="100" t="s">
+      <c r="C27" s="75" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="C28" s="100" t="s">
+      <c r="C28" s="75" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="2:3">
-      <c r="C29" s="100" t="s">
+      <c r="C29" s="75" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5430,42 +5424,37 @@
       <c r="B31" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="100" t="s">
+      <c r="C31" s="75" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="32" spans="2:3">
-      <c r="C32" s="100" t="s">
+      <c r="C32" s="75" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="119"/>
-      <c r="C33" s="120" t="s">
+      <c r="C33" s="75" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="119"/>
-      <c r="C34" s="120" t="s">
+      <c r="C34" s="75" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="119"/>
-      <c r="C35" s="119" t="s">
+      <c r="C35" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="119"/>
-      <c r="C36" s="119" t="s">
+      <c r="C36" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="37" spans="2:3">
-      <c r="B37" s="119"/>
-      <c r="C37" s="119" t="s">
+      <c r="C37" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5477,47 +5466,42 @@
       <c r="B39" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="100" t="s">
+      <c r="C39" s="75" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="40" spans="2:3">
-      <c r="C40" s="100" t="s">
+      <c r="C40" s="75" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="C41" s="100" t="s">
+      <c r="C41" s="75" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" spans="2:3">
-      <c r="B42" s="119"/>
-      <c r="C42" s="120" t="s">
+      <c r="C42" s="75" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="B43" s="119"/>
-      <c r="C43" s="119" t="s">
+      <c r="C43" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" spans="2:3">
-      <c r="B44" s="119"/>
-      <c r="C44" s="119" t="s">
+      <c r="C44" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="B45" s="119"/>
-      <c r="C45" s="119" t="s">
+      <c r="C45" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="46" spans="2:3">
-      <c r="B46" s="119"/>
-      <c r="C46" s="119" t="s">
+      <c r="C46" t="s">
         <v>127</v>
       </c>
     </row>
@@ -5529,17 +5513,17 @@
       <c r="B48" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="100" t="s">
+      <c r="C48" s="75" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="49" spans="2:3">
-      <c r="C49" s="100" t="s">
+      <c r="C49" s="75" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="50" spans="2:3">
-      <c r="C50" s="100" t="s">
+      <c r="C50" s="75" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5547,7 +5531,7 @@
       <c r="B51" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="100" t="s">
+      <c r="C51" s="75" t="s">
         <v>85</v>
       </c>
     </row>

--- a/IG/AI Native-提案演習_IG.xlsx
+++ b/IG/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB9BC81-3836-44AD-9205-3A6007B4BCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B56974C-E254-42FB-93EB-3D02724950DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（5日）'!$A$1:$L$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="173">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -375,21 +375,6 @@
   </si>
   <si>
     <t>AI-02</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-01
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-01
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-01
-</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -448,16 +433,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-01
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-01
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>AI Native-提案演習</t>
     <rPh sb="10" eb="14">
       <t>テイアンエンシュウ</t>
@@ -626,13 +601,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>提案書サンプル</t>
-    <rPh sb="0" eb="3">
-      <t>テイアンショ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>2 日目</t>
     <rPh sb="2" eb="3">
       <t>ニチ</t>
@@ -676,32 +644,6 @@
     <t>予備</t>
     <rPh sb="0" eb="2">
       <t>ヨビ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>発表会（ブロック代表の決定）</t>
-    <rPh sb="0" eb="2">
-      <t>ハッピョウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ダイヒョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ケッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>発表会（最終）</t>
-    <rPh sb="2" eb="3">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サイシュウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -883,89 +825,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">成果物の概要について説明する。
-■成果物の種類
-　・企画提案書
-　　PowerPoint形式で作成すること
-　・プロトタイプ
-　　作成したアプリケーションのソースコード一式を提出すること
-　　ルートディレクトリをそのままzip化して提出すること
-　・命名規約
-　　企画提案書　→　チーム名_企画提案書.pptx
-　　プロトタイプ　→　チーム名_プロトタイプ.zip
-■提出方法
-　・提出方法：Teamの共有フォルダに格納してください。
-　・提出先：全体連絡・共通＞02_AIネイティブ提案企画研修＞03_提出先＞02_チーム演習
-</t>
-    <rPh sb="0" eb="3">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>テイシュツ</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">成果物の概要について説明する。
-■成果物の種類
-　・企画提案書
-　　PowerPoint形式で作成すること
-　・プロトタイプ
-　　作成したアプリケーションのソースコード一式を提出すること
-　　ルートディレクトリをそのままzip化して提出すること
-　・命名規約
-　　企画提案書　→　受講者ID_氏名_企画提案書.pptx
-　　プロトタイプ　→　受講者ID_氏名_プロトタイプ.zip
-■提出方法
-　・提出方法：Teamの共有フォルダに格納してください。
-　・提出先：全体連絡・共通＞02_AIネイティブ提案企画研修＞03_提出先＞01_個人演習
-</t>
-    <rPh sb="0" eb="3">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>テイシュツ</t>
-    </rPh>
-    <rPh sb="196" eb="198">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>評価基準を意識して発表することを説明する。</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キジュン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イシキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハッピョウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>サービスの決定（チーム）</t>
     <rPh sb="5" eb="7">
       <t>ケッテイ</t>
@@ -1009,47 +868,10 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>個人演習で作成した成果物をチーム内で提案することを説明する。
-■手順
-1. 提案順を決定する。
-2. 企画提案書およびプロトタイプを用いてサービスを提案する。
-3. 提案内容に対する質疑応答を行う。
-※手順2～3を参加者ごとに繰り返し実施する。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>チームとして提案するサービスを決定することを説明する。
-サービスの決定方法は問わないが、以下のいずれかの方法で決定すること。
-・チームメンバーが提案したサービス案の中から、代表となるサービスを選定する。
-・複数のサービス案の良い点を組み合わせ、新たなサービスとして再構築する。
-決定にあたっては、提供価値、社会的意義、実現性、市場性などの観点を考慮すること。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>決定したサービスについて、チームで企画提案書およびプロトタイプを作成することを説明する。
 個人演習で作成した成果物やチーム内での議論を踏まえ、サービス内容をブラッシュアップすること。
 また、課題の背景、ターゲットユーザー、提供価値、社会的意義、実現性、市場性などの観点からサービスを深掘りし、チームとしての提案内容を具体化すること。
 ブラッシュアップおよび深掘りした内容を企画提案書にまとめるとともに、サービスの利用イメージが伝わるプロトタイプを作成すること。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>発表のリハーサル</t>
-    <rPh sb="0" eb="2">
-      <t>ハッピョウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>各チーム内でリハーサルを行う。</t>
-    <rPh sb="0" eb="1">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オコナ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1106,15 +928,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>個人演習で作成した成果物をチーム内で提案することを説明する。
-■手順
-1. 提案順を決定する。
-2. 企画提案書およびプロトタイプを用いてサービスを提案する。
-3. 提案内容に対する質疑応答を行う。
-※手順2～3をチームごとに繰り返し実施する。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>NTTデータ デジタルソサエティ事業部が掲げる理念であり、ITやデジタル技術を活用して社会課題の解決に貢献し、より良い社会を創り出すことを意味する。
 利用者である国民の目線を重視しながら、行政サービスの利便性向上やデジタル化を推進することで、誰一人取り残さない社会の実現を目指している。</t>
     <phoneticPr fontId="3"/>
@@ -1166,42 +979,6 @@
     </rPh>
     <rPh sb="50" eb="52">
       <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>まずは「日常の不便」を出発点にすることで、現実的で価値のある改善アイデアにつながることを説明する。
-※注意点
-自分だけの不便を起点にすると視野が狭くなりやすいため、そのままではサービスとしての価値が限定されてしまいます。
-そこで、段階的に視点を広げることで、社会的な意味のある課題へと発展させます。
-① 自分の不便（起点）
-② 他の人も同じか？（共通性の確認）
-③ どの層に共通するか？（対象の整理・分類）
-④ 社会課題として成立するか？（抽象化・構造化）
-このように段階的に拡張することで、単なる個人の体験ではなく、サービスや仕組みとして解決すべき社会課題として捉えることができる。</t>
-    <rPh sb="4" eb="6">
-      <t>ニチジョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>フベン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>シュッパツテン</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ゲンジツテキ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カチ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カイゼン</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="52" eb="55">
-      <t>チュウイテン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1324,23 +1101,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>現状課題（What＝具体的なこまりごと）を説明する。</t>
-    <rPh sb="10" eb="13">
-      <t>グタイテキ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>背景（Why＝なぜ？）を説明する。</t>
-    <rPh sb="12" eb="14">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>提案内容と提案先企業が記載されていることを説明する。</t>
     <rPh sb="0" eb="2">
       <t>テイアン</t>
@@ -1379,17 +1139,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>サービスの提供価値について説明する。
-※Before / After フレームを利用するとわかりやすい。</t>
-    <rPh sb="13" eb="15">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-02
 </t>
     <phoneticPr fontId="3"/>
@@ -1397,29 +1146,6 @@
   <si>
     <t xml:space="preserve">・AI-02
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">リスクと課題について説明する。
-リスク：うまくいかない可能性・障害要因
-課題：解決すべき問題そのもの
-対策：課題に対する、解決策
-</t>
-    <rPh sb="10" eb="12">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>タイサク</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="61" eb="64">
-      <t>カイケツサク</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1433,29 +1159,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サービスの利用者体験イメージを説明する。
-ペルソナ：サービスを使う代表的なユーザー像を具体的に作ったもの
-ストーリーボード：ユーザーがサービスを使う流れを物語（ストーリー）形式で描いたもの</t>
-    <rPh sb="5" eb="7">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>タイケン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>周囲の環境変化や市場の動きがどのように影響するかを分析していることを説明する。
 ・社会動向：社会全体で起きている大きな変化
 ・業界動向：対象となる業界内で起きている変化
@@ -1466,7 +1169,32 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>現状課題を解決するためのサービス概要（サービスの全体像）を説明する。
+    <t>ー</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案書のサンプルについて</t>
+    <rPh sb="0" eb="3">
+      <t>テイアンショ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>市場機会（まだ十分に満たされていないニーズが存在し、価値提供できる可能性がある領域）について説明する。
+※3C分析により、顧客ニーズ・競合状況・自社の強みを整理し、市場機会を明らかにしている。</t>
+    <rPh sb="0" eb="2">
+      <t>シジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>現状課題を解決するためのサービス概要（サービスの全体像）について説明する。
 ※利用者目線のみ</t>
     <rPh sb="0" eb="2">
       <t>ゲンジョウ</t>
@@ -1480,46 +1208,529 @@
     <rPh sb="16" eb="18">
       <t>ガイヨウ</t>
     </rPh>
-    <rPh sb="29" eb="31">
+    <rPh sb="32" eb="34">
       <t>セツメイ</t>
     </rPh>
-    <rPh sb="36" eb="39">
+    <rPh sb="39" eb="42">
       <t>リヨウシャ</t>
     </rPh>
-    <rPh sb="39" eb="41">
+    <rPh sb="42" eb="44">
       <t>メセン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>サービスの今後の展望について説明する。</t>
+    <t>サービスの利用者体験イメージ（利用者がサービスを利用する前から利用後まで、どのような体験をし、どのような価値を感じるのかを具体的に描いたもの）について説明する。
+ペルソナ：サービスを使う代表的なユーザー像を具体的に作ったもの
+ストーリーボード：ユーザーがサービスを使う流れを物語（ストーリー）形式で描いたもの</t>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>サービスの提供価値（サービスによって利用者が得られるメリットや良い変化）について説明する。
+※Before / After フレームを利用するとわかりやすい。</t>
+    <rPh sb="28" eb="30">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">リスク、課題、対策について説明する。
+リスク：うまくいかない可能性・障害要因
+課題：解決すべき問題そのもの
+対策：課題に対する、解決策
+</t>
+    <rPh sb="7" eb="9">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>カイケツサク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>サービスの今後の展望（サービスを今後どのように発展させていくか、将来的にどのような価値を実現したいか）について説明する。</t>
     <rPh sb="5" eb="7">
       <t>コンゴ</t>
     </rPh>
     <rPh sb="8" eb="10">
       <t>テンボウ</t>
     </rPh>
-    <rPh sb="14" eb="16">
+    <rPh sb="55" eb="57">
       <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>市場機会について説明する。
-3C分析により、顧客ニーズ・競合状況・自社の強みを整理し、市場機会（まだ十分に満たされていないニーズが存在し、価値提供できる可能性がある領域）を明らかにしている。</t>
+    <t xml:space="preserve">成果物の概要について説明する。
+■成果物の種類
+　・企画提案書
+　　PowerPoint形式
+　・プロトタイプ
+　　作成したアプリケーションのソースコード一式
+　　※ルートディレクトリをそのままzip化する
+　・命名規約
+　　企画提案書　→　受講者ID_氏名_企画提案書.pptx
+　　プロトタイプ　→　受講者ID_氏名_プロトタイプ.zip
+■提出方法
+　・提出先：Teamの共有フォルダに格納してください。
+　　※全体連絡・共通＞02_AIネイティブ提案企画研修＞03_提出先＞01_個人演習
+</t>
+    <rPh sb="0" eb="3">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">成果物の概要について説明する。
+■成果物の種類
+　・企画提案書
+　　PowerPoint形式
+　・プロトタイプ
+　　作成したアプリケーションのソースコード一式
+　　※ルートディレクトリをそのままzip化する
+　・命名規約
+　　企画提案書　→　チーム名_企画提案書.pptx
+　　プロトタイプ　→　チーム名_プロトタイプ.zip
+■提出方法
+　・提出先：Teamの共有フォルダ
+　　※全体連絡・共通＞02_AIネイティブ提案企画研修＞03_提出先＞02_チーム演習
+</t>
+    <rPh sb="0" eb="3">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">評価基準は存在してること説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※本研修の提案書として正しい内容であればよい。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <rPh sb="0" eb="2">
-      <t>シジョウ</t>
+      <t>ヒョウカ</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>キカイ</t>
+      <t>キジュン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>テイアンショ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">チームとして提案するサービスを決定することを説明する。
+サービスの決定方法は問わないが、以下のいずれかの方法で決定すること。
+・チームメンバーが提案したサービス案の中から、代表となるサービスを選定する。
+・複数のサービス案の良い点を組み合わせ、新たなサービスとして再構築する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※決定にあたっては、提供価値、社会的意義、実現性、市場性などの観点を考慮すること。</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景（サービスを取り巻く状況や市場動向を説明＝Why＝なぜ？）について説明する。</t>
+    <rPh sb="35" eb="37">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>現状課題（背景によって発生している問題を説明＝What＝具体的なこまりごと）について説明する。</t>
+    <rPh sb="28" eb="31">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>はじめに</t>
+    <phoneticPr fontId="23"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">本資料はあくまでサンプルであることを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※記載内容や構成は一例であり、サービスの特性に応じて自由に調整しても良い。</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イチレイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>トクセイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>発表に向けて、チーム内で提案内容のリハーサルを実施してもらうことを説明する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案のリハーサル</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>個人演習で作成した成果物をチーム内で提案してもらうことを説明する。
+■手順
+1. 提案内容の発表順を決定する。
+2. 企画提案書およびプロトタイプを用いてサービスを提案する。
+3. 提案内容に対する質疑応答を行う。
+※手順2～3を繰り返し実施する。</t>
+  </si>
+  <si>
+    <t>チーム演習で作成した成果物をブロック内で提案してもらうことを説明する。
+■手順
+1. 提案内容の発表順を決定する。（15分）
+2. 企画提案書およびプロトタイプを用いてサービスを提案する。（15分）
+3. 提案内容に対する質疑応答を行う。（5分）
+※手順2～3をチームごとに繰り返し実施する。</t>
+    <rPh sb="3" eb="5">
+      <t>エンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ブロック代表の成果物を全体に提案してもらうことを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">※提案内容の発表順については講師側で決定しておく。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+■手順
+1. 企画提案書およびプロトタイプを用いてサービスを提案する。（15分）
+2. 提案内容に対する質疑応答を行う。（8分）
+※手順1～2をブロック代表ごとに繰り返し実施する。</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>コウシ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">まずは「日常の不便」を出発点にすることで、現実的で価値のある改善アイデアにつながることを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※注意点
+自分だけの不便を起点にすると視野が狭くなりやすいため、そのままではサービスとしての価値が限定されてしまう。
+そこで、段階的に視点を広げることで、社会的な意味のある課題へと発展させる。
+1. 自分の不便（起点）
+2. 他の人も同じか？（共通性の確認）
+3. どの層に共通するか？（対象の整理・分類）
+4. 社会課題として成立するか？（抽象化・構造化）
+このように段階的に拡張することで、単なる個人の体験ではなく、サービスや仕組みとして解決すべき社会課題として捉えることができる。</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t>ニチジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フベン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>シュッパツテン</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ゲンジツテキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>チュウイテン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>オリエンテーション（2日目以降）</t>
+    <rPh sb="11" eb="12">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>オリエンテーション（初日）</t>
+    <rPh sb="10" eb="12">
+      <t>ショニチ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・本日のスケジュールの説明</t>
+    <rPh sb="1" eb="3">
+      <t>ホンジツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・共通1
+</t>
+    <rPh sb="1" eb="3">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案会（ブロック代表の決定）</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カイ</t>
     </rPh>
     <rPh sb="8" eb="10">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ー</t>
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案会（最終）</t>
+    <rPh sb="0" eb="3">
+      <t>テイアンカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョウシツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ダイヒョウ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1950,7 +2161,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2116,9 +2327,6 @@
     <xf numFmtId="20" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -2263,15 +2471,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2287,6 +2486,15 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2296,6 +2504,33 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
@@ -2314,40 +2549,10 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2732,19 +2937,19 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="96" t="str">
+      <c r="B2" s="95" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案演習_IG」</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="3" spans="1:11" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -2761,10 +2966,10 @@
     </row>
     <row r="4" spans="1:11" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="98"/>
+      <c r="C4" s="97"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2776,8 +2981,8 @@
     </row>
     <row r="5" spans="1:11" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="100"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -2794,10 +2999,10 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="16.2">
-      <c r="B7" s="101" t="s">
+      <c r="B7" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="101"/>
+      <c r="C7" s="100"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -2820,19 +3025,19 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H9" s="24"/>
       <c r="I9" s="24" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J9" s="24"/>
       <c r="K9" s="24" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.25" customHeight="1">
@@ -2842,252 +3047,249 @@
       <c r="B10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="62" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="62" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="62" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="62" t="s">
         <v>3</v>
       </c>
       <c r="J10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="K10" s="63" t="s">
+      <c r="K10" s="62" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="39"/>
-      <c r="B11" s="58">
+      <c r="B11" s="57">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="61" t="str">
+      <c r="C11" s="60" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="57">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="94"/>
-      <c r="F11" s="58">
+      <c r="E11" s="93"/>
+      <c r="F11" s="57">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="94" t="str">
-        <f>master!B39</f>
+      <c r="G11" s="93" t="str">
+        <f>master!B40</f>
         <v>チーム演習</v>
       </c>
-      <c r="H11" s="58">
+      <c r="H11" s="57">
         <v>0.40625</v>
       </c>
-      <c r="I11" s="95"/>
-      <c r="J11" s="58">
+      <c r="I11" s="94"/>
+      <c r="J11" s="57">
         <v>0.40625</v>
       </c>
-      <c r="K11" s="83" t="str">
-        <f>master!B48</f>
-        <v>発表会（ブロック代表の決定）</v>
+      <c r="K11" s="82" t="str">
+        <f>master!B49</f>
+        <v>提案会（ブロック代表の決定）</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="90">
+      <c r="B12" s="89">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C12" s="61" t="str">
+      <c r="C12" s="60" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="84"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="83"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="38"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="62" t="str">
-        <f>master!B16</f>
-        <v>まとめ</v>
-      </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="84"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="83"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="38"/>
-      <c r="B14" s="58">
+      <c r="B14" s="57">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="61" t="str">
+      <c r="C14" s="60" t="str">
         <f>master!B18</f>
-        <v>提案書サンプル</v>
-      </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="84"/>
+        <v>提案書のサンプルについて</v>
+      </c>
+      <c r="D14" s="59"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="83"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="39"/>
-      <c r="B15" s="92" t="s">
+      <c r="B15" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="84"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="83"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="37">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="58">
+      <c r="B16" s="57">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="94" t="str">
-        <f>master!B31</f>
+      <c r="C16" s="93" t="str">
+        <f>master!B32</f>
         <v>個人演習</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="84"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="83"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="38"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="84"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="83"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="38"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="84"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="83"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="39"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="84"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="83"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="57">
+      <c r="A20" s="56">
         <v>0.5</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="84"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="83"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="52"/>
       <c r="B21" s="54"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="95"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="94"/>
       <c r="J21" s="54"/>
-      <c r="K21" s="85"/>
+      <c r="K21" s="84"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="38"/>
       <c r="B22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="63" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="63" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="63" t="s">
         <v>1</v>
       </c>
       <c r="H22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="I22" s="64" t="s">
+      <c r="I22" s="63" t="s">
         <v>1</v>
       </c>
       <c r="J22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="K22" s="64" t="s">
+      <c r="K22" s="63" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3096,23 +3298,23 @@
       <c r="B23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="65"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="65"/>
+      <c r="G23" s="64"/>
       <c r="H23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="65"/>
+      <c r="I23" s="64"/>
       <c r="J23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="65"/>
+      <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="37">
@@ -3121,199 +3323,199 @@
       <c r="B24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="65"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="65"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="65"/>
+      <c r="I24" s="64"/>
       <c r="J24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="K24" s="65"/>
+      <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="38"/>
       <c r="B25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="66"/>
+      <c r="C25" s="65"/>
       <c r="D25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="66"/>
+      <c r="E25" s="65"/>
       <c r="F25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="66"/>
+      <c r="G25" s="65"/>
       <c r="H25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="66"/>
+      <c r="I25" s="65"/>
       <c r="J25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="66"/>
+      <c r="K25" s="65"/>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="38"/>
       <c r="B26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="94"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="94"/>
+      <c r="E26" s="93"/>
       <c r="F26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="94"/>
+      <c r="G26" s="93"/>
       <c r="H26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="I26" s="94"/>
+      <c r="I26" s="93"/>
       <c r="J26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="K26" s="83" t="str">
-        <f>master!B51</f>
-        <v>発表会（最終）</v>
+      <c r="K26" s="82" t="str">
+        <f>master!B52</f>
+        <v>提案会（最終）</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="95"/>
+      <c r="C27" s="94"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="95"/>
+      <c r="E27" s="94"/>
       <c r="F27" s="42"/>
-      <c r="G27" s="95"/>
+      <c r="G27" s="94"/>
       <c r="H27" s="42"/>
-      <c r="I27" s="95"/>
+      <c r="I27" s="94"/>
       <c r="J27" s="42"/>
-      <c r="K27" s="84"/>
+      <c r="K27" s="83"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="37">
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="42"/>
-      <c r="C28" s="95"/>
+      <c r="C28" s="94"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="95"/>
+      <c r="E28" s="94"/>
       <c r="F28" s="42"/>
-      <c r="G28" s="95"/>
+      <c r="G28" s="94"/>
       <c r="H28" s="42"/>
-      <c r="I28" s="95"/>
+      <c r="I28" s="94"/>
       <c r="J28" s="42"/>
-      <c r="K28" s="84"/>
+      <c r="K28" s="83"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="38"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="95"/>
+      <c r="C29" s="94"/>
       <c r="D29" s="42"/>
-      <c r="E29" s="95"/>
+      <c r="E29" s="94"/>
       <c r="F29" s="42"/>
-      <c r="G29" s="95"/>
+      <c r="G29" s="94"/>
       <c r="H29" s="42"/>
-      <c r="I29" s="95"/>
+      <c r="I29" s="94"/>
       <c r="J29" s="42"/>
-      <c r="K29" s="84"/>
+      <c r="K29" s="83"/>
       <c r="L29" s="51"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="38"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="95"/>
+      <c r="C30" s="94"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="95"/>
+      <c r="E30" s="94"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="95"/>
+      <c r="G30" s="94"/>
       <c r="H30" s="42"/>
-      <c r="I30" s="95"/>
+      <c r="I30" s="94"/>
       <c r="J30" s="42"/>
-      <c r="K30" s="84"/>
+      <c r="K30" s="83"/>
       <c r="L30" s="51"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="39"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="95"/>
+      <c r="C31" s="94"/>
       <c r="D31" s="42"/>
-      <c r="E31" s="95"/>
+      <c r="E31" s="94"/>
       <c r="F31" s="42"/>
-      <c r="G31" s="95"/>
+      <c r="G31" s="94"/>
       <c r="H31" s="42"/>
-      <c r="I31" s="95"/>
+      <c r="I31" s="94"/>
       <c r="J31" s="42"/>
-      <c r="K31" s="84"/>
+      <c r="K31" s="83"/>
       <c r="L31" s="51"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="57">
+      <c r="A32" s="56">
         <v>0.625</v>
       </c>
       <c r="B32" s="42"/>
-      <c r="C32" s="95"/>
+      <c r="C32" s="94"/>
       <c r="D32" s="42"/>
-      <c r="E32" s="95"/>
+      <c r="E32" s="94"/>
       <c r="F32" s="42"/>
-      <c r="G32" s="95"/>
+      <c r="G32" s="94"/>
       <c r="H32" s="42"/>
-      <c r="I32" s="95"/>
+      <c r="I32" s="94"/>
       <c r="J32" s="42"/>
-      <c r="K32" s="84"/>
+      <c r="K32" s="83"/>
       <c r="L32" s="51"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="52"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="95"/>
+      <c r="C33" s="94"/>
       <c r="D33" s="42"/>
-      <c r="E33" s="95"/>
+      <c r="E33" s="94"/>
       <c r="F33" s="42"/>
-      <c r="G33" s="95"/>
+      <c r="G33" s="94"/>
       <c r="H33" s="42"/>
-      <c r="I33" s="95"/>
+      <c r="I33" s="94"/>
       <c r="J33" s="42"/>
-      <c r="K33" s="84"/>
+      <c r="K33" s="83"/>
       <c r="L33" s="51"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="52"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="95"/>
+      <c r="C34" s="94"/>
       <c r="D34" s="42"/>
-      <c r="E34" s="95"/>
+      <c r="E34" s="94"/>
       <c r="F34" s="42"/>
-      <c r="G34" s="95"/>
+      <c r="G34" s="94"/>
       <c r="H34" s="42"/>
-      <c r="I34" s="95"/>
+      <c r="I34" s="94"/>
       <c r="J34" s="42"/>
-      <c r="K34" s="84"/>
+      <c r="K34" s="83"/>
       <c r="L34" s="51"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="39"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="95"/>
+      <c r="C35" s="94"/>
       <c r="D35" s="42"/>
-      <c r="E35" s="95"/>
+      <c r="E35" s="94"/>
       <c r="F35" s="42"/>
-      <c r="G35" s="95"/>
+      <c r="G35" s="94"/>
       <c r="H35" s="42"/>
-      <c r="I35" s="95"/>
+      <c r="I35" s="94"/>
       <c r="J35" s="42"/>
-      <c r="K35" s="84"/>
+      <c r="K35" s="83"/>
       <c r="L35" s="51"/>
     </row>
     <row r="36" spans="1:12">
@@ -3321,57 +3523,57 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="42"/>
-      <c r="C36" s="95"/>
+      <c r="C36" s="94"/>
       <c r="D36" s="42"/>
-      <c r="E36" s="95"/>
+      <c r="E36" s="94"/>
       <c r="F36" s="42"/>
-      <c r="G36" s="95"/>
+      <c r="G36" s="94"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="95"/>
+      <c r="I36" s="94"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="84"/>
+      <c r="K36" s="83"/>
       <c r="L36" s="51"/>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="38"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="95"/>
+      <c r="C37" s="94"/>
       <c r="D37" s="42"/>
-      <c r="E37" s="95"/>
+      <c r="E37" s="94"/>
       <c r="F37" s="42"/>
-      <c r="G37" s="95"/>
+      <c r="G37" s="94"/>
       <c r="H37" s="42"/>
-      <c r="I37" s="95"/>
+      <c r="I37" s="94"/>
       <c r="J37" s="42"/>
-      <c r="K37" s="84"/>
+      <c r="K37" s="83"/>
       <c r="L37" s="51"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="38"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="95"/>
+      <c r="C38" s="94"/>
       <c r="D38" s="42"/>
-      <c r="E38" s="95"/>
+      <c r="E38" s="94"/>
       <c r="F38" s="42"/>
-      <c r="G38" s="95"/>
+      <c r="G38" s="94"/>
       <c r="H38" s="42"/>
-      <c r="I38" s="95"/>
+      <c r="I38" s="94"/>
       <c r="J38" s="42"/>
-      <c r="K38" s="84"/>
+      <c r="K38" s="83"/>
       <c r="L38" s="51"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="38"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="95"/>
+      <c r="C39" s="94"/>
       <c r="D39" s="42"/>
-      <c r="E39" s="95"/>
+      <c r="E39" s="94"/>
       <c r="F39" s="42"/>
-      <c r="G39" s="95"/>
+      <c r="G39" s="94"/>
       <c r="H39" s="42"/>
-      <c r="I39" s="95"/>
+      <c r="I39" s="94"/>
       <c r="J39" s="42"/>
-      <c r="K39" s="84"/>
+      <c r="K39" s="83"/>
       <c r="L39" s="51"/>
     </row>
     <row r="40" spans="1:12">
@@ -3379,76 +3581,76 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="B40" s="42"/>
-      <c r="C40" s="95"/>
+      <c r="C40" s="94"/>
       <c r="D40" s="42"/>
-      <c r="E40" s="95"/>
+      <c r="E40" s="94"/>
       <c r="F40" s="42"/>
-      <c r="G40" s="95"/>
+      <c r="G40" s="94"/>
       <c r="H40" s="42"/>
-      <c r="I40" s="95"/>
+      <c r="I40" s="94"/>
       <c r="J40" s="42"/>
-      <c r="K40" s="84"/>
+      <c r="K40" s="83"/>
       <c r="L40" s="51"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="38"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="95"/>
+      <c r="C41" s="94"/>
       <c r="D41" s="42"/>
-      <c r="E41" s="95"/>
+      <c r="E41" s="94"/>
       <c r="F41" s="42"/>
-      <c r="G41" s="95"/>
+      <c r="G41" s="94"/>
       <c r="H41" s="42"/>
-      <c r="I41" s="95"/>
+      <c r="I41" s="94"/>
       <c r="J41" s="42"/>
-      <c r="K41" s="84"/>
+      <c r="K41" s="83"/>
       <c r="L41" s="53"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="42"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="93"/>
+      <c r="C42" s="92"/>
       <c r="D42" s="42"/>
-      <c r="E42" s="93"/>
+      <c r="E42" s="92"/>
       <c r="F42" s="42"/>
-      <c r="G42" s="93"/>
+      <c r="G42" s="92"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="93"/>
+      <c r="I42" s="92"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="85"/>
+      <c r="K42" s="84"/>
       <c r="L42" s="51"/>
     </row>
     <row r="43" spans="1:12" ht="14.25" customHeight="1">
       <c r="A43" s="41"/>
-      <c r="B43" s="86">
+      <c r="B43" s="85">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" s="86">
+      <c r="C43" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="85">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="86">
+      <c r="E43" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="85">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="86">
+      <c r="G43" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="85">
         <v>0.73958333333333337</v>
       </c>
-      <c r="I43" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="J43" s="86">
+      <c r="I43" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="J43" s="85">
         <v>0.73958333333333337</v>
       </c>
-      <c r="K43" s="87" t="s">
-        <v>93</v>
+      <c r="K43" s="86" t="s">
+        <v>87</v>
       </c>
       <c r="L43" s="52"/>
     </row>
@@ -3471,7 +3673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L13"/>
+  <dimension ref="A2:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3514,10 +3716,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="107"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3528,16 +3730,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3550,10 +3752,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="33"/>
-      <c r="D7" s="109" t="s">
+      <c r="D7" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="109"/>
+      <c r="E7" s="105"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -3593,74 +3795,99 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103" t="s">
+      <c r="B11" s="102"/>
+      <c r="C11" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="103" t="s">
+      <c r="D11" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103" t="s">
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="110" t="s">
+      <c r="H11" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="102" t="s">
+      <c r="I11" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102" t="s">
+      <c r="J11" s="101"/>
+      <c r="K11" s="101" t="s">
         <v>31</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="111"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="107"/>
       <c r="I12" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="103"/>
+      <c r="K12" s="102"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="104" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="105"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="55" t="s">
-        <v>45</v>
+        <v>168</v>
+      </c>
+      <c r="D13" s="129" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="130" t="s">
+        <v>42</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="56">
+      <c r="J13" s="55">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="10"/>
     </row>
+    <row r="14" spans="1:12" ht="25.2">
+      <c r="A14" s="10"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="129" t="s">
+        <v>169</v>
+      </c>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="130" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="55">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="B4:C4"/>
@@ -3684,7 +3911,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H13:H14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3694,7 +3921,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N59"/>
+  <dimension ref="A2:N60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3744,12 +3971,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3760,30 +3987,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30"/>
     </row>
@@ -3824,8 +4051,8 @@
       <c r="B9" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="59" t="s">
-        <v>53</v>
+      <c r="C9" s="58" t="s">
+        <v>48</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>19</v>
@@ -3846,8 +4073,8 @@
       <c r="B10" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="59" t="s">
-        <v>54</v>
+      <c r="C10" s="58" t="s">
+        <v>49</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>19</v>
@@ -3866,10 +4093,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D11" s="36" t="s">
         <v>19</v>
@@ -3888,10 +4115,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="B12" s="34" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>19</v>
@@ -3910,28 +4137,28 @@
     </row>
     <row r="14" spans="1:14" ht="24" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="103" t="s">
+      <c r="C14" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="103" t="s">
+      <c r="D14" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103" t="s">
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="102" t="s">
+      <c r="H14" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="124" t="s">
+      <c r="I14" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="125"/>
-      <c r="K14" s="102" t="s">
+      <c r="J14" s="121"/>
+      <c r="K14" s="101" t="s">
         <v>33</v>
       </c>
       <c r="L14" s="6"/>
@@ -3940,27 +4167,27 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="10"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="102"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="101"/>
       <c r="I15" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="103"/>
+      <c r="K15" s="102"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="63">
       <c r="A16" s="10"/>
-      <c r="B16" s="88" t="str">
+      <c r="B16" s="87" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
@@ -3968,13 +4195,13 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D16" s="127" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="128"/>
-      <c r="F16" s="129"/>
+      <c r="D16" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="109"/>
+      <c r="F16" s="110"/>
       <c r="G16" s="50" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="48" t="s">
@@ -3988,9 +4215,9 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="102" customHeight="1">
+    <row r="17" spans="1:14" ht="63">
       <c r="A17" s="10"/>
-      <c r="B17" s="121" t="str">
+      <c r="B17" s="117" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -3998,13 +4225,13 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D17" s="127" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" s="128"/>
-      <c r="F17" s="129"/>
+      <c r="D17" s="108" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="109"/>
+      <c r="F17" s="110"/>
       <c r="G17" s="50" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="48" t="s">
@@ -4018,20 +4245,20 @@
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="176.4">
+    <row r="18" spans="1:14" ht="163.80000000000001">
       <c r="A18" s="11"/>
-      <c r="B18" s="122"/>
+      <c r="B18" s="118"/>
       <c r="C18" s="50" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D18" s="127" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="128"/>
-      <c r="F18" s="129"/>
+      <c r="D18" s="108" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="109"/>
+      <c r="F18" s="110"/>
       <c r="G18" s="50" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="48" t="s">
@@ -4047,18 +4274,18 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="122"/>
+      <c r="B19" s="118"/>
       <c r="C19" s="50" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D19" s="127" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="128"/>
-      <c r="F19" s="129"/>
+      <c r="D19" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="109"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="48" t="s">
@@ -4074,18 +4301,18 @@
     </row>
     <row r="20" spans="1:14" ht="151.19999999999999">
       <c r="A20" s="11"/>
-      <c r="B20" s="122"/>
+      <c r="B20" s="118"/>
       <c r="C20" s="50" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D20" s="127" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" s="128"/>
-      <c r="F20" s="129"/>
+      <c r="D20" s="108" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="109"/>
+      <c r="F20" s="110"/>
       <c r="G20" s="50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="48" t="s">
@@ -4101,18 +4328,18 @@
     </row>
     <row r="21" spans="1:14" ht="252">
       <c r="A21" s="11"/>
-      <c r="B21" s="122"/>
+      <c r="B21" s="118"/>
       <c r="C21" s="50" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D21" s="127" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="128"/>
-      <c r="F21" s="129"/>
+      <c r="D21" s="108" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="109"/>
+      <c r="F21" s="110"/>
       <c r="G21" s="50" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="48" t="s">
@@ -4128,18 +4355,18 @@
     </row>
     <row r="22" spans="1:14" ht="126">
       <c r="A22" s="11"/>
-      <c r="B22" s="122"/>
+      <c r="B22" s="118"/>
       <c r="C22" s="50" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D22" s="127" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="128"/>
-      <c r="F22" s="129"/>
+      <c r="D22" s="108" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="109"/>
+      <c r="F22" s="110"/>
       <c r="G22" s="50" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="48" t="s">
@@ -4155,18 +4382,18 @@
     </row>
     <row r="23" spans="1:14" ht="63">
       <c r="A23" s="11"/>
-      <c r="B23" s="122"/>
+      <c r="B23" s="118"/>
       <c r="C23" s="50" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D23" s="127" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="128"/>
-      <c r="F23" s="129"/>
+      <c r="D23" s="108" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="109"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="50" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="48" t="s">
@@ -4182,18 +4409,18 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="122"/>
+      <c r="B24" s="118"/>
       <c r="C24" s="50" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D24" s="127" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" s="128"/>
-      <c r="F24" s="129"/>
+      <c r="D24" s="108" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="109"/>
+      <c r="F24" s="110"/>
       <c r="G24" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="48" t="s">
@@ -4209,18 +4436,18 @@
     </row>
     <row r="25" spans="1:14" ht="75.599999999999994">
       <c r="A25" s="11"/>
-      <c r="B25" s="122"/>
+      <c r="B25" s="118"/>
       <c r="C25" s="50" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D25" s="127" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="128"/>
-      <c r="F25" s="129"/>
+      <c r="D25" s="108" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="109"/>
+      <c r="F25" s="110"/>
       <c r="G25" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="48" t="s">
@@ -4236,18 +4463,18 @@
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="122"/>
+      <c r="B26" s="118"/>
       <c r="C26" s="50" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D26" s="127" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="128"/>
-      <c r="F26" s="129"/>
+      <c r="D26" s="108" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" s="109"/>
+      <c r="F26" s="110"/>
       <c r="G26" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="48" t="s">
@@ -4263,18 +4490,18 @@
     </row>
     <row r="27" spans="1:14" ht="88.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="123"/>
+      <c r="B27" s="118"/>
       <c r="C27" s="50" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D27" s="127" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="128"/>
-      <c r="F27" s="129"/>
+      <c r="D27" s="108" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="109"/>
+      <c r="F27" s="110"/>
       <c r="G27" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="48" t="s">
@@ -4290,21 +4517,18 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="88" t="str">
-        <f>master!B16</f>
-        <v>まとめ</v>
-      </c>
+      <c r="B28" s="119"/>
       <c r="C28" s="50" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D28" s="127" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" s="128"/>
-      <c r="F28" s="129"/>
+      <c r="D28" s="108" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="109"/>
+      <c r="F28" s="110"/>
       <c r="G28" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="48" t="s">
@@ -4318,23 +4542,23 @@
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="25.2">
+    <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="121" t="str">
+      <c r="B29" s="117" t="str">
         <f>master!B18</f>
-        <v>提案書サンプル</v>
+        <v>提案書のサンプルについて</v>
       </c>
       <c r="C29" s="50" t="str">
         <f>master!C18</f>
-        <v>１．サマリ</v>
-      </c>
-      <c r="D29" s="127" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" s="128"/>
-      <c r="F29" s="129"/>
+        <v>はじめに</v>
+      </c>
+      <c r="D29" s="108" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="109"/>
+      <c r="F29" s="110"/>
       <c r="G29" s="50" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="48" t="s">
@@ -4350,25 +4574,25 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="122"/>
+      <c r="B30" s="118"/>
       <c r="C30" s="50" t="str">
         <f>master!C19</f>
-        <v>２．背景</v>
-      </c>
-      <c r="D30" s="127" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" s="128"/>
-      <c r="F30" s="129"/>
+        <v>１．サマリ</v>
+      </c>
+      <c r="D30" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="109"/>
+      <c r="F30" s="110"/>
       <c r="G30" s="50" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="48" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="46">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K30" s="43"/>
       <c r="L30" s="6"/>
@@ -4377,18 +4601,18 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="122"/>
+      <c r="B31" s="118"/>
       <c r="C31" s="50" t="str">
         <f>master!C20</f>
-        <v>３．現状課題</v>
-      </c>
-      <c r="D31" s="127" t="s">
-        <v>147</v>
-      </c>
-      <c r="E31" s="128"/>
-      <c r="F31" s="129"/>
+        <v>２．背景</v>
+      </c>
+      <c r="D31" s="108" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="109"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="50" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="48" t="s">
@@ -4402,20 +4626,20 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="63">
+    <row r="32" spans="1:14" ht="25.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="122"/>
+      <c r="B32" s="118"/>
       <c r="C32" s="50" t="str">
         <f>master!C21</f>
-        <v>４．業界動向・市場分析</v>
-      </c>
-      <c r="D32" s="127" t="s">
-        <v>158</v>
-      </c>
-      <c r="E32" s="128"/>
-      <c r="F32" s="129"/>
+        <v>３．現状課題</v>
+      </c>
+      <c r="D32" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="109"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="50" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="48" t="s">
@@ -4429,20 +4653,20 @@
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="50.4">
+    <row r="33" spans="1:14" ht="63">
       <c r="A33" s="11"/>
-      <c r="B33" s="122"/>
+      <c r="B33" s="118"/>
       <c r="C33" s="50" t="str">
         <f>master!C22</f>
-        <v>５．市場機会</v>
-      </c>
-      <c r="D33" s="127" t="s">
-        <v>161</v>
-      </c>
-      <c r="E33" s="128"/>
-      <c r="F33" s="129"/>
+        <v>４．業界動向・市場分析</v>
+      </c>
+      <c r="D33" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="109"/>
+      <c r="F33" s="110"/>
       <c r="G33" s="50" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="48" t="s">
@@ -4458,18 +4682,18 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="122"/>
+      <c r="B34" s="118"/>
       <c r="C34" s="50" t="str">
         <f>master!C23</f>
-        <v>６．サービス概要</v>
-      </c>
-      <c r="D34" s="127" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="128"/>
-      <c r="F34" s="129"/>
+        <v>５．市場機会</v>
+      </c>
+      <c r="D34" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="109"/>
+      <c r="F34" s="110"/>
       <c r="G34" s="50" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="48" t="s">
@@ -4483,20 +4707,20 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="50.4">
+    <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="122"/>
+      <c r="B35" s="118"/>
       <c r="C35" s="50" t="str">
         <f>master!C24</f>
-        <v>７．利用者体験イメージ</v>
-      </c>
-      <c r="D35" s="127" t="s">
-        <v>157</v>
-      </c>
-      <c r="E35" s="128"/>
-      <c r="F35" s="129"/>
+        <v>６．サービス概要</v>
+      </c>
+      <c r="D35" s="108" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="109"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="50" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="48" t="s">
@@ -4510,20 +4734,20 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="25.2">
+    <row r="36" spans="1:14" ht="63">
       <c r="A36" s="11"/>
-      <c r="B36" s="122"/>
+      <c r="B36" s="118"/>
       <c r="C36" s="50" t="str">
         <f>master!C25</f>
-        <v>８．事業構成</v>
-      </c>
-      <c r="D36" s="127" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="128"/>
-      <c r="F36" s="129"/>
+        <v>７．利用者体験イメージ</v>
+      </c>
+      <c r="D36" s="108" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" s="109"/>
+      <c r="F36" s="110"/>
       <c r="G36" s="50" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="48" t="s">
@@ -4537,20 +4761,20 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="37.799999999999997">
+    <row r="37" spans="1:14" ht="25.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="122"/>
+      <c r="B37" s="118"/>
       <c r="C37" s="50" t="str">
         <f>master!C26</f>
-        <v>９．提供価値</v>
-      </c>
-      <c r="D37" s="127" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" s="128"/>
-      <c r="F37" s="129"/>
+        <v>８．事業構成</v>
+      </c>
+      <c r="D37" s="108" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="109"/>
+      <c r="F37" s="110"/>
       <c r="G37" s="50" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="48" t="s">
@@ -4564,20 +4788,20 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="63">
+    <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="122"/>
+      <c r="B38" s="118"/>
       <c r="C38" s="50" t="str">
         <f>master!C27</f>
-        <v>１０．収益モデル</v>
-      </c>
-      <c r="D38" s="127" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="128"/>
-      <c r="F38" s="129"/>
+        <v>９．提供価値</v>
+      </c>
+      <c r="D38" s="108" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="109"/>
+      <c r="F38" s="110"/>
       <c r="G38" s="50" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="48" t="s">
@@ -4593,18 +4817,18 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="122"/>
+      <c r="B39" s="118"/>
       <c r="C39" s="50" t="str">
         <f>master!C28</f>
-        <v>１１．リスク・課題</v>
-      </c>
-      <c r="D39" s="127" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" s="128"/>
-      <c r="F39" s="129"/>
+        <v>１０．収益モデル</v>
+      </c>
+      <c r="D39" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" s="109"/>
+      <c r="F39" s="110"/>
       <c r="G39" s="50" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="48" t="s">
@@ -4618,587 +4842,603 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="25.2">
+    <row r="40" spans="1:14" ht="63">
       <c r="A40" s="11"/>
-      <c r="B40" s="123"/>
+      <c r="B40" s="118"/>
       <c r="C40" s="50" t="str">
         <f>master!C29</f>
-        <v>１２．今後の展望</v>
-      </c>
-      <c r="D40" s="127" t="s">
-        <v>160</v>
-      </c>
-      <c r="E40" s="128"/>
-      <c r="F40" s="129"/>
+        <v>１１．リスク・課題</v>
+      </c>
+      <c r="D40" s="108" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="109"/>
+      <c r="F40" s="110"/>
       <c r="G40" s="50" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="48" t="s">
         <v>24</v>
       </c>
       <c r="J40" s="46">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="113.4">
+    <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="118" t="str">
-        <f>master!B31</f>
-        <v>個人演習</v>
-      </c>
-      <c r="C41" s="70" t="str">
-        <f>master!C31</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D41" s="112" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" s="113"/>
-      <c r="F41" s="114"/>
-      <c r="G41" s="70" t="s">
-        <v>104</v>
-      </c>
-      <c r="H41" s="71"/>
-      <c r="I41" s="72" t="s">
+      <c r="B41" s="119"/>
+      <c r="C41" s="50" t="str">
+        <f>master!C30</f>
+        <v>１２．今後の展望</v>
+      </c>
+      <c r="D41" s="108" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="109"/>
+      <c r="F41" s="110"/>
+      <c r="G41" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="H41" s="12"/>
+      <c r="I41" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="73">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K41" s="74"/>
+      <c r="J41" s="46">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K41" s="43"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="201.6">
+    <row r="42" spans="1:14" ht="113.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="119"/>
-      <c r="C42" s="70" t="str">
+      <c r="B42" s="126" t="str">
+        <f>master!B32</f>
+        <v>個人演習</v>
+      </c>
+      <c r="C42" s="69" t="str">
         <f>master!C32</f>
-        <v>演習成果物の説明</v>
-      </c>
-      <c r="D42" s="112" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="113"/>
-      <c r="F42" s="114"/>
-      <c r="G42" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="H42" s="71"/>
-      <c r="I42" s="72" t="s">
+        <v>演習内容の説明</v>
+      </c>
+      <c r="D42" s="111" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42" s="112"/>
+      <c r="F42" s="113"/>
+      <c r="G42" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="H42" s="70"/>
+      <c r="I42" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="73">
+      <c r="J42" s="72">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K42" s="74"/>
+      <c r="K42" s="73"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="176.4">
+    <row r="43" spans="1:14" ht="201.6">
       <c r="A43" s="11"/>
-      <c r="B43" s="119"/>
-      <c r="C43" s="70" t="str">
+      <c r="B43" s="127"/>
+      <c r="C43" s="69" t="str">
         <f>master!C33</f>
-        <v>サービスの検討</v>
-      </c>
-      <c r="D43" s="112" t="s">
-        <v>115</v>
-      </c>
-      <c r="E43" s="113"/>
-      <c r="F43" s="114"/>
-      <c r="G43" s="70" t="s">
-        <v>108</v>
-      </c>
-      <c r="H43" s="71"/>
-      <c r="I43" s="72" t="s">
+        <v>演習成果物の説明</v>
+      </c>
+      <c r="D43" s="111" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="112"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H43" s="70"/>
+      <c r="I43" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="73">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K43" s="74"/>
+      <c r="J43" s="72">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K43" s="73"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="138.6">
+    <row r="44" spans="1:14" ht="176.4">
       <c r="A44" s="11"/>
-      <c r="B44" s="119"/>
-      <c r="C44" s="70" t="str">
+      <c r="B44" s="127"/>
+      <c r="C44" s="69" t="str">
         <f>master!C34</f>
-        <v>サービスのブラッシュアップ</v>
-      </c>
-      <c r="D44" s="112" t="s">
-        <v>114</v>
-      </c>
-      <c r="E44" s="113"/>
-      <c r="F44" s="114"/>
-      <c r="G44" s="70" t="s">
-        <v>110</v>
-      </c>
-      <c r="H44" s="71"/>
-      <c r="I44" s="72" t="s">
+        <v>サービスの検討</v>
+      </c>
+      <c r="D44" s="111" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" s="112"/>
+      <c r="F44" s="113"/>
+      <c r="G44" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="H44" s="70"/>
+      <c r="I44" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="73">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K44" s="74"/>
+      <c r="J44" s="72">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K44" s="73"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="63">
+    <row r="45" spans="1:14" ht="138.6">
       <c r="A45" s="11"/>
-      <c r="B45" s="119"/>
-      <c r="C45" s="70" t="str">
+      <c r="B45" s="127"/>
+      <c r="C45" s="69" t="str">
         <f>master!C35</f>
-        <v>サービスの決定</v>
-      </c>
-      <c r="D45" s="112" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" s="113"/>
-      <c r="F45" s="114"/>
-      <c r="G45" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45" s="71"/>
-      <c r="I45" s="72" t="s">
+        <v>サービスのブラッシュアップ</v>
+      </c>
+      <c r="D45" s="111" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45" s="112"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="H45" s="70"/>
+      <c r="I45" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="73">
+      <c r="J45" s="72">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K45" s="74"/>
+      <c r="K45" s="73"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="138.6">
+    <row r="46" spans="1:14" ht="63">
       <c r="A46" s="11"/>
-      <c r="B46" s="119"/>
-      <c r="C46" s="70" t="str">
+      <c r="B46" s="127"/>
+      <c r="C46" s="69" t="str">
         <f>master!C36</f>
-        <v>成果物の作成</v>
-      </c>
-      <c r="D46" s="112" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="113"/>
-      <c r="F46" s="114"/>
-      <c r="G46" s="70" t="s">
-        <v>110</v>
-      </c>
-      <c r="H46" s="71"/>
-      <c r="I46" s="72" t="s">
+        <v>サービスの決定</v>
+      </c>
+      <c r="D46" s="111" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" s="112"/>
+      <c r="F46" s="113"/>
+      <c r="G46" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="H46" s="70"/>
+      <c r="I46" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="K46" s="74"/>
+      <c r="J46" s="72">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K46" s="73"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="25.2">
+    <row r="47" spans="1:14" ht="138.6">
       <c r="A47" s="11"/>
-      <c r="B47" s="120"/>
-      <c r="C47" s="70" t="str">
+      <c r="B47" s="127"/>
+      <c r="C47" s="69" t="str">
         <f>master!C37</f>
-        <v>成果物の提出</v>
-      </c>
-      <c r="D47" s="112" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="113"/>
-      <c r="F47" s="114"/>
-      <c r="G47" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="H47" s="71"/>
-      <c r="I47" s="72" t="s">
+        <v>成果物の作成</v>
+      </c>
+      <c r="D47" s="111" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47" s="112"/>
+      <c r="F47" s="113"/>
+      <c r="G47" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="H47" s="70"/>
+      <c r="I47" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="K47" s="74"/>
+      <c r="J47" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="K47" s="73"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="100.8">
+    <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="118" t="str">
-        <f>master!B39</f>
-        <v>チーム演習</v>
-      </c>
-      <c r="C48" s="70" t="str">
-        <f>master!C39</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D48" s="112" t="s">
-        <v>122</v>
-      </c>
-      <c r="E48" s="113"/>
-      <c r="F48" s="114"/>
-      <c r="G48" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="H48" s="71"/>
-      <c r="I48" s="72" t="s">
+      <c r="B48" s="128"/>
+      <c r="C48" s="69" t="str">
+        <f>master!C38</f>
+        <v>成果物の提出</v>
+      </c>
+      <c r="D48" s="111" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="112"/>
+      <c r="F48" s="113"/>
+      <c r="G48" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="H48" s="70"/>
+      <c r="I48" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="73">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K48" s="74"/>
+      <c r="J48" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="K48" s="73"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="201.6">
+    <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="119"/>
-      <c r="C49" s="70" t="str">
+      <c r="B49" s="126" t="str">
+        <f>master!B40</f>
+        <v>チーム演習</v>
+      </c>
+      <c r="C49" s="69" t="str">
         <f>master!C40</f>
-        <v>演習成果物の説明</v>
-      </c>
-      <c r="D49" s="112" t="s">
-        <v>117</v>
-      </c>
-      <c r="E49" s="113"/>
-      <c r="F49" s="114"/>
-      <c r="G49" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="H49" s="71"/>
-      <c r="I49" s="72" t="s">
+        <v>演習内容の説明</v>
+      </c>
+      <c r="D49" s="111" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" s="112"/>
+      <c r="F49" s="113"/>
+      <c r="G49" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="70"/>
+      <c r="I49" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="73">
+      <c r="J49" s="72">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K49" s="74"/>
+      <c r="K49" s="73"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="25.2">
+    <row r="50" spans="1:14" ht="201.6">
       <c r="A50" s="11"/>
-      <c r="B50" s="119"/>
-      <c r="C50" s="70" t="str">
+      <c r="B50" s="127"/>
+      <c r="C50" s="69" t="str">
         <f>master!C41</f>
-        <v>【参考】最終発表時の評価基準</v>
-      </c>
-      <c r="D50" s="112" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="113"/>
-      <c r="F50" s="114"/>
-      <c r="G50" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="H50" s="71"/>
-      <c r="I50" s="72" t="s">
+        <v>演習成果物の説明</v>
+      </c>
+      <c r="D50" s="111" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="112"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="70"/>
+      <c r="I50" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="73">
+      <c r="J50" s="72">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K50" s="74"/>
+      <c r="K50" s="73"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="113.4">
+    <row r="51" spans="1:14" ht="37.799999999999997">
       <c r="A51" s="11"/>
-      <c r="B51" s="119"/>
-      <c r="C51" s="70" t="str">
+      <c r="B51" s="127"/>
+      <c r="C51" s="69" t="str">
         <f>master!C42</f>
-        <v>サービスの提案</v>
-      </c>
-      <c r="D51" s="112" t="s">
-        <v>124</v>
-      </c>
-      <c r="E51" s="113"/>
-      <c r="F51" s="114"/>
-      <c r="G51" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="H51" s="71"/>
-      <c r="I51" s="72" t="s">
+        <v>【参考】最終発表時の評価基準</v>
+      </c>
+      <c r="D51" s="111" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="112"/>
+      <c r="F51" s="113"/>
+      <c r="G51" s="69" t="s">
+        <v>154</v>
+      </c>
+      <c r="H51" s="70"/>
+      <c r="I51" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J51" s="73">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="K51" s="74"/>
+      <c r="J51" s="72">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K51" s="73"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="100.8">
+    <row r="52" spans="1:14" ht="113.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="119"/>
-      <c r="C52" s="70" t="str">
+      <c r="B52" s="127"/>
+      <c r="C52" s="69" t="str">
         <f>master!C43</f>
-        <v>サービスの決定（チーム）</v>
-      </c>
-      <c r="D52" s="112" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" s="113"/>
-      <c r="F52" s="114"/>
-      <c r="G52" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="H52" s="71"/>
-      <c r="I52" s="72" t="s">
+        <v>サービスの提案</v>
+      </c>
+      <c r="D52" s="111" t="s">
+        <v>162</v>
+      </c>
+      <c r="E52" s="112"/>
+      <c r="F52" s="113"/>
+      <c r="G52" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="70"/>
+      <c r="I52" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J52" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="K52" s="74"/>
+      <c r="J52" s="72">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="K52" s="73"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="113.4">
+    <row r="53" spans="1:14" ht="100.8">
       <c r="A53" s="11"/>
-      <c r="B53" s="119"/>
-      <c r="C53" s="70" t="str">
+      <c r="B53" s="127"/>
+      <c r="C53" s="69" t="str">
         <f>master!C44</f>
-        <v>成果物の作成</v>
-      </c>
-      <c r="D53" s="112" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="113"/>
-      <c r="F53" s="114"/>
-      <c r="G53" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="H53" s="71"/>
-      <c r="I53" s="72" t="s">
+        <v>サービスの決定（チーム）</v>
+      </c>
+      <c r="D53" s="111" t="s">
+        <v>147</v>
+      </c>
+      <c r="E53" s="112"/>
+      <c r="F53" s="113"/>
+      <c r="G53" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="H53" s="70"/>
+      <c r="I53" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J53" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="K53" s="74"/>
+      <c r="J53" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="K53" s="73"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="25.2">
+    <row r="54" spans="1:14" ht="113.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="119"/>
-      <c r="C54" s="70" t="str">
+      <c r="B54" s="127"/>
+      <c r="C54" s="69" t="str">
         <f>master!C45</f>
-        <v>成果物の提出</v>
-      </c>
-      <c r="D54" s="112" t="s">
-        <v>111</v>
-      </c>
-      <c r="E54" s="113"/>
-      <c r="F54" s="114"/>
-      <c r="G54" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="71"/>
-      <c r="I54" s="72" t="s">
+        <v>成果物の作成</v>
+      </c>
+      <c r="D54" s="111" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="112"/>
+      <c r="F54" s="113"/>
+      <c r="G54" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="H54" s="70"/>
+      <c r="I54" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="K54" s="74"/>
+      <c r="J54" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="K54" s="73"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="120"/>
-      <c r="C55" s="70" t="str">
+      <c r="B55" s="127"/>
+      <c r="C55" s="69" t="str">
         <f>master!C46</f>
-        <v>発表のリハーサル</v>
-      </c>
-      <c r="D55" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" s="113"/>
-      <c r="F55" s="114"/>
-      <c r="G55" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="71"/>
-      <c r="I55" s="72" t="s">
+        <v>成果物の提出</v>
+      </c>
+      <c r="D55" s="111" t="s">
+        <v>103</v>
+      </c>
+      <c r="E55" s="112"/>
+      <c r="F55" s="113"/>
+      <c r="G55" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="H55" s="70"/>
+      <c r="I55" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J55" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="K55" s="74"/>
+      <c r="J55" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="K55" s="73"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="100.8">
+    <row r="56" spans="1:14" ht="25.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="115" t="str">
-        <f>master!B48</f>
-        <v>発表会（ブロック代表の決定）</v>
-      </c>
-      <c r="C56" s="77" t="str">
-        <f>master!C48</f>
-        <v>ブロック内発表の説明</v>
-      </c>
-      <c r="D56" s="130" t="s">
-        <v>130</v>
-      </c>
-      <c r="E56" s="131"/>
-      <c r="F56" s="132"/>
-      <c r="G56" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="H56" s="78"/>
-      <c r="I56" s="79" t="s">
+      <c r="B56" s="128"/>
+      <c r="C56" s="69" t="str">
+        <f>master!C47</f>
+        <v>提案のリハーサル</v>
+      </c>
+      <c r="D56" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" s="112"/>
+      <c r="F56" s="113"/>
+      <c r="G56" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="70"/>
+      <c r="I56" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="80">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K56" s="81"/>
+      <c r="J56" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="K56" s="73"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="113.4">
+    <row r="57" spans="1:14" ht="100.8">
       <c r="A57" s="11"/>
-      <c r="B57" s="116"/>
-      <c r="C57" s="77" t="str">
+      <c r="B57" s="123" t="str">
+        <f>master!B49</f>
+        <v>提案会（ブロック代表の決定）</v>
+      </c>
+      <c r="C57" s="76" t="str">
         <f>master!C49</f>
-        <v>ブロック内発表の実施</v>
-      </c>
-      <c r="D57" s="130" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" s="131"/>
-      <c r="F57" s="132"/>
-      <c r="G57" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="H57" s="78"/>
-      <c r="I57" s="79" t="s">
+        <v>ブロック内発表の説明</v>
+      </c>
+      <c r="D57" s="114" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" s="115"/>
+      <c r="F57" s="116"/>
+      <c r="G57" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="H57" s="77"/>
+      <c r="I57" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J57" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="K57" s="81"/>
+      <c r="J57" s="79">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K57" s="80"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="25.2">
+    <row r="58" spans="1:14" ht="113.4">
       <c r="A58" s="11"/>
-      <c r="B58" s="117"/>
-      <c r="C58" s="77" t="str">
+      <c r="B58" s="124"/>
+      <c r="C58" s="76" t="str">
         <f>master!C50</f>
-        <v>ブロック代表（選抜チーム）の決定</v>
-      </c>
-      <c r="D58" s="130" t="s">
-        <v>132</v>
-      </c>
-      <c r="E58" s="131"/>
-      <c r="F58" s="132"/>
-      <c r="G58" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="H58" s="78"/>
-      <c r="I58" s="79" t="s">
+        <v>ブロック内発表の実施</v>
+      </c>
+      <c r="D58" s="114" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" s="115"/>
+      <c r="F58" s="116"/>
+      <c r="G58" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="H58" s="77"/>
+      <c r="I58" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J58" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K58" s="81"/>
+      <c r="J58" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="K58" s="80"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="138.6">
+    <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="82" t="str">
-        <f>master!B51</f>
-        <v>発表会（最終）</v>
-      </c>
-      <c r="C59" s="77" t="str">
+      <c r="B59" s="125"/>
+      <c r="C59" s="76" t="str">
         <f>master!C51</f>
-        <v>全体発表</v>
-      </c>
-      <c r="D59" s="130"/>
-      <c r="E59" s="131"/>
-      <c r="F59" s="132"/>
-      <c r="G59" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="H59" s="78"/>
-      <c r="I59" s="79" t="s">
+        <v>ブロック代表（選抜チーム）の決定</v>
+      </c>
+      <c r="D59" s="114" t="s">
+        <v>117</v>
+      </c>
+      <c r="E59" s="115"/>
+      <c r="F59" s="116"/>
+      <c r="G59" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="H59" s="77"/>
+      <c r="I59" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J59" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="K59" s="81"/>
+      <c r="J59" s="79">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K59" s="80"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
+    <row r="60" spans="1:14" ht="113.4">
+      <c r="A60" s="11"/>
+      <c r="B60" s="81" t="str">
+        <f>master!B52</f>
+        <v>提案会（最終）</v>
+      </c>
+      <c r="C60" s="76" t="str">
+        <f>master!C52</f>
+        <v>全体発表</v>
+      </c>
+      <c r="D60" s="114" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" s="115"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="77"/>
+      <c r="I60" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="K60" s="80"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="D16:F16"/>
+  <mergeCells count="59">
+    <mergeCell ref="B17:B28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B29:B41"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
     <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B17:B27"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="B4:E4"/>
@@ -5214,20 +5454,34 @@
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B41:B47"/>
-    <mergeCell ref="B48:B55"/>
-    <mergeCell ref="B29:B40"/>
-    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D56:F56"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5240,7 +5494,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H16:H59</xm:sqref>
+          <xm:sqref>H16:H60</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5250,7 +5504,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C51"/>
+  <dimension ref="B1:C52"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -5260,279 +5514,284 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="66" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" s="74" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" s="74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="C21" s="74" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22" s="74" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="C23" s="74" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="C24" s="74" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="C19" s="75" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="C20" s="75" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="C21" s="75" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="C22" s="75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="C23" s="75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="C24" s="76" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" s="75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="C26" s="74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="C27" s="74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28" s="74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="C29" s="74" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="C30" s="74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="74" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="75" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="C27" s="75" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="C28" s="75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="C29" s="75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="C32" s="75" t="s">
-        <v>105</v>
-      </c>
-    </row>
     <row r="33" spans="2:3">
-      <c r="C33" s="75" t="s">
-        <v>99</v>
+      <c r="C33" s="74" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="C34" s="75" t="s">
-        <v>109</v>
+      <c r="C34" s="74" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="C35" t="s">
-        <v>100</v>
+      <c r="C35" s="74" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="2:3">
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="75" t="s">
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="40" spans="2:3">
-      <c r="C40" s="75" t="s">
-        <v>105</v>
+      <c r="C40" s="74" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="C41" s="75" t="s">
-        <v>83</v>
+      <c r="C41" s="74" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="2:3">
-      <c r="C42" s="75" t="s">
-        <v>121</v>
+      <c r="C42" s="74" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="C43" t="s">
-        <v>120</v>
+      <c r="C43" s="74" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="2:3">
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
+      <c r="C47" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="48" spans="2:3">
-      <c r="B48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="75" t="s">
-        <v>103</v>
-      </c>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
     </row>
     <row r="49" spans="2:3">
-      <c r="C49" s="75" t="s">
-        <v>84</v>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="74" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="2:3">
-      <c r="C50" s="75" t="s">
-        <v>131</v>
+      <c r="C50" s="74" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="2:3">
-      <c r="B51" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="75" t="s">
-        <v>85</v>
+      <c r="C51" s="74" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="74" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/IG/AI Native-提案演習_IG.xlsx
+++ b/IG/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B56974C-E254-42FB-93EB-3D02724950DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E6C45A1-4317-41AB-95B5-32555B341790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,6 +24,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1726,10 +1727,7 @@
       <t>テイアンカイ</t>
     </rPh>
     <rPh sb="4" eb="6">
-      <t>キョウシツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ダイヒョウ</t>
+      <t>キョウシツダイヒョウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2447,6 +2445,9 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2465,6 +2466,9 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2486,6 +2490,15 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2495,6 +2508,15 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2504,6 +2526,15 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2513,15 +2544,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2530,30 +2552,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2937,17 +2935,17 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="95" t="str">
+      <c r="B2" s="96" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案演習_IG」</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
       <c r="J2" s="68"/>
       <c r="K2" s="68"/>
     </row>
@@ -2966,10 +2964,10 @@
     </row>
     <row r="4" spans="1:11" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="97"/>
+      <c r="C4" s="98"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2981,8 +2979,8 @@
     </row>
     <row r="5" spans="1:11" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="100"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -2999,10 +2997,10 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="16.2">
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="100"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -3716,10 +3714,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="103"/>
+      <c r="C4" s="105"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3730,16 +3728,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3752,10 +3750,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="33"/>
-      <c r="D7" s="105" t="s">
+      <c r="D7" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="107"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -3795,46 +3793,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102" t="s">
+      <c r="B11" s="104"/>
+      <c r="C11" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102" t="s">
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="106" t="s">
+      <c r="H11" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="101" t="s">
+      <c r="I11" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101" t="s">
+      <c r="J11" s="103"/>
+      <c r="K11" s="103" t="s">
         <v>31</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="107"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="109"/>
       <c r="I12" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="102"/>
+      <c r="K12" s="104"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -3843,12 +3841,12 @@
       <c r="C13" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="129" t="s">
+      <c r="D13" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="130" t="s">
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="95" t="s">
         <v>42</v>
       </c>
       <c r="H13" s="19"/>
@@ -3867,12 +3865,12 @@
       <c r="C14" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D14" s="129" t="s">
+      <c r="D14" s="102" t="s">
         <v>169</v>
       </c>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="130" t="s">
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="95" t="s">
         <v>170</v>
       </c>
       <c r="H14" s="19"/>
@@ -3971,12 +3969,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3987,30 +3985,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="122"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="130"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30"/>
     </row>
@@ -4137,28 +4135,28 @@
     </row>
     <row r="14" spans="1:14" ht="24" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="102" t="s">
+      <c r="C14" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="102" t="s">
+      <c r="D14" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="102" t="s">
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="101" t="s">
+      <c r="H14" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="120" t="s">
+      <c r="I14" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="121"/>
-      <c r="K14" s="101" t="s">
+      <c r="J14" s="129"/>
+      <c r="K14" s="103" t="s">
         <v>33</v>
       </c>
       <c r="L14" s="6"/>
@@ -4167,20 +4165,20 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="10"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="101"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
       <c r="I15" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="102"/>
+      <c r="K15" s="104"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
@@ -4195,11 +4193,11 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D16" s="108" t="s">
+      <c r="D16" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="109"/>
-      <c r="F16" s="110"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="50" t="s">
         <v>114</v>
       </c>
@@ -4217,7 +4215,7 @@
     </row>
     <row r="17" spans="1:14" ht="63">
       <c r="A17" s="10"/>
-      <c r="B17" s="117" t="str">
+      <c r="B17" s="110" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4225,11 +4223,11 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D17" s="108" t="s">
+      <c r="D17" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="E17" s="109"/>
-      <c r="F17" s="110"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
       <c r="G17" s="50" t="s">
         <v>114</v>
       </c>
@@ -4247,16 +4245,16 @@
     </row>
     <row r="18" spans="1:14" ht="163.80000000000001">
       <c r="A18" s="11"/>
-      <c r="B18" s="118"/>
+      <c r="B18" s="111"/>
       <c r="C18" s="50" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D18" s="108" t="s">
+      <c r="D18" s="113" t="s">
         <v>166</v>
       </c>
-      <c r="E18" s="109"/>
-      <c r="F18" s="110"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="115"/>
       <c r="G18" s="50" t="s">
         <v>165</v>
       </c>
@@ -4274,16 +4272,16 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="118"/>
+      <c r="B19" s="111"/>
       <c r="C19" s="50" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D19" s="108" t="s">
+      <c r="D19" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="109"/>
-      <c r="F19" s="110"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
       <c r="G19" s="50" t="s">
         <v>37</v>
       </c>
@@ -4301,16 +4299,16 @@
     </row>
     <row r="20" spans="1:14" ht="151.19999999999999">
       <c r="A20" s="11"/>
-      <c r="B20" s="118"/>
+      <c r="B20" s="111"/>
       <c r="C20" s="50" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D20" s="108" t="s">
+      <c r="D20" s="113" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="109"/>
-      <c r="F20" s="110"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="50" t="s">
         <v>44</v>
       </c>
@@ -4328,16 +4326,16 @@
     </row>
     <row r="21" spans="1:14" ht="252">
       <c r="A21" s="11"/>
-      <c r="B21" s="118"/>
+      <c r="B21" s="111"/>
       <c r="C21" s="50" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D21" s="108" t="s">
+      <c r="D21" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="109"/>
-      <c r="F21" s="110"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="50" t="s">
         <v>46</v>
       </c>
@@ -4355,16 +4353,16 @@
     </row>
     <row r="22" spans="1:14" ht="126">
       <c r="A22" s="11"/>
-      <c r="B22" s="118"/>
+      <c r="B22" s="111"/>
       <c r="C22" s="50" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D22" s="108" t="s">
+      <c r="D22" s="113" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="109"/>
-      <c r="F22" s="110"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="115"/>
       <c r="G22" s="50" t="s">
         <v>45</v>
       </c>
@@ -4382,16 +4380,16 @@
     </row>
     <row r="23" spans="1:14" ht="63">
       <c r="A23" s="11"/>
-      <c r="B23" s="118"/>
+      <c r="B23" s="111"/>
       <c r="C23" s="50" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D23" s="108" t="s">
+      <c r="D23" s="113" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="109"/>
-      <c r="F23" s="110"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="115"/>
       <c r="G23" s="50" t="s">
         <v>114</v>
       </c>
@@ -4409,16 +4407,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="118"/>
+      <c r="B24" s="111"/>
       <c r="C24" s="50" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D24" s="108" t="s">
+      <c r="D24" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="109"/>
-      <c r="F24" s="110"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="50" t="s">
         <v>38</v>
       </c>
@@ -4436,16 +4434,16 @@
     </row>
     <row r="25" spans="1:14" ht="75.599999999999994">
       <c r="A25" s="11"/>
-      <c r="B25" s="118"/>
+      <c r="B25" s="111"/>
       <c r="C25" s="50" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D25" s="108" t="s">
+      <c r="D25" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="109"/>
-      <c r="F25" s="110"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="115"/>
       <c r="G25" s="50" t="s">
         <v>38</v>
       </c>
@@ -4463,16 +4461,16 @@
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="118"/>
+      <c r="B26" s="111"/>
       <c r="C26" s="50" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D26" s="108" t="s">
+      <c r="D26" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="109"/>
-      <c r="F26" s="110"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="115"/>
       <c r="G26" s="50" t="s">
         <v>39</v>
       </c>
@@ -4490,16 +4488,16 @@
     </row>
     <row r="27" spans="1:14" ht="88.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="118"/>
+      <c r="B27" s="111"/>
       <c r="C27" s="50" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D27" s="108" t="s">
+      <c r="D27" s="113" t="s">
         <v>128</v>
       </c>
-      <c r="E27" s="109"/>
-      <c r="F27" s="110"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="115"/>
       <c r="G27" s="50" t="s">
         <v>40</v>
       </c>
@@ -4517,16 +4515,16 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="119"/>
+      <c r="B28" s="112"/>
       <c r="C28" s="50" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D28" s="108" t="s">
+      <c r="D28" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="109"/>
-      <c r="F28" s="110"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="50" t="s">
         <v>39</v>
       </c>
@@ -4544,7 +4542,7 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="117" t="str">
+      <c r="B29" s="110" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
@@ -4552,11 +4550,11 @@
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D29" s="108" t="s">
+      <c r="D29" s="113" t="s">
         <v>151</v>
       </c>
-      <c r="E29" s="109"/>
-      <c r="F29" s="110"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="115"/>
       <c r="G29" s="50" t="s">
         <v>132</v>
       </c>
@@ -4574,16 +4572,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="118"/>
+      <c r="B30" s="111"/>
       <c r="C30" s="50" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D30" s="108" t="s">
+      <c r="D30" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="109"/>
-      <c r="F30" s="110"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="115"/>
       <c r="G30" s="50" t="s">
         <v>90</v>
       </c>
@@ -4601,16 +4599,16 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="118"/>
+      <c r="B31" s="111"/>
       <c r="C31" s="50" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D31" s="108" t="s">
+      <c r="D31" s="113" t="s">
         <v>148</v>
       </c>
-      <c r="E31" s="109"/>
-      <c r="F31" s="110"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="115"/>
       <c r="G31" s="50" t="s">
         <v>90</v>
       </c>
@@ -4628,16 +4626,16 @@
     </row>
     <row r="32" spans="1:14" ht="25.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="118"/>
+      <c r="B32" s="111"/>
       <c r="C32" s="50" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D32" s="108" t="s">
+      <c r="D32" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="109"/>
-      <c r="F32" s="110"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="50" t="s">
         <v>90</v>
       </c>
@@ -4655,16 +4653,16 @@
     </row>
     <row r="33" spans="1:14" ht="63">
       <c r="A33" s="11"/>
-      <c r="B33" s="118"/>
+      <c r="B33" s="111"/>
       <c r="C33" s="50" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D33" s="108" t="s">
+      <c r="D33" s="113" t="s">
         <v>135</v>
       </c>
-      <c r="E33" s="109"/>
-      <c r="F33" s="110"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="115"/>
       <c r="G33" s="50" t="s">
         <v>133</v>
       </c>
@@ -4682,16 +4680,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="118"/>
+      <c r="B34" s="111"/>
       <c r="C34" s="50" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D34" s="108" t="s">
+      <c r="D34" s="113" t="s">
         <v>138</v>
       </c>
-      <c r="E34" s="109"/>
-      <c r="F34" s="110"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
       <c r="G34" s="50" t="s">
         <v>132</v>
       </c>
@@ -4709,16 +4707,16 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="118"/>
+      <c r="B35" s="111"/>
       <c r="C35" s="50" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D35" s="108" t="s">
+      <c r="D35" s="113" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="109"/>
-      <c r="F35" s="110"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="115"/>
       <c r="G35" s="50" t="s">
         <v>132</v>
       </c>
@@ -4736,16 +4734,16 @@
     </row>
     <row r="36" spans="1:14" ht="63">
       <c r="A36" s="11"/>
-      <c r="B36" s="118"/>
+      <c r="B36" s="111"/>
       <c r="C36" s="50" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D36" s="108" t="s">
+      <c r="D36" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="E36" s="109"/>
-      <c r="F36" s="110"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="50" t="s">
         <v>133</v>
       </c>
@@ -4763,16 +4761,16 @@
     </row>
     <row r="37" spans="1:14" ht="25.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="118"/>
+      <c r="B37" s="111"/>
       <c r="C37" s="50" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D37" s="108" t="s">
+      <c r="D37" s="113" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="109"/>
-      <c r="F37" s="110"/>
+      <c r="E37" s="114"/>
+      <c r="F37" s="115"/>
       <c r="G37" s="50" t="s">
         <v>90</v>
       </c>
@@ -4790,16 +4788,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="118"/>
+      <c r="B38" s="111"/>
       <c r="C38" s="50" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D38" s="108" t="s">
+      <c r="D38" s="113" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="109"/>
-      <c r="F38" s="110"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="115"/>
       <c r="G38" s="50" t="s">
         <v>132</v>
       </c>
@@ -4817,16 +4815,16 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="118"/>
+      <c r="B39" s="111"/>
       <c r="C39" s="50" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D39" s="108" t="s">
+      <c r="D39" s="113" t="s">
         <v>134</v>
       </c>
-      <c r="E39" s="109"/>
-      <c r="F39" s="110"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="115"/>
       <c r="G39" s="50" t="s">
         <v>133</v>
       </c>
@@ -4844,16 +4842,16 @@
     </row>
     <row r="40" spans="1:14" ht="63">
       <c r="A40" s="11"/>
-      <c r="B40" s="118"/>
+      <c r="B40" s="111"/>
       <c r="C40" s="50" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D40" s="108" t="s">
+      <c r="D40" s="113" t="s">
         <v>142</v>
       </c>
-      <c r="E40" s="109"/>
-      <c r="F40" s="110"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="50" t="s">
         <v>133</v>
       </c>
@@ -4871,16 +4869,16 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="119"/>
+      <c r="B41" s="112"/>
       <c r="C41" s="50" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D41" s="108" t="s">
+      <c r="D41" s="113" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="109"/>
-      <c r="F41" s="110"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="115"/>
       <c r="G41" s="50" t="s">
         <v>132</v>
       </c>
@@ -4898,7 +4896,7 @@
     </row>
     <row r="42" spans="1:14" ht="113.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="126" t="str">
+      <c r="B42" s="122" t="str">
         <f>master!B32</f>
         <v>個人演習</v>
       </c>
@@ -4906,11 +4904,11 @@
         <f>master!C32</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D42" s="111" t="s">
+      <c r="D42" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="E42" s="112"/>
-      <c r="F42" s="113"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="121"/>
       <c r="G42" s="69" t="s">
         <v>96</v>
       </c>
@@ -4928,16 +4926,16 @@
     </row>
     <row r="43" spans="1:14" ht="201.6">
       <c r="A43" s="11"/>
-      <c r="B43" s="127"/>
+      <c r="B43" s="123"/>
       <c r="C43" s="69" t="str">
         <f>master!C33</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D43" s="111" t="s">
+      <c r="D43" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="112"/>
-      <c r="F43" s="113"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="121"/>
       <c r="G43" s="69" t="s">
         <v>98</v>
       </c>
@@ -4955,16 +4953,16 @@
     </row>
     <row r="44" spans="1:14" ht="176.4">
       <c r="A44" s="11"/>
-      <c r="B44" s="127"/>
+      <c r="B44" s="123"/>
       <c r="C44" s="69" t="str">
         <f>master!C34</f>
         <v>サービスの検討</v>
       </c>
-      <c r="D44" s="111" t="s">
+      <c r="D44" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="E44" s="112"/>
-      <c r="F44" s="113"/>
+      <c r="E44" s="120"/>
+      <c r="F44" s="121"/>
       <c r="G44" s="69" t="s">
         <v>100</v>
       </c>
@@ -4982,16 +4980,16 @@
     </row>
     <row r="45" spans="1:14" ht="138.6">
       <c r="A45" s="11"/>
-      <c r="B45" s="127"/>
+      <c r="B45" s="123"/>
       <c r="C45" s="69" t="str">
         <f>master!C35</f>
         <v>サービスのブラッシュアップ</v>
       </c>
-      <c r="D45" s="111" t="s">
+      <c r="D45" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="E45" s="112"/>
-      <c r="F45" s="113"/>
+      <c r="E45" s="120"/>
+      <c r="F45" s="121"/>
       <c r="G45" s="69" t="s">
         <v>102</v>
       </c>
@@ -5009,16 +5007,16 @@
     </row>
     <row r="46" spans="1:14" ht="63">
       <c r="A46" s="11"/>
-      <c r="B46" s="127"/>
+      <c r="B46" s="123"/>
       <c r="C46" s="69" t="str">
         <f>master!C36</f>
         <v>サービスの決定</v>
       </c>
-      <c r="D46" s="111" t="s">
+      <c r="D46" s="119" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="112"/>
-      <c r="F46" s="113"/>
+      <c r="E46" s="120"/>
+      <c r="F46" s="121"/>
       <c r="G46" s="69" t="s">
         <v>99</v>
       </c>
@@ -5036,16 +5034,16 @@
     </row>
     <row r="47" spans="1:14" ht="138.6">
       <c r="A47" s="11"/>
-      <c r="B47" s="127"/>
+      <c r="B47" s="123"/>
       <c r="C47" s="69" t="str">
         <f>master!C37</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D47" s="111" t="s">
+      <c r="D47" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="E47" s="112"/>
-      <c r="F47" s="113"/>
+      <c r="E47" s="120"/>
+      <c r="F47" s="121"/>
       <c r="G47" s="69" t="s">
         <v>102</v>
       </c>
@@ -5063,16 +5061,16 @@
     </row>
     <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="128"/>
+      <c r="B48" s="124"/>
       <c r="C48" s="69" t="str">
         <f>master!C38</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D48" s="111" t="s">
+      <c r="D48" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="112"/>
-      <c r="F48" s="113"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="121"/>
       <c r="G48" s="69" t="s">
         <v>108</v>
       </c>
@@ -5090,7 +5088,7 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="126" t="str">
+      <c r="B49" s="122" t="str">
         <f>master!B40</f>
         <v>チーム演習</v>
       </c>
@@ -5098,11 +5096,11 @@
         <f>master!C40</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D49" s="111" t="s">
+      <c r="D49" s="119" t="s">
         <v>111</v>
       </c>
-      <c r="E49" s="112"/>
-      <c r="F49" s="113"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="121"/>
       <c r="G49" s="69" t="s">
         <v>152</v>
       </c>
@@ -5120,16 +5118,16 @@
     </row>
     <row r="50" spans="1:14" ht="201.6">
       <c r="A50" s="11"/>
-      <c r="B50" s="127"/>
+      <c r="B50" s="123"/>
       <c r="C50" s="69" t="str">
         <f>master!C41</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D50" s="111" t="s">
+      <c r="D50" s="119" t="s">
         <v>145</v>
       </c>
-      <c r="E50" s="112"/>
-      <c r="F50" s="113"/>
+      <c r="E50" s="120"/>
+      <c r="F50" s="121"/>
       <c r="G50" s="69" t="s">
         <v>153</v>
       </c>
@@ -5147,16 +5145,16 @@
     </row>
     <row r="51" spans="1:14" ht="37.799999999999997">
       <c r="A51" s="11"/>
-      <c r="B51" s="127"/>
+      <c r="B51" s="123"/>
       <c r="C51" s="69" t="str">
         <f>master!C42</f>
         <v>【参考】最終発表時の評価基準</v>
       </c>
-      <c r="D51" s="111" t="s">
+      <c r="D51" s="119" t="s">
         <v>146</v>
       </c>
-      <c r="E51" s="112"/>
-      <c r="F51" s="113"/>
+      <c r="E51" s="120"/>
+      <c r="F51" s="121"/>
       <c r="G51" s="69" t="s">
         <v>154</v>
       </c>
@@ -5174,16 +5172,16 @@
     </row>
     <row r="52" spans="1:14" ht="113.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="127"/>
+      <c r="B52" s="123"/>
       <c r="C52" s="69" t="str">
         <f>master!C43</f>
         <v>サービスの提案</v>
       </c>
-      <c r="D52" s="111" t="s">
+      <c r="D52" s="119" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="112"/>
-      <c r="F52" s="113"/>
+      <c r="E52" s="120"/>
+      <c r="F52" s="121"/>
       <c r="G52" s="69" t="s">
         <v>155</v>
       </c>
@@ -5201,16 +5199,16 @@
     </row>
     <row r="53" spans="1:14" ht="100.8">
       <c r="A53" s="11"/>
-      <c r="B53" s="127"/>
+      <c r="B53" s="123"/>
       <c r="C53" s="69" t="str">
         <f>master!C44</f>
         <v>サービスの決定（チーム）</v>
       </c>
-      <c r="D53" s="111" t="s">
+      <c r="D53" s="119" t="s">
         <v>147</v>
       </c>
-      <c r="E53" s="112"/>
-      <c r="F53" s="113"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="121"/>
       <c r="G53" s="69" t="s">
         <v>152</v>
       </c>
@@ -5228,16 +5226,16 @@
     </row>
     <row r="54" spans="1:14" ht="113.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="127"/>
+      <c r="B54" s="123"/>
       <c r="C54" s="69" t="str">
         <f>master!C45</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D54" s="111" t="s">
+      <c r="D54" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="E54" s="112"/>
-      <c r="F54" s="113"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="121"/>
       <c r="G54" s="69" t="s">
         <v>155</v>
       </c>
@@ -5255,16 +5253,16 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="127"/>
+      <c r="B55" s="123"/>
       <c r="C55" s="69" t="str">
         <f>master!C46</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D55" s="111" t="s">
+      <c r="D55" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="E55" s="112"/>
-      <c r="F55" s="113"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="121"/>
       <c r="G55" s="69" t="s">
         <v>156</v>
       </c>
@@ -5282,16 +5280,16 @@
     </row>
     <row r="56" spans="1:14" ht="25.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="128"/>
+      <c r="B56" s="124"/>
       <c r="C56" s="69" t="str">
         <f>master!C47</f>
         <v>提案のリハーサル</v>
       </c>
-      <c r="D56" s="111" t="s">
+      <c r="D56" s="119" t="s">
         <v>160</v>
       </c>
-      <c r="E56" s="112"/>
-      <c r="F56" s="113"/>
+      <c r="E56" s="120"/>
+      <c r="F56" s="121"/>
       <c r="G56" s="69" t="s">
         <v>156</v>
       </c>
@@ -5309,7 +5307,7 @@
     </row>
     <row r="57" spans="1:14" ht="100.8">
       <c r="A57" s="11"/>
-      <c r="B57" s="123" t="str">
+      <c r="B57" s="116" t="str">
         <f>master!B49</f>
         <v>提案会（ブロック代表の決定）</v>
       </c>
@@ -5317,11 +5315,11 @@
         <f>master!C49</f>
         <v>ブロック内発表の説明</v>
       </c>
-      <c r="D57" s="114" t="s">
+      <c r="D57" s="125" t="s">
         <v>115</v>
       </c>
-      <c r="E57" s="115"/>
-      <c r="F57" s="116"/>
+      <c r="E57" s="126"/>
+      <c r="F57" s="127"/>
       <c r="G57" s="76" t="s">
         <v>157</v>
       </c>
@@ -5339,16 +5337,16 @@
     </row>
     <row r="58" spans="1:14" ht="113.4">
       <c r="A58" s="11"/>
-      <c r="B58" s="124"/>
+      <c r="B58" s="117"/>
       <c r="C58" s="76" t="str">
         <f>master!C50</f>
         <v>ブロック内発表の実施</v>
       </c>
-      <c r="D58" s="114" t="s">
+      <c r="D58" s="125" t="s">
         <v>163</v>
       </c>
-      <c r="E58" s="115"/>
-      <c r="F58" s="116"/>
+      <c r="E58" s="126"/>
+      <c r="F58" s="127"/>
       <c r="G58" s="76" t="s">
         <v>158</v>
       </c>
@@ -5366,16 +5364,16 @@
     </row>
     <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="125"/>
+      <c r="B59" s="118"/>
       <c r="C59" s="76" t="str">
         <f>master!C51</f>
         <v>ブロック代表（選抜チーム）の決定</v>
       </c>
-      <c r="D59" s="114" t="s">
+      <c r="D59" s="125" t="s">
         <v>117</v>
       </c>
-      <c r="E59" s="115"/>
-      <c r="F59" s="116"/>
+      <c r="E59" s="126"/>
+      <c r="F59" s="127"/>
       <c r="G59" s="76" t="s">
         <v>159</v>
       </c>
@@ -5401,11 +5399,11 @@
         <f>master!C52</f>
         <v>全体発表</v>
       </c>
-      <c r="D60" s="114" t="s">
+      <c r="D60" s="125" t="s">
         <v>164</v>
       </c>
-      <c r="E60" s="115"/>
-      <c r="F60" s="116"/>
+      <c r="E60" s="126"/>
+      <c r="F60" s="127"/>
       <c r="G60" s="76" t="s">
         <v>158</v>
       </c>
@@ -5423,6 +5421,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="K14:K15"/>
     <mergeCell ref="B17:B28"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="B29:B41"/>
@@ -5439,49 +5480,6 @@
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="D44:F44"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D56:F56"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/IG/AI Native-提案演習_IG.xlsx
+++ b/IG/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E6C45A1-4317-41AB-95B5-32555B341790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17DF8D2-36DA-4BEC-89AE-D357B4F7CB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -34,7 +33,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{9C44B6D1-EFF1-4F80-B895-9B2F45D9F0E8}">
       <text>
         <r>
           <rPr>
@@ -64,7 +63,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{938B8858-7680-4470-B4E9-3F8DB4920554}">
       <text>
         <r>
           <rPr>
@@ -89,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="172">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -307,19 +306,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>研修ファイルサーバの保存先</t>
-    <rPh sb="0" eb="2">
-      <t>ケンシュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>実施上のの注意点</t>
@@ -2159,7 +2145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2490,6 +2476,42 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2499,15 +2521,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
@@ -2517,15 +2530,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2535,23 +2539,11 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3023,19 +3015,19 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9" s="24"/>
       <c r="I9" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" s="24"/>
       <c r="K9" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.25" customHeight="1">
@@ -3624,31 +3616,31 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C43" s="86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D43" s="85">
         <v>0.73958333333333337</v>
       </c>
       <c r="E43" s="86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F43" s="85">
         <v>0.73958333333333337</v>
       </c>
       <c r="G43" s="86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H43" s="85">
         <v>0.73958333333333337</v>
       </c>
       <c r="I43" s="86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J43" s="85">
         <v>0.73958333333333337</v>
       </c>
       <c r="K43" s="86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L43" s="52"/>
     </row>
@@ -3749,7 +3741,9 @@
       <c r="B7" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="33"/>
+      <c r="C7" s="33" t="s">
+        <v>15</v>
+      </c>
       <c r="D7" s="107" t="s">
         <v>20</v>
       </c>
@@ -3768,7 +3762,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>19</v>
@@ -3809,11 +3803,11 @@
         <v>23</v>
       </c>
       <c r="I11" s="103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J11" s="103"/>
       <c r="K11" s="103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -3839,15 +3833,15 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D13" s="102" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="102"/>
       <c r="F13" s="102"/>
       <c r="G13" s="95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="49" t="s">
@@ -3863,15 +3857,15 @@
       <c r="A14" s="10"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D14" s="102" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E14" s="102"/>
       <c r="F14" s="102"/>
       <c r="G14" s="95" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="49" t="s">
@@ -3985,30 +3979,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30"/>
     </row>
@@ -4028,10 +4022,10 @@
       <c r="C8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="33"/>
+      <c r="D8" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="107"/>
       <c r="F8" s="33" t="s">
         <v>10</v>
       </c>
@@ -4047,15 +4041,15 @@
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="36"/>
+      <c r="E9" s="132"/>
       <c r="F9" s="36" t="s">
         <v>21</v>
       </c>
@@ -4069,15 +4063,15 @@
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="36"/>
+      <c r="E10" s="132"/>
       <c r="F10" s="36" t="s">
         <v>21</v>
       </c>
@@ -4091,15 +4085,15 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="132"/>
       <c r="F11" s="36" t="s">
         <v>21</v>
       </c>
@@ -4113,15 +4107,15 @@
     </row>
     <row r="12" spans="1:14">
       <c r="B12" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="36"/>
+      <c r="E12" s="132"/>
       <c r="F12" s="36" t="s">
         <v>21</v>
       </c>
@@ -4152,12 +4146,12 @@
       <c r="H14" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="128" t="s">
+      <c r="I14" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="120"/>
+      <c r="K14" s="103" t="s">
         <v>32</v>
-      </c>
-      <c r="J14" s="129"/>
-      <c r="K14" s="103" t="s">
-        <v>33</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -4193,13 +4187,13 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D16" s="113" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="114"/>
-      <c r="F16" s="115"/>
+      <c r="D16" s="110" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="111"/>
+      <c r="F16" s="112"/>
       <c r="G16" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="48" t="s">
@@ -4215,7 +4209,7 @@
     </row>
     <row r="17" spans="1:14" ht="63">
       <c r="A17" s="10"/>
-      <c r="B17" s="110" t="str">
+      <c r="B17" s="122" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4223,13 +4217,13 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D17" s="113" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="114"/>
-      <c r="F17" s="115"/>
+      <c r="D17" s="110" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="111"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="48" t="s">
@@ -4245,18 +4239,18 @@
     </row>
     <row r="18" spans="1:14" ht="163.80000000000001">
       <c r="A18" s="11"/>
-      <c r="B18" s="111"/>
+      <c r="B18" s="123"/>
       <c r="C18" s="50" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D18" s="113" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="114"/>
-      <c r="F18" s="115"/>
+      <c r="D18" s="110" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="111"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="48" t="s">
@@ -4272,18 +4266,18 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="111"/>
+      <c r="B19" s="123"/>
       <c r="C19" s="50" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D19" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="114"/>
-      <c r="F19" s="115"/>
+      <c r="D19" s="110" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="111"/>
+      <c r="F19" s="112"/>
       <c r="G19" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="48" t="s">
@@ -4299,18 +4293,18 @@
     </row>
     <row r="20" spans="1:14" ht="151.19999999999999">
       <c r="A20" s="11"/>
-      <c r="B20" s="111"/>
+      <c r="B20" s="123"/>
       <c r="C20" s="50" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D20" s="113" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="114"/>
-      <c r="F20" s="115"/>
+      <c r="D20" s="110" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="111"/>
+      <c r="F20" s="112"/>
       <c r="G20" s="50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="48" t="s">
@@ -4326,18 +4320,18 @@
     </row>
     <row r="21" spans="1:14" ht="252">
       <c r="A21" s="11"/>
-      <c r="B21" s="111"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="50" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D21" s="113" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="114"/>
-      <c r="F21" s="115"/>
+      <c r="D21" s="110" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="111"/>
+      <c r="F21" s="112"/>
       <c r="G21" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="48" t="s">
@@ -4353,18 +4347,18 @@
     </row>
     <row r="22" spans="1:14" ht="126">
       <c r="A22" s="11"/>
-      <c r="B22" s="111"/>
+      <c r="B22" s="123"/>
       <c r="C22" s="50" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D22" s="113" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="114"/>
-      <c r="F22" s="115"/>
+      <c r="D22" s="110" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="111"/>
+      <c r="F22" s="112"/>
       <c r="G22" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="48" t="s">
@@ -4380,18 +4374,18 @@
     </row>
     <row r="23" spans="1:14" ht="63">
       <c r="A23" s="11"/>
-      <c r="B23" s="111"/>
+      <c r="B23" s="123"/>
       <c r="C23" s="50" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D23" s="113" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="114"/>
-      <c r="F23" s="115"/>
+      <c r="D23" s="110" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="111"/>
+      <c r="F23" s="112"/>
       <c r="G23" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="48" t="s">
@@ -4407,18 +4401,18 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="111"/>
+      <c r="B24" s="123"/>
       <c r="C24" s="50" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D24" s="113" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="114"/>
-      <c r="F24" s="115"/>
+      <c r="D24" s="110" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="111"/>
+      <c r="F24" s="112"/>
       <c r="G24" s="50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="48" t="s">
@@ -4434,18 +4428,18 @@
     </row>
     <row r="25" spans="1:14" ht="75.599999999999994">
       <c r="A25" s="11"/>
-      <c r="B25" s="111"/>
+      <c r="B25" s="123"/>
       <c r="C25" s="50" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D25" s="113" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" s="114"/>
-      <c r="F25" s="115"/>
+      <c r="D25" s="110" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="111"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="48" t="s">
@@ -4461,18 +4455,18 @@
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="111"/>
+      <c r="B26" s="123"/>
       <c r="C26" s="50" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D26" s="113" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="114"/>
-      <c r="F26" s="115"/>
+      <c r="D26" s="110" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="111"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="48" t="s">
@@ -4488,18 +4482,18 @@
     </row>
     <row r="27" spans="1:14" ht="88.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="111"/>
+      <c r="B27" s="123"/>
       <c r="C27" s="50" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D27" s="113" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" s="114"/>
-      <c r="F27" s="115"/>
+      <c r="D27" s="110" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="111"/>
+      <c r="F27" s="112"/>
       <c r="G27" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="48" t="s">
@@ -4515,18 +4509,18 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="112"/>
+      <c r="B28" s="124"/>
       <c r="C28" s="50" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D28" s="113" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" s="114"/>
-      <c r="F28" s="115"/>
+      <c r="D28" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="111"/>
+      <c r="F28" s="112"/>
       <c r="G28" s="50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="48" t="s">
@@ -4542,7 +4536,7 @@
     </row>
     <row r="29" spans="1:14" ht="37.799999999999997">
       <c r="A29" s="11"/>
-      <c r="B29" s="110" t="str">
+      <c r="B29" s="122" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
@@ -4550,13 +4544,13 @@
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D29" s="113" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" s="114"/>
-      <c r="F29" s="115"/>
+      <c r="D29" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="111"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="48" t="s">
@@ -4572,18 +4566,18 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="111"/>
+      <c r="B30" s="123"/>
       <c r="C30" s="50" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D30" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" s="114"/>
-      <c r="F30" s="115"/>
+      <c r="D30" s="110" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="111"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="48" t="s">
@@ -4599,18 +4593,18 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="111"/>
+      <c r="B31" s="123"/>
       <c r="C31" s="50" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D31" s="113" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31" s="114"/>
-      <c r="F31" s="115"/>
+      <c r="D31" s="110" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" s="111"/>
+      <c r="F31" s="112"/>
       <c r="G31" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="48" t="s">
@@ -4626,18 +4620,18 @@
     </row>
     <row r="32" spans="1:14" ht="25.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="111"/>
+      <c r="B32" s="123"/>
       <c r="C32" s="50" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D32" s="113" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32" s="114"/>
-      <c r="F32" s="115"/>
+      <c r="D32" s="110" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="111"/>
+      <c r="F32" s="112"/>
       <c r="G32" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="48" t="s">
@@ -4653,18 +4647,18 @@
     </row>
     <row r="33" spans="1:14" ht="63">
       <c r="A33" s="11"/>
-      <c r="B33" s="111"/>
+      <c r="B33" s="123"/>
       <c r="C33" s="50" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D33" s="113" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="114"/>
-      <c r="F33" s="115"/>
+      <c r="D33" s="110" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="111"/>
+      <c r="F33" s="112"/>
       <c r="G33" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="48" t="s">
@@ -4680,18 +4674,18 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="111"/>
+      <c r="B34" s="123"/>
       <c r="C34" s="50" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D34" s="113" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="114"/>
-      <c r="F34" s="115"/>
+      <c r="D34" s="110" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="111"/>
+      <c r="F34" s="112"/>
       <c r="G34" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="48" t="s">
@@ -4707,18 +4701,18 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="111"/>
+      <c r="B35" s="123"/>
       <c r="C35" s="50" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D35" s="113" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="114"/>
-      <c r="F35" s="115"/>
+      <c r="D35" s="110" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="111"/>
+      <c r="F35" s="112"/>
       <c r="G35" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="48" t="s">
@@ -4734,18 +4728,18 @@
     </row>
     <row r="36" spans="1:14" ht="63">
       <c r="A36" s="11"/>
-      <c r="B36" s="111"/>
+      <c r="B36" s="123"/>
       <c r="C36" s="50" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D36" s="113" t="s">
-        <v>140</v>
-      </c>
-      <c r="E36" s="114"/>
-      <c r="F36" s="115"/>
+      <c r="D36" s="110" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="111"/>
+      <c r="F36" s="112"/>
       <c r="G36" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="48" t="s">
@@ -4761,18 +4755,18 @@
     </row>
     <row r="37" spans="1:14" ht="25.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="111"/>
+      <c r="B37" s="123"/>
       <c r="C37" s="50" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D37" s="113" t="s">
-        <v>131</v>
-      </c>
-      <c r="E37" s="114"/>
-      <c r="F37" s="115"/>
+      <c r="D37" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="111"/>
+      <c r="F37" s="112"/>
       <c r="G37" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="48" t="s">
@@ -4788,18 +4782,18 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="111"/>
+      <c r="B38" s="123"/>
       <c r="C38" s="50" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D38" s="113" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
+      <c r="D38" s="110" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="111"/>
+      <c r="F38" s="112"/>
       <c r="G38" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="48" t="s">
@@ -4815,18 +4809,18 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="111"/>
+      <c r="B39" s="123"/>
       <c r="C39" s="50" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D39" s="113" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="114"/>
-      <c r="F39" s="115"/>
+      <c r="D39" s="110" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="111"/>
+      <c r="F39" s="112"/>
       <c r="G39" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="48" t="s">
@@ -4842,18 +4836,18 @@
     </row>
     <row r="40" spans="1:14" ht="63">
       <c r="A40" s="11"/>
-      <c r="B40" s="111"/>
+      <c r="B40" s="123"/>
       <c r="C40" s="50" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D40" s="113" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="114"/>
-      <c r="F40" s="115"/>
+      <c r="D40" s="110" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="111"/>
+      <c r="F40" s="112"/>
       <c r="G40" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="48" t="s">
@@ -4869,18 +4863,18 @@
     </row>
     <row r="41" spans="1:14" ht="37.799999999999997">
       <c r="A41" s="11"/>
-      <c r="B41" s="112"/>
+      <c r="B41" s="124"/>
       <c r="C41" s="50" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D41" s="113" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="114"/>
-      <c r="F41" s="115"/>
+      <c r="D41" s="110" t="s">
+        <v>142</v>
+      </c>
+      <c r="E41" s="111"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="48" t="s">
@@ -4896,7 +4890,7 @@
     </row>
     <row r="42" spans="1:14" ht="113.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="122" t="str">
+      <c r="B42" s="128" t="str">
         <f>master!B32</f>
         <v>個人演習</v>
       </c>
@@ -4904,13 +4898,13 @@
         <f>master!C32</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D42" s="119" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" s="120"/>
-      <c r="F42" s="121"/>
+      <c r="D42" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="114"/>
+      <c r="F42" s="115"/>
       <c r="G42" s="69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H42" s="70"/>
       <c r="I42" s="71" t="s">
@@ -4926,18 +4920,18 @@
     </row>
     <row r="43" spans="1:14" ht="201.6">
       <c r="A43" s="11"/>
-      <c r="B43" s="123"/>
+      <c r="B43" s="129"/>
       <c r="C43" s="69" t="str">
         <f>master!C33</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D43" s="119" t="s">
-        <v>144</v>
-      </c>
-      <c r="E43" s="120"/>
-      <c r="F43" s="121"/>
+      <c r="D43" s="113" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="114"/>
+      <c r="F43" s="115"/>
       <c r="G43" s="69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H43" s="70"/>
       <c r="I43" s="71" t="s">
@@ -4953,18 +4947,18 @@
     </row>
     <row r="44" spans="1:14" ht="176.4">
       <c r="A44" s="11"/>
-      <c r="B44" s="123"/>
+      <c r="B44" s="129"/>
       <c r="C44" s="69" t="str">
         <f>master!C34</f>
         <v>サービスの検討</v>
       </c>
-      <c r="D44" s="119" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44" s="120"/>
-      <c r="F44" s="121"/>
+      <c r="D44" s="113" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="114"/>
+      <c r="F44" s="115"/>
       <c r="G44" s="69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H44" s="70"/>
       <c r="I44" s="71" t="s">
@@ -4980,18 +4974,18 @@
     </row>
     <row r="45" spans="1:14" ht="138.6">
       <c r="A45" s="11"/>
-      <c r="B45" s="123"/>
+      <c r="B45" s="129"/>
       <c r="C45" s="69" t="str">
         <f>master!C35</f>
         <v>サービスのブラッシュアップ</v>
       </c>
-      <c r="D45" s="119" t="s">
-        <v>106</v>
-      </c>
-      <c r="E45" s="120"/>
-      <c r="F45" s="121"/>
+      <c r="D45" s="113" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="114"/>
+      <c r="F45" s="115"/>
       <c r="G45" s="69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H45" s="70"/>
       <c r="I45" s="71" t="s">
@@ -5007,18 +5001,18 @@
     </row>
     <row r="46" spans="1:14" ht="63">
       <c r="A46" s="11"/>
-      <c r="B46" s="123"/>
+      <c r="B46" s="129"/>
       <c r="C46" s="69" t="str">
         <f>master!C36</f>
         <v>サービスの決定</v>
       </c>
-      <c r="D46" s="119" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" s="120"/>
-      <c r="F46" s="121"/>
+      <c r="D46" s="113" t="s">
+        <v>104</v>
+      </c>
+      <c r="E46" s="114"/>
+      <c r="F46" s="115"/>
       <c r="G46" s="69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H46" s="70"/>
       <c r="I46" s="71" t="s">
@@ -5034,25 +5028,25 @@
     </row>
     <row r="47" spans="1:14" ht="138.6">
       <c r="A47" s="11"/>
-      <c r="B47" s="123"/>
+      <c r="B47" s="129"/>
       <c r="C47" s="69" t="str">
         <f>master!C37</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D47" s="119" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47" s="120"/>
-      <c r="F47" s="121"/>
+      <c r="D47" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="114"/>
+      <c r="F47" s="115"/>
       <c r="G47" s="69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H47" s="70"/>
       <c r="I47" s="71" t="s">
         <v>24</v>
       </c>
       <c r="J47" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K47" s="73"/>
       <c r="L47" s="6"/>
@@ -5061,25 +5055,25 @@
     </row>
     <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="124"/>
+      <c r="B48" s="130"/>
       <c r="C48" s="69" t="str">
         <f>master!C38</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D48" s="119" t="s">
-        <v>103</v>
-      </c>
-      <c r="E48" s="120"/>
-      <c r="F48" s="121"/>
+      <c r="D48" s="113" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="114"/>
+      <c r="F48" s="115"/>
       <c r="G48" s="69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H48" s="70"/>
       <c r="I48" s="71" t="s">
         <v>24</v>
       </c>
       <c r="J48" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K48" s="73"/>
       <c r="L48" s="6"/>
@@ -5088,7 +5082,7 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="122" t="str">
+      <c r="B49" s="128" t="str">
         <f>master!B40</f>
         <v>チーム演習</v>
       </c>
@@ -5096,13 +5090,13 @@
         <f>master!C40</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D49" s="119" t="s">
-        <v>111</v>
-      </c>
-      <c r="E49" s="120"/>
-      <c r="F49" s="121"/>
+      <c r="D49" s="113" t="s">
+        <v>110</v>
+      </c>
+      <c r="E49" s="114"/>
+      <c r="F49" s="115"/>
       <c r="G49" s="69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H49" s="70"/>
       <c r="I49" s="71" t="s">
@@ -5118,18 +5112,18 @@
     </row>
     <row r="50" spans="1:14" ht="201.6">
       <c r="A50" s="11"/>
-      <c r="B50" s="123"/>
+      <c r="B50" s="129"/>
       <c r="C50" s="69" t="str">
         <f>master!C41</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D50" s="119" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="120"/>
-      <c r="F50" s="121"/>
+      <c r="D50" s="113" t="s">
+        <v>144</v>
+      </c>
+      <c r="E50" s="114"/>
+      <c r="F50" s="115"/>
       <c r="G50" s="69" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H50" s="70"/>
       <c r="I50" s="71" t="s">
@@ -5145,18 +5139,18 @@
     </row>
     <row r="51" spans="1:14" ht="37.799999999999997">
       <c r="A51" s="11"/>
-      <c r="B51" s="123"/>
+      <c r="B51" s="129"/>
       <c r="C51" s="69" t="str">
         <f>master!C42</f>
         <v>【参考】最終発表時の評価基準</v>
       </c>
-      <c r="D51" s="119" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="120"/>
-      <c r="F51" s="121"/>
+      <c r="D51" s="113" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="114"/>
+      <c r="F51" s="115"/>
       <c r="G51" s="69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H51" s="70"/>
       <c r="I51" s="71" t="s">
@@ -5172,18 +5166,18 @@
     </row>
     <row r="52" spans="1:14" ht="113.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="123"/>
+      <c r="B52" s="129"/>
       <c r="C52" s="69" t="str">
         <f>master!C43</f>
         <v>サービスの提案</v>
       </c>
-      <c r="D52" s="119" t="s">
-        <v>162</v>
-      </c>
-      <c r="E52" s="120"/>
-      <c r="F52" s="121"/>
+      <c r="D52" s="113" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="114"/>
+      <c r="F52" s="115"/>
       <c r="G52" s="69" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H52" s="70"/>
       <c r="I52" s="71" t="s">
@@ -5199,25 +5193,25 @@
     </row>
     <row r="53" spans="1:14" ht="100.8">
       <c r="A53" s="11"/>
-      <c r="B53" s="123"/>
+      <c r="B53" s="129"/>
       <c r="C53" s="69" t="str">
         <f>master!C44</f>
         <v>サービスの決定（チーム）</v>
       </c>
-      <c r="D53" s="119" t="s">
-        <v>147</v>
-      </c>
-      <c r="E53" s="120"/>
-      <c r="F53" s="121"/>
+      <c r="D53" s="113" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" s="114"/>
+      <c r="F53" s="115"/>
       <c r="G53" s="69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H53" s="70"/>
       <c r="I53" s="71" t="s">
         <v>24</v>
       </c>
       <c r="J53" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K53" s="73"/>
       <c r="L53" s="6"/>
@@ -5226,25 +5220,25 @@
     </row>
     <row r="54" spans="1:14" ht="113.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="123"/>
+      <c r="B54" s="129"/>
       <c r="C54" s="69" t="str">
         <f>master!C45</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D54" s="119" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" s="120"/>
-      <c r="F54" s="121"/>
+      <c r="D54" s="113" t="s">
+        <v>112</v>
+      </c>
+      <c r="E54" s="114"/>
+      <c r="F54" s="115"/>
       <c r="G54" s="69" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H54" s="70"/>
       <c r="I54" s="71" t="s">
         <v>24</v>
       </c>
       <c r="J54" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K54" s="73"/>
       <c r="L54" s="6"/>
@@ -5253,25 +5247,25 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="123"/>
+      <c r="B55" s="129"/>
       <c r="C55" s="69" t="str">
         <f>master!C46</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D55" s="119" t="s">
-        <v>103</v>
-      </c>
-      <c r="E55" s="120"/>
-      <c r="F55" s="121"/>
+      <c r="D55" s="113" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="114"/>
+      <c r="F55" s="115"/>
       <c r="G55" s="69" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H55" s="70"/>
       <c r="I55" s="71" t="s">
         <v>24</v>
       </c>
       <c r="J55" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K55" s="73"/>
       <c r="L55" s="6"/>
@@ -5280,25 +5274,25 @@
     </row>
     <row r="56" spans="1:14" ht="25.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="124"/>
+      <c r="B56" s="130"/>
       <c r="C56" s="69" t="str">
         <f>master!C47</f>
         <v>提案のリハーサル</v>
       </c>
-      <c r="D56" s="119" t="s">
-        <v>160</v>
-      </c>
-      <c r="E56" s="120"/>
-      <c r="F56" s="121"/>
+      <c r="D56" s="113" t="s">
+        <v>159</v>
+      </c>
+      <c r="E56" s="114"/>
+      <c r="F56" s="115"/>
       <c r="G56" s="69" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H56" s="70"/>
       <c r="I56" s="71" t="s">
         <v>24</v>
       </c>
       <c r="J56" s="72" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K56" s="73"/>
       <c r="L56" s="6"/>
@@ -5307,7 +5301,7 @@
     </row>
     <row r="57" spans="1:14" ht="100.8">
       <c r="A57" s="11"/>
-      <c r="B57" s="116" t="str">
+      <c r="B57" s="125" t="str">
         <f>master!B49</f>
         <v>提案会（ブロック代表の決定）</v>
       </c>
@@ -5315,13 +5309,13 @@
         <f>master!C49</f>
         <v>ブロック内発表の説明</v>
       </c>
-      <c r="D57" s="125" t="s">
-        <v>115</v>
-      </c>
-      <c r="E57" s="126"/>
-      <c r="F57" s="127"/>
+      <c r="D57" s="116" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="117"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="76" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H57" s="77"/>
       <c r="I57" s="78" t="s">
@@ -5337,25 +5331,25 @@
     </row>
     <row r="58" spans="1:14" ht="113.4">
       <c r="A58" s="11"/>
-      <c r="B58" s="117"/>
+      <c r="B58" s="126"/>
       <c r="C58" s="76" t="str">
         <f>master!C50</f>
         <v>ブロック内発表の実施</v>
       </c>
-      <c r="D58" s="125" t="s">
-        <v>163</v>
-      </c>
-      <c r="E58" s="126"/>
-      <c r="F58" s="127"/>
+      <c r="D58" s="116" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="117"/>
+      <c r="F58" s="118"/>
       <c r="G58" s="76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H58" s="77"/>
       <c r="I58" s="78" t="s">
         <v>24</v>
       </c>
       <c r="J58" s="79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K58" s="80"/>
       <c r="L58" s="6"/>
@@ -5364,18 +5358,18 @@
     </row>
     <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="118"/>
+      <c r="B59" s="127"/>
       <c r="C59" s="76" t="str">
         <f>master!C51</f>
         <v>ブロック代表（選抜チーム）の決定</v>
       </c>
-      <c r="D59" s="125" t="s">
-        <v>117</v>
-      </c>
-      <c r="E59" s="126"/>
-      <c r="F59" s="127"/>
+      <c r="D59" s="116" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" s="117"/>
+      <c r="F59" s="118"/>
       <c r="G59" s="76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H59" s="77"/>
       <c r="I59" s="78" t="s">
@@ -5399,20 +5393,20 @@
         <f>master!C52</f>
         <v>全体発表</v>
       </c>
-      <c r="D60" s="125" t="s">
-        <v>164</v>
-      </c>
-      <c r="E60" s="126"/>
-      <c r="F60" s="127"/>
+      <c r="D60" s="116" t="s">
+        <v>163</v>
+      </c>
+      <c r="E60" s="117"/>
+      <c r="F60" s="118"/>
       <c r="G60" s="76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H60" s="77"/>
       <c r="I60" s="78" t="s">
         <v>24</v>
       </c>
       <c r="J60" s="79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K60" s="80"/>
       <c r="L60" s="6"/>
@@ -5420,7 +5414,51 @@
       <c r="N60" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="60">
+    <mergeCell ref="B17:B28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B29:B41"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="D60:F60"/>
@@ -5437,49 +5475,6 @@
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="B17:B28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B29:B41"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="B49:B56"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D44:F44"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5512,7 +5507,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -5529,76 +5524,76 @@
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="2:3">
@@ -5607,70 +5602,70 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="74" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" s="74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" s="74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" s="74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" s="74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="C24" s="74" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" s="75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" s="74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" s="74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" s="74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" s="74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="2:3">
@@ -5679,40 +5674,40 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32" s="74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" s="74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" s="74" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="C35" s="74" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="2:3">
@@ -5721,45 +5716,45 @@
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C40" s="74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" s="74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" s="74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" s="74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="2:3">
@@ -5768,28 +5763,28 @@
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C49" s="74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="C50" s="74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="C51" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C52" s="74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/IG/AI Native-提案演習_IG.xlsx
+++ b/IG/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17DF8D2-36DA-4BEC-89AE-D357B4F7CB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99893187-EF72-46E6-B6E9-C26F69A46DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（5日）'!$A$1:$L$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -63,7 +63,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{938B8858-7680-4470-B4E9-3F8DB4920554}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{938B8858-7680-4470-B4E9-3F8DB4920554}">
       <text>
         <r>
           <rPr>
@@ -499,51 +499,51 @@
   </si>
   <si>
     <t>１．サマリ</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>２．背景</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>３．現状課題</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>４．業界動向・市場分析</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>５．市場機会</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>６．サービス概要</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>７．利用者体験イメージ</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>８．事業構成</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>９．提供価値</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>１０．収益モデル</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>１１．リスク・課題</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>１２．今後の展望</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>演習内容の説明</t>
@@ -1425,7 +1425,7 @@
   </si>
   <si>
     <t>はじめに</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <r>
@@ -1722,7 +1722,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1799,13 +1799,6 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2145,7 +2138,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2185,10 +2178,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2206,19 +2199,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2230,251 +2214,260 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2485,6 +2478,15 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2494,6 +2496,15 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2503,47 +2514,14 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2927,19 +2905,19 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="96" t="str">
+      <c r="B2" s="93" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案演習_IG」</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="3" spans="1:11" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -2956,10 +2934,10 @@
     </row>
     <row r="4" spans="1:11" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="98"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2971,8 +2949,8 @@
     </row>
     <row r="5" spans="1:11" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="100"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -2989,10 +2967,10 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="16.2">
-      <c r="B7" s="101" t="s">
+      <c r="B7" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="101"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -3009,644 +2987,644 @@
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="24"/>
-      <c r="C9" s="24" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24" t="s">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24" t="s">
+      <c r="F9" s="21"/>
+      <c r="G9" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24" t="s">
+      <c r="H9" s="21"/>
+      <c r="I9" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24" t="s">
+      <c r="J9" s="21"/>
+      <c r="K9" s="21" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A10" s="37">
+      <c r="A10" s="34">
         <v>0.39583333333333331</v>
       </c>
       <c r="B10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="59" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="59" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="59" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="59" t="s">
         <v>3</v>
       </c>
       <c r="J10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="K10" s="62" t="s">
+      <c r="K10" s="59" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="39"/>
-      <c r="B11" s="57">
+      <c r="A11" s="36"/>
+      <c r="B11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="60" t="str">
+      <c r="C11" s="57" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="57">
+      <c r="E11" s="90"/>
+      <c r="F11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="93" t="str">
+      <c r="G11" s="90" t="str">
         <f>master!B40</f>
         <v>チーム演習</v>
       </c>
-      <c r="H11" s="57">
+      <c r="H11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="I11" s="94"/>
-      <c r="J11" s="57">
+      <c r="I11" s="91"/>
+      <c r="J11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="K11" s="82" t="str">
+      <c r="K11" s="79" t="str">
         <f>master!B49</f>
         <v>提案会（ブロック代表の決定）</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="37">
+      <c r="A12" s="34">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="89">
+      <c r="B12" s="86">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C12" s="60" t="str">
+      <c r="C12" s="57" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="83"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="80"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="38"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="83"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="80"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="38"/>
-      <c r="B14" s="57">
+      <c r="A14" s="35"/>
+      <c r="B14" s="54">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="60" t="str">
+      <c r="C14" s="57" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="83"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="80"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="39"/>
-      <c r="B15" s="91" t="s">
+      <c r="A15" s="36"/>
+      <c r="B15" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="61"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="83"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="80"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="37">
+      <c r="A16" s="34">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="57">
+      <c r="B16" s="54">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="93" t="str">
+      <c r="C16" s="90" t="str">
         <f>master!B32</f>
         <v>個人演習</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="83"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="80"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="38"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="83"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="38"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="83"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="80"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="39"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="83"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="80"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="56">
+      <c r="A20" s="53">
         <v>0.5</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="83"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="80"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="52"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="84"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="81"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="E22" s="63" t="s">
+      <c r="E22" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="G22" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="I22" s="63" t="s">
+      <c r="I22" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="K22" s="63" t="s">
+      <c r="K22" s="60" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="39"/>
-      <c r="B23" s="38" t="s">
+      <c r="A23" s="36"/>
+      <c r="B23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="38" t="s">
+      <c r="C23" s="61"/>
+      <c r="D23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="64"/>
-      <c r="F23" s="38" t="s">
+      <c r="E23" s="61"/>
+      <c r="F23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="64"/>
-      <c r="H23" s="38" t="s">
+      <c r="G23" s="61"/>
+      <c r="H23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="64"/>
-      <c r="J23" s="38" t="s">
+      <c r="I23" s="61"/>
+      <c r="J23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="64"/>
+      <c r="K23" s="61"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="37">
+      <c r="A24" s="34">
         <v>0.54166666666666663</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="38" t="s">
+      <c r="C24" s="61"/>
+      <c r="D24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="64"/>
-      <c r="F24" s="38" t="s">
+      <c r="E24" s="61"/>
+      <c r="F24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="64"/>
-      <c r="H24" s="38" t="s">
+      <c r="G24" s="61"/>
+      <c r="H24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="64"/>
-      <c r="J24" s="38" t="s">
+      <c r="I24" s="61"/>
+      <c r="J24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="K24" s="64"/>
+      <c r="K24" s="61"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39" t="s">
+      <c r="A25" s="35"/>
+      <c r="B25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="39" t="s">
+      <c r="C25" s="62"/>
+      <c r="D25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="39" t="s">
+      <c r="E25" s="62"/>
+      <c r="F25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="39" t="s">
+      <c r="G25" s="62"/>
+      <c r="H25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="65"/>
-      <c r="J25" s="39" t="s">
+      <c r="I25" s="62"/>
+      <c r="J25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="65"/>
+      <c r="K25" s="62"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="38"/>
-      <c r="B26" s="40">
+      <c r="A26" s="35"/>
+      <c r="B26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="93"/>
-      <c r="D26" s="40">
+      <c r="C26" s="90"/>
+      <c r="D26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="93"/>
-      <c r="F26" s="40">
+      <c r="E26" s="90"/>
+      <c r="F26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="93"/>
-      <c r="H26" s="40">
+      <c r="G26" s="90"/>
+      <c r="H26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="I26" s="93"/>
-      <c r="J26" s="40">
+      <c r="I26" s="90"/>
+      <c r="J26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="K26" s="82" t="str">
+      <c r="K26" s="79" t="str">
         <f>master!B52</f>
         <v>提案会（最終）</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="39"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="83"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="80"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="37">
+      <c r="A28" s="34">
         <v>0.58333333333333337</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="83"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="80"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="38"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="94"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="51"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="48"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="38"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="51"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="91"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="48"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="39"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="51"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="48"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="56">
+      <c r="A32" s="53">
         <v>0.625</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="51"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="48"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="52"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="51"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="48"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="52"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="51"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="91"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="91"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="48"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="39"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="51"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="91"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="91"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="91"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="48"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="37">
+      <c r="A36" s="34">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B36" s="42"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="94"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="51"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="80"/>
+      <c r="L36" s="48"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="38"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="94"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="51"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="91"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="48"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="38"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="94"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="94"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="51"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="91"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="91"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="48"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="38"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="51"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="48"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="40">
+      <c r="A40" s="37">
         <v>0.70833333333333337</v>
       </c>
-      <c r="B40" s="42"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="94"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="51"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="91"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="48"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="38"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="42"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="53"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="80"/>
+      <c r="L41" s="50"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="42"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="51"/>
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="89"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="89"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="48"/>
     </row>
     <row r="43" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A43" s="41"/>
-      <c r="B43" s="85">
+      <c r="A43" s="38"/>
+      <c r="B43" s="82">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="86" t="s">
+      <c r="C43" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="85">
+      <c r="D43" s="82">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="86" t="s">
+      <c r="E43" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="F43" s="85">
+      <c r="F43" s="82">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="86" t="s">
+      <c r="G43" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="H43" s="85">
+      <c r="H43" s="82">
         <v>0.73958333333333337</v>
       </c>
-      <c r="I43" s="86" t="s">
+      <c r="I43" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="J43" s="85">
+      <c r="J43" s="82">
         <v>0.73958333333333337</v>
       </c>
-      <c r="K43" s="86" t="s">
+      <c r="K43" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="L43" s="52"/>
+      <c r="L43" s="49"/>
     </row>
     <row r="44" spans="1:12" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
-      <c r="L44" s="22"/>
+      <c r="L44" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3663,7 +3641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L14"/>
+  <dimension ref="A2:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3673,25 +3651,25 @@
     <col min="5" max="5" width="16.33203125" style="10" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" style="24" customWidth="1"/>
     <col min="9" max="10" width="6.6640625" style="10" customWidth="1"/>
     <col min="11" max="11" width="38.44140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="4.6640625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" s="31" customFormat="1" ht="36.75" customHeight="1">
+    <row r="2" spans="1:12" s="28" customFormat="1" ht="36.75" customHeight="1">
       <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:12">
@@ -3700,36 +3678,36 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="26"/>
+      <c r="H3" s="23"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="105"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="26"/>
+      <c r="H4" s="23"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3738,159 +3716,151 @@
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="107" t="s">
+      <c r="D7" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="107"/>
-      <c r="F7" s="33" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="30" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="36" t="s">
+      <c r="E8" s="41"/>
+      <c r="F8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="33" t="s">
         <v>18</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="23"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="10"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+    <row r="10" spans="1:12">
+      <c r="A10" s="10"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="105" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="104" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="108" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103" t="s">
-        <v>30</v>
-      </c>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="101"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="63">
       <c r="A12" s="10"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="104"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="52">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K12" s="19"/>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:12" ht="63">
+    <row r="13" spans="1:12" ht="25.2">
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="95" t="s">
-        <v>41</v>
+        <v>166</v>
+      </c>
+      <c r="D13" s="99" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="92" t="s">
+        <v>169</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="55">
+      <c r="I13" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="52">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" spans="1:12" ht="25.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" s="102" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="95" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="55">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="10"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="K11:K12"/>
     <mergeCell ref="D13:F13"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3903,7 +3873,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H13:H14</xm:sqref>
+          <xm:sqref>H12:H13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3913,7 +3883,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N60"/>
+  <dimension ref="A2:N59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3963,12 +3933,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3979,81 +3949,89 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="30"/>
-    </row>
-    <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="30"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="27"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="B7" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="104"/>
+      <c r="F7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="44"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="107" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="107"/>
+      <c r="B8" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="41"/>
       <c r="F8" s="33" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="47"/>
-      <c r="J8" s="6"/>
+        <v>18</v>
+      </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="B9" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="131" t="s">
+      <c r="B9" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="36" t="s">
+      <c r="E9" s="41"/>
+      <c r="F9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="33" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="6"/>
@@ -4062,20 +4040,20 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="B10" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="131" t="s">
+      <c r="B10" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="132"/>
-      <c r="F10" s="36" t="s">
+      <c r="E10" s="41"/>
+      <c r="F10" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="33" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="6"/>
@@ -4084,20 +4062,20 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="B11" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="131" t="s">
+      <c r="B11" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="36" t="s">
+      <c r="E11" s="41"/>
+      <c r="F11" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="33" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="6"/>
@@ -4105,1363 +4083,1298 @@
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14">
-      <c r="B12" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="131" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="14" spans="1:14" ht="24" customHeight="1">
+    <row r="13" spans="1:14" ht="24" customHeight="1">
+      <c r="A13" s="10"/>
+      <c r="B13" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="100" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="125" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="126"/>
+      <c r="K13" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="10"/>
-      <c r="B14" s="104" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="104" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="104" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="103" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="119" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="120"/>
-      <c r="K14" s="103" t="s">
-        <v>32</v>
-      </c>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="101"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" ht="63">
       <c r="A15" s="10"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="104"/>
+      <c r="B15" s="84" t="str">
+        <f>master!B4</f>
+        <v>導入</v>
+      </c>
+      <c r="C15" s="47" t="str">
+        <f>master!C4</f>
+        <v>はじめに　｜　“Be a social designer”とは</v>
+      </c>
+      <c r="D15" s="110" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="111"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="43">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K15" s="40"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="63">
       <c r="A16" s="10"/>
-      <c r="B16" s="87" t="str">
-        <f>master!B4</f>
-        <v>導入</v>
-      </c>
-      <c r="C16" s="50" t="str">
-        <f>master!C4</f>
-        <v>はじめに　｜　“Be a social designer”とは</v>
+      <c r="B16" s="107" t="str">
+        <f>master!B5</f>
+        <v>企画提案のステップ</v>
+      </c>
+      <c r="C16" s="47" t="str">
+        <f>master!C5</f>
+        <v>企画提案のステップ</v>
       </c>
       <c r="D16" s="110" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" s="111"/>
       <c r="F16" s="112"/>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="47" t="s">
         <v>113</v>
       </c>
       <c r="H16" s="12"/>
-      <c r="I16" s="48" t="s">
+      <c r="I16" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="43">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K16" s="43"/>
+      <c r="K16" s="40"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="63">
-      <c r="A17" s="10"/>
-      <c r="B17" s="122" t="str">
-        <f>master!B5</f>
-        <v>企画提案のステップ</v>
-      </c>
-      <c r="C17" s="50" t="str">
-        <f>master!C5</f>
-        <v>企画提案のステップ</v>
+    <row r="17" spans="1:14" ht="163.80000000000001">
+      <c r="A17" s="11"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="47" t="str">
+        <f>master!C6</f>
+        <v>STEP①-1　日常の不便を考える</v>
       </c>
       <c r="D17" s="110" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="E17" s="111"/>
       <c r="F17" s="112"/>
-      <c r="G17" s="50" t="s">
-        <v>113</v>
+      <c r="G17" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="H17" s="12"/>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="46">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K17" s="43"/>
+      <c r="J17" s="43">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K17" s="40"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="163.80000000000001">
+    <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="123"/>
-      <c r="C18" s="50" t="str">
-        <f>master!C6</f>
-        <v>STEP①-1　日常の不便を考える</v>
+      <c r="B18" s="108"/>
+      <c r="C18" s="47" t="str">
+        <f>master!C7</f>
+        <v>STEP①-2　課題の深掘り</v>
       </c>
       <c r="D18" s="110" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="E18" s="111"/>
       <c r="F18" s="112"/>
-      <c r="G18" s="50" t="s">
-        <v>164</v>
+      <c r="G18" s="47" t="s">
+        <v>36</v>
       </c>
       <c r="H18" s="12"/>
-      <c r="I18" s="48" t="s">
+      <c r="I18" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="46">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K18" s="43"/>
+      <c r="J18" s="43">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K18" s="40"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="37.799999999999997">
+    <row r="19" spans="1:14" ht="151.19999999999999">
       <c r="A19" s="11"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="50" t="str">
-        <f>master!C7</f>
-        <v>STEP①-2　課題の深掘り</v>
+      <c r="B19" s="108"/>
+      <c r="C19" s="47" t="str">
+        <f>master!C8</f>
+        <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
       <c r="D19" s="110" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" s="111"/>
       <c r="F19" s="112"/>
-      <c r="G19" s="50" t="s">
-        <v>36</v>
+      <c r="G19" s="47" t="s">
+        <v>43</v>
       </c>
       <c r="H19" s="12"/>
-      <c r="I19" s="48" t="s">
+      <c r="I19" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="46">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K19" s="43"/>
+      <c r="J19" s="43">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K19" s="40"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="151.19999999999999">
+    <row r="20" spans="1:14" ht="252">
       <c r="A20" s="11"/>
-      <c r="B20" s="123"/>
-      <c r="C20" s="50" t="str">
-        <f>master!C8</f>
-        <v>STEP①-3　ITアイデアへ落とし込む</v>
+      <c r="B20" s="108"/>
+      <c r="C20" s="47" t="str">
+        <f>master!C9</f>
+        <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
       <c r="D20" s="110" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20" s="111"/>
       <c r="F20" s="112"/>
-      <c r="G20" s="50" t="s">
-        <v>43</v>
+      <c r="G20" s="47" t="s">
+        <v>45</v>
       </c>
       <c r="H20" s="12"/>
-      <c r="I20" s="48" t="s">
+      <c r="I20" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="46">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K20" s="43"/>
+      <c r="J20" s="43">
+        <v>0</v>
+      </c>
+      <c r="K20" s="40"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="252">
+    <row r="21" spans="1:14" ht="126">
       <c r="A21" s="11"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="50" t="str">
-        <f>master!C9</f>
-        <v>STEP②-1 創出したアイデアに関する調査・確認</v>
+      <c r="B21" s="108"/>
+      <c r="C21" s="47" t="str">
+        <f>master!C10</f>
+        <v>STEP②-2 環境分析</v>
       </c>
       <c r="D21" s="110" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" s="111"/>
       <c r="F21" s="112"/>
-      <c r="G21" s="50" t="s">
-        <v>45</v>
+      <c r="G21" s="47" t="s">
+        <v>44</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="48" t="s">
+      <c r="I21" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="46">
-        <v>0</v>
-      </c>
-      <c r="K21" s="43"/>
+      <c r="J21" s="43">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K21" s="40"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="126">
+    <row r="22" spans="1:14" ht="63">
       <c r="A22" s="11"/>
-      <c r="B22" s="123"/>
-      <c r="C22" s="50" t="str">
-        <f>master!C10</f>
-        <v>STEP②-2 環境分析</v>
+      <c r="B22" s="108"/>
+      <c r="C22" s="47" t="str">
+        <f>master!C11</f>
+        <v>（参考）PEST分析</v>
       </c>
       <c r="D22" s="110" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" s="111"/>
       <c r="F22" s="112"/>
-      <c r="G22" s="50" t="s">
-        <v>44</v>
+      <c r="G22" s="47" t="s">
+        <v>113</v>
       </c>
       <c r="H22" s="12"/>
-      <c r="I22" s="48" t="s">
+      <c r="I22" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="46">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K22" s="43"/>
+      <c r="J22" s="43">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K22" s="40"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="63">
+    <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="50" t="str">
-        <f>master!C11</f>
-        <v>（参考）PEST分析</v>
+      <c r="B23" s="108"/>
+      <c r="C23" s="47" t="str">
+        <f>master!C12</f>
+        <v>（参考） 3C分析</v>
       </c>
       <c r="D23" s="110" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E23" s="111"/>
       <c r="F23" s="112"/>
-      <c r="G23" s="50" t="s">
-        <v>113</v>
+      <c r="G23" s="47" t="s">
+        <v>37</v>
       </c>
       <c r="H23" s="12"/>
-      <c r="I23" s="48" t="s">
+      <c r="I23" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="46">
+      <c r="J23" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K23" s="43"/>
+      <c r="K23" s="40"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="123"/>
-      <c r="C24" s="50" t="str">
-        <f>master!C12</f>
-        <v>（参考） 3C分析</v>
+      <c r="B24" s="108"/>
+      <c r="C24" s="47" t="str">
+        <f>master!C13</f>
+        <v>（参考） SWOT分析</v>
       </c>
       <c r="D24" s="110" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E24" s="111"/>
       <c r="F24" s="112"/>
-      <c r="G24" s="50" t="s">
+      <c r="G24" s="47" t="s">
         <v>37</v>
       </c>
       <c r="H24" s="12"/>
-      <c r="I24" s="48" t="s">
+      <c r="I24" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="46">
+      <c r="J24" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K24" s="43"/>
+      <c r="K24" s="40"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="75.599999999999994">
+    <row r="25" spans="1:14" ht="113.4">
       <c r="A25" s="11"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="50" t="str">
-        <f>master!C13</f>
-        <v>（参考） SWOT分析</v>
+      <c r="B25" s="108"/>
+      <c r="C25" s="47" t="str">
+        <f>master!C14</f>
+        <v>STEP③-1 提案書作成</v>
       </c>
       <c r="D25" s="110" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25" s="111"/>
       <c r="F25" s="112"/>
-      <c r="G25" s="50" t="s">
-        <v>37</v>
+      <c r="G25" s="47" t="s">
+        <v>38</v>
       </c>
       <c r="H25" s="12"/>
-      <c r="I25" s="48" t="s">
+      <c r="I25" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K25" s="43"/>
+      <c r="K25" s="40"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="113.4">
+    <row r="26" spans="1:14" ht="88.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="123"/>
-      <c r="C26" s="50" t="str">
-        <f>master!C14</f>
-        <v>STEP③-1 提案書作成</v>
+      <c r="B26" s="108"/>
+      <c r="C26" s="47" t="str">
+        <f>master!C15</f>
+        <v>STEP③-2 プロトタイプ作成</v>
       </c>
       <c r="D26" s="110" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E26" s="111"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="50" t="s">
-        <v>38</v>
+      <c r="G26" s="47" t="s">
+        <v>39</v>
       </c>
       <c r="H26" s="12"/>
-      <c r="I26" s="48" t="s">
+      <c r="I26" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="46">
+      <c r="J26" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K26" s="43"/>
+      <c r="K26" s="40"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="88.2">
+    <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="123"/>
-      <c r="C27" s="50" t="str">
-        <f>master!C15</f>
-        <v>STEP③-2 プロトタイプ作成</v>
+      <c r="B27" s="109"/>
+      <c r="C27" s="47" t="str">
+        <f>master!C16</f>
+        <v>まとめ</v>
       </c>
       <c r="D27" s="110" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" s="111"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="50" t="s">
-        <v>39</v>
+      <c r="G27" s="47" t="s">
+        <v>38</v>
       </c>
       <c r="H27" s="12"/>
-      <c r="I27" s="48" t="s">
+      <c r="I27" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="46">
+      <c r="J27" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K27" s="43"/>
+      <c r="K27" s="40"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="113.4">
+    <row r="28" spans="1:14" ht="37.799999999999997">
       <c r="A28" s="11"/>
-      <c r="B28" s="124"/>
-      <c r="C28" s="50" t="str">
-        <f>master!C16</f>
-        <v>まとめ</v>
+      <c r="B28" s="107" t="str">
+        <f>master!B18</f>
+        <v>提案書のサンプルについて</v>
+      </c>
+      <c r="C28" s="47" t="str">
+        <f>master!C18</f>
+        <v>はじめに</v>
       </c>
       <c r="D28" s="110" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="E28" s="111"/>
       <c r="F28" s="112"/>
-      <c r="G28" s="50" t="s">
-        <v>38</v>
+      <c r="G28" s="47" t="s">
+        <v>131</v>
       </c>
       <c r="H28" s="12"/>
-      <c r="I28" s="48" t="s">
+      <c r="I28" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="46">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K28" s="43"/>
+      <c r="J28" s="43">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K28" s="40"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="37.799999999999997">
+    <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="122" t="str">
-        <f>master!B18</f>
-        <v>提案書のサンプルについて</v>
-      </c>
-      <c r="C29" s="50" t="str">
-        <f>master!C18</f>
-        <v>はじめに</v>
+      <c r="B29" s="108"/>
+      <c r="C29" s="47" t="str">
+        <f>master!C19</f>
+        <v>１．サマリ</v>
       </c>
       <c r="D29" s="110" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="E29" s="111"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="50" t="s">
-        <v>131</v>
+      <c r="G29" s="47" t="s">
+        <v>89</v>
       </c>
       <c r="H29" s="12"/>
-      <c r="I29" s="48" t="s">
+      <c r="I29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="46">
+      <c r="J29" s="43">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K29" s="43"/>
+      <c r="K29" s="40"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="123"/>
-      <c r="C30" s="50" t="str">
-        <f>master!C19</f>
-        <v>１．サマリ</v>
+      <c r="B30" s="108"/>
+      <c r="C30" s="47" t="str">
+        <f>master!C20</f>
+        <v>２．背景</v>
       </c>
       <c r="D30" s="110" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E30" s="111"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="50" t="s">
+      <c r="G30" s="47" t="s">
         <v>89</v>
       </c>
       <c r="H30" s="12"/>
-      <c r="I30" s="48" t="s">
+      <c r="I30" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="46">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K30" s="43"/>
+      <c r="J30" s="43">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K30" s="40"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="123"/>
-      <c r="C31" s="50" t="str">
-        <f>master!C20</f>
-        <v>２．背景</v>
+      <c r="B31" s="108"/>
+      <c r="C31" s="47" t="str">
+        <f>master!C21</f>
+        <v>３．現状課題</v>
       </c>
       <c r="D31" s="110" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E31" s="111"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="50" t="s">
+      <c r="G31" s="47" t="s">
         <v>89</v>
       </c>
       <c r="H31" s="12"/>
-      <c r="I31" s="48" t="s">
+      <c r="I31" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J31" s="46">
+      <c r="J31" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K31" s="43"/>
+      <c r="K31" s="40"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="25.2">
+    <row r="32" spans="1:14" ht="63">
       <c r="A32" s="11"/>
-      <c r="B32" s="123"/>
-      <c r="C32" s="50" t="str">
-        <f>master!C21</f>
-        <v>３．現状課題</v>
+      <c r="B32" s="108"/>
+      <c r="C32" s="47" t="str">
+        <f>master!C22</f>
+        <v>４．業界動向・市場分析</v>
       </c>
       <c r="D32" s="110" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E32" s="111"/>
       <c r="F32" s="112"/>
-      <c r="G32" s="50" t="s">
-        <v>89</v>
+      <c r="G32" s="47" t="s">
+        <v>132</v>
       </c>
       <c r="H32" s="12"/>
-      <c r="I32" s="48" t="s">
+      <c r="I32" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="46">
+      <c r="J32" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K32" s="43"/>
+      <c r="K32" s="40"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="63">
+    <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="50" t="str">
-        <f>master!C22</f>
-        <v>４．業界動向・市場分析</v>
+      <c r="B33" s="108"/>
+      <c r="C33" s="47" t="str">
+        <f>master!C23</f>
+        <v>５．市場機会</v>
       </c>
       <c r="D33" s="110" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E33" s="111"/>
       <c r="F33" s="112"/>
-      <c r="G33" s="50" t="s">
-        <v>132</v>
+      <c r="G33" s="47" t="s">
+        <v>131</v>
       </c>
       <c r="H33" s="12"/>
-      <c r="I33" s="48" t="s">
+      <c r="I33" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="46">
+      <c r="J33" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K33" s="43"/>
+      <c r="K33" s="40"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="123"/>
-      <c r="C34" s="50" t="str">
-        <f>master!C23</f>
-        <v>５．市場機会</v>
+      <c r="B34" s="108"/>
+      <c r="C34" s="47" t="str">
+        <f>master!C24</f>
+        <v>６．サービス概要</v>
       </c>
       <c r="D34" s="110" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E34" s="111"/>
       <c r="F34" s="112"/>
-      <c r="G34" s="50" t="s">
+      <c r="G34" s="47" t="s">
         <v>131</v>
       </c>
       <c r="H34" s="12"/>
-      <c r="I34" s="48" t="s">
+      <c r="I34" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="46">
+      <c r="J34" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K34" s="43"/>
+      <c r="K34" s="40"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="37.799999999999997">
+    <row r="35" spans="1:14" ht="63">
       <c r="A35" s="11"/>
-      <c r="B35" s="123"/>
-      <c r="C35" s="50" t="str">
-        <f>master!C24</f>
-        <v>６．サービス概要</v>
+      <c r="B35" s="108"/>
+      <c r="C35" s="47" t="str">
+        <f>master!C25</f>
+        <v>７．利用者体験イメージ</v>
       </c>
       <c r="D35" s="110" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E35" s="111"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="50" t="s">
-        <v>131</v>
+      <c r="G35" s="47" t="s">
+        <v>132</v>
       </c>
       <c r="H35" s="12"/>
-      <c r="I35" s="48" t="s">
+      <c r="I35" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="46">
+      <c r="J35" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K35" s="43"/>
+      <c r="K35" s="40"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="63">
+    <row r="36" spans="1:14" ht="25.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="123"/>
-      <c r="C36" s="50" t="str">
-        <f>master!C25</f>
-        <v>７．利用者体験イメージ</v>
+      <c r="B36" s="108"/>
+      <c r="C36" s="47" t="str">
+        <f>master!C26</f>
+        <v>８．事業構成</v>
       </c>
       <c r="D36" s="110" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E36" s="111"/>
       <c r="F36" s="112"/>
-      <c r="G36" s="50" t="s">
-        <v>132</v>
+      <c r="G36" s="47" t="s">
+        <v>89</v>
       </c>
       <c r="H36" s="12"/>
-      <c r="I36" s="48" t="s">
+      <c r="I36" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J36" s="46">
+      <c r="J36" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K36" s="43"/>
+      <c r="K36" s="40"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="25.2">
+    <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="123"/>
-      <c r="C37" s="50" t="str">
-        <f>master!C26</f>
-        <v>８．事業構成</v>
+      <c r="B37" s="108"/>
+      <c r="C37" s="47" t="str">
+        <f>master!C27</f>
+        <v>９．提供価値</v>
       </c>
       <c r="D37" s="110" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E37" s="111"/>
       <c r="F37" s="112"/>
-      <c r="G37" s="50" t="s">
-        <v>89</v>
+      <c r="G37" s="47" t="s">
+        <v>131</v>
       </c>
       <c r="H37" s="12"/>
-      <c r="I37" s="48" t="s">
+      <c r="I37" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J37" s="46">
+      <c r="J37" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K37" s="43"/>
+      <c r="K37" s="40"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="37.799999999999997">
+    <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="123"/>
-      <c r="C38" s="50" t="str">
-        <f>master!C27</f>
-        <v>９．提供価値</v>
+      <c r="B38" s="108"/>
+      <c r="C38" s="47" t="str">
+        <f>master!C28</f>
+        <v>１０．収益モデル</v>
       </c>
       <c r="D38" s="110" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E38" s="111"/>
       <c r="F38" s="112"/>
-      <c r="G38" s="50" t="s">
-        <v>131</v>
+      <c r="G38" s="47" t="s">
+        <v>132</v>
       </c>
       <c r="H38" s="12"/>
-      <c r="I38" s="48" t="s">
+      <c r="I38" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="46">
+      <c r="J38" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K38" s="43"/>
+      <c r="K38" s="40"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="123"/>
-      <c r="C39" s="50" t="str">
-        <f>master!C28</f>
-        <v>１０．収益モデル</v>
+      <c r="B39" s="108"/>
+      <c r="C39" s="47" t="str">
+        <f>master!C29</f>
+        <v>１１．リスク・課題</v>
       </c>
       <c r="D39" s="110" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E39" s="111"/>
       <c r="F39" s="112"/>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="47" t="s">
         <v>132</v>
       </c>
       <c r="H39" s="12"/>
-      <c r="I39" s="48" t="s">
+      <c r="I39" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="46">
+      <c r="J39" s="43">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K39" s="43"/>
+      <c r="K39" s="40"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="63">
+    <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="123"/>
-      <c r="C40" s="50" t="str">
-        <f>master!C29</f>
-        <v>１１．リスク・課題</v>
+      <c r="B40" s="109"/>
+      <c r="C40" s="47" t="str">
+        <f>master!C30</f>
+        <v>１２．今後の展望</v>
       </c>
       <c r="D40" s="110" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E40" s="111"/>
       <c r="F40" s="112"/>
-      <c r="G40" s="50" t="s">
-        <v>132</v>
+      <c r="G40" s="47" t="s">
+        <v>131</v>
       </c>
       <c r="H40" s="12"/>
-      <c r="I40" s="48" t="s">
+      <c r="I40" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J40" s="46">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K40" s="43"/>
+      <c r="J40" s="43">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K40" s="40"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="37.799999999999997">
+    <row r="41" spans="1:14" ht="113.4">
       <c r="A41" s="11"/>
-      <c r="B41" s="124"/>
-      <c r="C41" s="50" t="str">
-        <f>master!C30</f>
-        <v>１２．今後の展望</v>
-      </c>
-      <c r="D41" s="110" t="s">
-        <v>142</v>
-      </c>
-      <c r="E41" s="111"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="48" t="s">
+      <c r="B41" s="119" t="str">
+        <f>master!B32</f>
+        <v>個人演習</v>
+      </c>
+      <c r="C41" s="66" t="str">
+        <f>master!C32</f>
+        <v>演習内容の説明</v>
+      </c>
+      <c r="D41" s="116" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="117"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="H41" s="67"/>
+      <c r="I41" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="46">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K41" s="43"/>
+      <c r="J41" s="69">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K41" s="70"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="113.4">
+    <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="128" t="str">
-        <f>master!B32</f>
-        <v>個人演習</v>
-      </c>
-      <c r="C42" s="69" t="str">
-        <f>master!C32</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D42" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="E42" s="114"/>
-      <c r="F42" s="115"/>
-      <c r="G42" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="H42" s="70"/>
-      <c r="I42" s="71" t="s">
+      <c r="B42" s="120"/>
+      <c r="C42" s="66" t="str">
+        <f>master!C33</f>
+        <v>演習成果物の説明</v>
+      </c>
+      <c r="D42" s="116" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="117"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="67"/>
+      <c r="I42" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="72">
+      <c r="J42" s="69">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K42" s="73"/>
+      <c r="K42" s="70"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="201.6">
+    <row r="43" spans="1:14" ht="176.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="129"/>
-      <c r="C43" s="69" t="str">
-        <f>master!C33</f>
-        <v>演習成果物の説明</v>
-      </c>
-      <c r="D43" s="113" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" s="114"/>
-      <c r="F43" s="115"/>
-      <c r="G43" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="H43" s="70"/>
-      <c r="I43" s="71" t="s">
+      <c r="B43" s="120"/>
+      <c r="C43" s="66" t="str">
+        <f>master!C34</f>
+        <v>サービスの検討</v>
+      </c>
+      <c r="D43" s="116" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="117"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="H43" s="67"/>
+      <c r="I43" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="72">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K43" s="73"/>
+      <c r="J43" s="69">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K43" s="70"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="176.4">
+    <row r="44" spans="1:14" ht="138.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="129"/>
-      <c r="C44" s="69" t="str">
-        <f>master!C34</f>
-        <v>サービスの検討</v>
-      </c>
-      <c r="D44" s="113" t="s">
-        <v>106</v>
-      </c>
-      <c r="E44" s="114"/>
-      <c r="F44" s="115"/>
-      <c r="G44" s="69" t="s">
-        <v>99</v>
-      </c>
-      <c r="H44" s="70"/>
-      <c r="I44" s="71" t="s">
+      <c r="B44" s="120"/>
+      <c r="C44" s="66" t="str">
+        <f>master!C35</f>
+        <v>サービスのブラッシュアップ</v>
+      </c>
+      <c r="D44" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="117"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="H44" s="67"/>
+      <c r="I44" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="72">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K44" s="73"/>
+      <c r="J44" s="69">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K44" s="70"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="138.6">
+    <row r="45" spans="1:14" ht="63">
       <c r="A45" s="11"/>
-      <c r="B45" s="129"/>
-      <c r="C45" s="69" t="str">
-        <f>master!C35</f>
-        <v>サービスのブラッシュアップ</v>
-      </c>
-      <c r="D45" s="113" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="114"/>
-      <c r="F45" s="115"/>
-      <c r="G45" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="H45" s="70"/>
-      <c r="I45" s="71" t="s">
+      <c r="B45" s="120"/>
+      <c r="C45" s="66" t="str">
+        <f>master!C36</f>
+        <v>サービスの決定</v>
+      </c>
+      <c r="D45" s="116" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" s="117"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="H45" s="67"/>
+      <c r="I45" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="72">
+      <c r="J45" s="69">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K45" s="73"/>
+      <c r="K45" s="70"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="63">
+    <row r="46" spans="1:14" ht="138.6">
       <c r="A46" s="11"/>
-      <c r="B46" s="129"/>
-      <c r="C46" s="69" t="str">
-        <f>master!C36</f>
-        <v>サービスの決定</v>
-      </c>
-      <c r="D46" s="113" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="114"/>
-      <c r="F46" s="115"/>
-      <c r="G46" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="H46" s="70"/>
-      <c r="I46" s="71" t="s">
+      <c r="B46" s="120"/>
+      <c r="C46" s="66" t="str">
+        <f>master!C37</f>
+        <v>成果物の作成</v>
+      </c>
+      <c r="D46" s="116" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="117"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="H46" s="67"/>
+      <c r="I46" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="72">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K46" s="73"/>
+      <c r="J46" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="K46" s="70"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="138.6">
+    <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="129"/>
-      <c r="C47" s="69" t="str">
-        <f>master!C37</f>
-        <v>成果物の作成</v>
-      </c>
-      <c r="D47" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="114"/>
-      <c r="F47" s="115"/>
-      <c r="G47" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="H47" s="70"/>
-      <c r="I47" s="71" t="s">
+      <c r="B47" s="121"/>
+      <c r="C47" s="66" t="str">
+        <f>master!C38</f>
+        <v>成果物の提出</v>
+      </c>
+      <c r="D47" s="116" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="117"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="66" t="s">
+        <v>107</v>
+      </c>
+      <c r="H47" s="67"/>
+      <c r="I47" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="72" t="s">
+      <c r="J47" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="K47" s="73"/>
+      <c r="K47" s="70"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="25.2">
+    <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="130"/>
-      <c r="C48" s="69" t="str">
-        <f>master!C38</f>
-        <v>成果物の提出</v>
-      </c>
-      <c r="D48" s="113" t="s">
-        <v>102</v>
-      </c>
-      <c r="E48" s="114"/>
-      <c r="F48" s="115"/>
-      <c r="G48" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="H48" s="70"/>
-      <c r="I48" s="71" t="s">
+      <c r="B48" s="119" t="str">
+        <f>master!B40</f>
+        <v>チーム演習</v>
+      </c>
+      <c r="C48" s="66" t="str">
+        <f>master!C40</f>
+        <v>演習内容の説明</v>
+      </c>
+      <c r="D48" s="116" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="H48" s="67"/>
+      <c r="I48" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="72" t="s">
-        <v>135</v>
-      </c>
-      <c r="K48" s="73"/>
+      <c r="J48" s="69">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K48" s="70"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="100.8">
+    <row r="49" spans="1:14" ht="201.6">
       <c r="A49" s="11"/>
-      <c r="B49" s="128" t="str">
-        <f>master!B40</f>
-        <v>チーム演習</v>
-      </c>
-      <c r="C49" s="69" t="str">
-        <f>master!C40</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D49" s="113" t="s">
-        <v>110</v>
-      </c>
-      <c r="E49" s="114"/>
-      <c r="F49" s="115"/>
-      <c r="G49" s="69" t="s">
-        <v>151</v>
-      </c>
-      <c r="H49" s="70"/>
-      <c r="I49" s="71" t="s">
+      <c r="B49" s="120"/>
+      <c r="C49" s="66" t="str">
+        <f>master!C41</f>
+        <v>演習成果物の説明</v>
+      </c>
+      <c r="D49" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" s="117"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="72">
+      <c r="J49" s="69">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K49" s="73"/>
+      <c r="K49" s="70"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="201.6">
+    <row r="50" spans="1:14" ht="37.799999999999997">
       <c r="A50" s="11"/>
-      <c r="B50" s="129"/>
-      <c r="C50" s="69" t="str">
-        <f>master!C41</f>
-        <v>演習成果物の説明</v>
-      </c>
-      <c r="D50" s="113" t="s">
-        <v>144</v>
-      </c>
-      <c r="E50" s="114"/>
-      <c r="F50" s="115"/>
-      <c r="G50" s="69" t="s">
-        <v>152</v>
-      </c>
-      <c r="H50" s="70"/>
-      <c r="I50" s="71" t="s">
+      <c r="B50" s="120"/>
+      <c r="C50" s="66" t="str">
+        <f>master!C42</f>
+        <v>【参考】最終発表時の評価基準</v>
+      </c>
+      <c r="D50" s="116" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="117"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="66" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="67"/>
+      <c r="I50" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="72">
+      <c r="J50" s="69">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K50" s="73"/>
+      <c r="K50" s="70"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="37.799999999999997">
+    <row r="51" spans="1:14" ht="113.4">
       <c r="A51" s="11"/>
-      <c r="B51" s="129"/>
-      <c r="C51" s="69" t="str">
-        <f>master!C42</f>
-        <v>【参考】最終発表時の評価基準</v>
-      </c>
-      <c r="D51" s="113" t="s">
-        <v>145</v>
-      </c>
-      <c r="E51" s="114"/>
-      <c r="F51" s="115"/>
-      <c r="G51" s="69" t="s">
-        <v>153</v>
-      </c>
-      <c r="H51" s="70"/>
-      <c r="I51" s="71" t="s">
+      <c r="B51" s="120"/>
+      <c r="C51" s="66" t="str">
+        <f>master!C43</f>
+        <v>サービスの提案</v>
+      </c>
+      <c r="D51" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="H51" s="67"/>
+      <c r="I51" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J51" s="72">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K51" s="73"/>
+      <c r="J51" s="69">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="K51" s="70"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="113.4">
+    <row r="52" spans="1:14" ht="100.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="129"/>
-      <c r="C52" s="69" t="str">
-        <f>master!C43</f>
-        <v>サービスの提案</v>
-      </c>
-      <c r="D52" s="113" t="s">
-        <v>161</v>
-      </c>
-      <c r="E52" s="114"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="H52" s="70"/>
-      <c r="I52" s="71" t="s">
+      <c r="B52" s="120"/>
+      <c r="C52" s="66" t="str">
+        <f>master!C44</f>
+        <v>サービスの決定（チーム）</v>
+      </c>
+      <c r="D52" s="116" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="117"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="H52" s="67"/>
+      <c r="I52" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J52" s="72">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="K52" s="73"/>
+      <c r="J52" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52" s="70"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="100.8">
+    <row r="53" spans="1:14" ht="113.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="129"/>
-      <c r="C53" s="69" t="str">
-        <f>master!C44</f>
-        <v>サービスの決定（チーム）</v>
-      </c>
-      <c r="D53" s="113" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" s="114"/>
-      <c r="F53" s="115"/>
-      <c r="G53" s="69" t="s">
-        <v>151</v>
-      </c>
-      <c r="H53" s="70"/>
-      <c r="I53" s="71" t="s">
+      <c r="B53" s="120"/>
+      <c r="C53" s="66" t="str">
+        <f>master!C45</f>
+        <v>成果物の作成</v>
+      </c>
+      <c r="D53" s="116" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="117"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="H53" s="67"/>
+      <c r="I53" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J53" s="72" t="s">
+      <c r="J53" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="K53" s="73"/>
+      <c r="K53" s="70"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="113.4">
+    <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="129"/>
-      <c r="C54" s="69" t="str">
-        <f>master!C45</f>
-        <v>成果物の作成</v>
-      </c>
-      <c r="D54" s="113" t="s">
-        <v>112</v>
-      </c>
-      <c r="E54" s="114"/>
-      <c r="F54" s="115"/>
-      <c r="G54" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="H54" s="70"/>
-      <c r="I54" s="71" t="s">
+      <c r="B54" s="120"/>
+      <c r="C54" s="66" t="str">
+        <f>master!C46</f>
+        <v>成果物の提出</v>
+      </c>
+      <c r="D54" s="116" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="117"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="66" t="s">
+        <v>155</v>
+      </c>
+      <c r="H54" s="67"/>
+      <c r="I54" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="72" t="s">
+      <c r="J54" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="K54" s="73"/>
+      <c r="K54" s="70"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="129"/>
-      <c r="C55" s="69" t="str">
-        <f>master!C46</f>
-        <v>成果物の提出</v>
-      </c>
-      <c r="D55" s="113" t="s">
-        <v>102</v>
-      </c>
-      <c r="E55" s="114"/>
-      <c r="F55" s="115"/>
-      <c r="G55" s="69" t="s">
+      <c r="B55" s="121"/>
+      <c r="C55" s="66" t="str">
+        <f>master!C47</f>
+        <v>提案のリハーサル</v>
+      </c>
+      <c r="D55" s="116" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" s="117"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="H55" s="70"/>
-      <c r="I55" s="71" t="s">
+      <c r="H55" s="67"/>
+      <c r="I55" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J55" s="72" t="s">
+      <c r="J55" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="K55" s="73"/>
+      <c r="K55" s="70"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="25.2">
+    <row r="56" spans="1:14" ht="100.8">
       <c r="A56" s="11"/>
-      <c r="B56" s="130"/>
-      <c r="C56" s="69" t="str">
-        <f>master!C47</f>
-        <v>提案のリハーサル</v>
-      </c>
-      <c r="D56" s="113" t="s">
-        <v>159</v>
-      </c>
-      <c r="E56" s="114"/>
-      <c r="F56" s="115"/>
-      <c r="G56" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="H56" s="70"/>
-      <c r="I56" s="71" t="s">
+      <c r="B56" s="113" t="str">
+        <f>master!B49</f>
+        <v>提案会（ブロック代表の決定）</v>
+      </c>
+      <c r="C56" s="73" t="str">
+        <f>master!C49</f>
+        <v>ブロック内発表の説明</v>
+      </c>
+      <c r="D56" s="122" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="123"/>
+      <c r="F56" s="124"/>
+      <c r="G56" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="74"/>
+      <c r="I56" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="72" t="s">
-        <v>135</v>
-      </c>
-      <c r="K56" s="73"/>
+      <c r="J56" s="76">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K56" s="77"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="100.8">
+    <row r="57" spans="1:14" ht="113.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="125" t="str">
-        <f>master!B49</f>
-        <v>提案会（ブロック代表の決定）</v>
-      </c>
-      <c r="C57" s="76" t="str">
-        <f>master!C49</f>
-        <v>ブロック内発表の説明</v>
-      </c>
-      <c r="D57" s="116" t="s">
-        <v>114</v>
-      </c>
-      <c r="E57" s="117"/>
-      <c r="F57" s="118"/>
-      <c r="G57" s="76" t="s">
-        <v>156</v>
-      </c>
-      <c r="H57" s="77"/>
-      <c r="I57" s="78" t="s">
+      <c r="B57" s="114"/>
+      <c r="C57" s="73" t="str">
+        <f>master!C50</f>
+        <v>ブロック内発表の実施</v>
+      </c>
+      <c r="D57" s="122" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="123"/>
+      <c r="F57" s="124"/>
+      <c r="G57" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="H57" s="74"/>
+      <c r="I57" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="J57" s="79">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K57" s="80"/>
+      <c r="J57" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="K57" s="77"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="113.4">
+    <row r="58" spans="1:14" ht="25.2">
       <c r="A58" s="11"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="76" t="str">
-        <f>master!C50</f>
-        <v>ブロック内発表の実施</v>
-      </c>
-      <c r="D58" s="116" t="s">
-        <v>162</v>
-      </c>
-      <c r="E58" s="117"/>
-      <c r="F58" s="118"/>
-      <c r="G58" s="76" t="s">
-        <v>157</v>
-      </c>
-      <c r="H58" s="77"/>
-      <c r="I58" s="78" t="s">
+      <c r="B58" s="115"/>
+      <c r="C58" s="73" t="str">
+        <f>master!C51</f>
+        <v>ブロック代表（選抜チーム）の決定</v>
+      </c>
+      <c r="D58" s="122" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" s="123"/>
+      <c r="F58" s="124"/>
+      <c r="G58" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="H58" s="74"/>
+      <c r="I58" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="J58" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="K58" s="80"/>
+      <c r="J58" s="76">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K58" s="77"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="25.2">
+    <row r="59" spans="1:14" ht="113.4">
       <c r="A59" s="11"/>
-      <c r="B59" s="127"/>
-      <c r="C59" s="76" t="str">
-        <f>master!C51</f>
-        <v>ブロック代表（選抜チーム）の決定</v>
-      </c>
-      <c r="D59" s="116" t="s">
-        <v>116</v>
-      </c>
-      <c r="E59" s="117"/>
-      <c r="F59" s="118"/>
-      <c r="G59" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="H59" s="77"/>
-      <c r="I59" s="78" t="s">
+      <c r="B59" s="78" t="str">
+        <f>master!B52</f>
+        <v>提案会（最終）</v>
+      </c>
+      <c r="C59" s="73" t="str">
+        <f>master!C52</f>
+        <v>全体発表</v>
+      </c>
+      <c r="D59" s="122" t="s">
+        <v>163</v>
+      </c>
+      <c r="E59" s="123"/>
+      <c r="F59" s="124"/>
+      <c r="G59" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="74"/>
+      <c r="I59" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="J59" s="79">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K59" s="80"/>
+      <c r="J59" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="K59" s="77"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="113.4">
-      <c r="A60" s="11"/>
-      <c r="B60" s="81" t="str">
-        <f>master!B52</f>
-        <v>提案会（最終）</v>
-      </c>
-      <c r="C60" s="76" t="str">
-        <f>master!C52</f>
-        <v>全体発表</v>
-      </c>
-      <c r="D60" s="116" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" s="117"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="76" t="s">
-        <v>157</v>
-      </c>
-      <c r="H60" s="77"/>
-      <c r="I60" s="78" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="K60" s="80"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-    </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B17:B28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B29:B41"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D60:F60"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
@@ -5471,10 +5384,53 @@
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B16:B27"/>
     <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B28:B40"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="B48:B55"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D43:F43"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5487,7 +5443,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H16:H60</xm:sqref>
+          <xm:sqref>H15:H59</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5511,16 +5467,16 @@
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="63" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
@@ -5597,101 +5553,101 @@
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="74" t="s">
+      <c r="C18" s="71" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="71" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="71" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="C21" s="74" t="s">
+      <c r="C21" s="71" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="C22" s="74" t="s">
+      <c r="C22" s="71" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="C23" s="74" t="s">
+      <c r="C23" s="71" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="C24" s="74" t="s">
+      <c r="C24" s="71" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:3">
-      <c r="C25" s="75" t="s">
+      <c r="C25" s="72" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:3">
-      <c r="C26" s="74" t="s">
+      <c r="C26" s="71" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:3">
-      <c r="C27" s="74" t="s">
+      <c r="C27" s="71" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="C28" s="74" t="s">
+      <c r="C28" s="71" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" spans="2:3">
-      <c r="C29" s="74" t="s">
+      <c r="C29" s="71" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="30" spans="2:3">
-      <c r="C30" s="74" t="s">
+      <c r="C30" s="71" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="31" spans="2:3">
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="74" t="s">
+      <c r="C32" s="71" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="C33" s="74" t="s">
+      <c r="C33" s="71" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="C34" s="74" t="s">
+      <c r="C34" s="71" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="C35" s="74" t="s">
+      <c r="C35" s="71" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5711,29 +5667,29 @@
       </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="71" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="C41" s="74" t="s">
+      <c r="C41" s="71" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="2:3">
-      <c r="C42" s="74" t="s">
+      <c r="C42" s="71" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="C43" s="74" t="s">
+      <c r="C43" s="71" t="s">
         <v>109</v>
       </c>
     </row>
@@ -5758,24 +5714,24 @@
       </c>
     </row>
     <row r="48" spans="2:3">
-      <c r="B48" s="67"/>
-      <c r="C48" s="67"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="64"/>
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
         <v>170</v>
       </c>
-      <c r="C49" s="74" t="s">
+      <c r="C49" s="71" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="50" spans="2:3">
-      <c r="C50" s="74" t="s">
+      <c r="C50" s="71" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="51" spans="2:3">
-      <c r="C51" s="74" t="s">
+      <c r="C51" s="71" t="s">
         <v>115</v>
       </c>
     </row>
@@ -5783,7 +5739,7 @@
       <c r="B52" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="74" t="s">
+      <c r="C52" s="71" t="s">
         <v>79</v>
       </c>
     </row>

--- a/IG/AI Native-提案演習_IG.xlsx
+++ b/IG/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99893187-EF72-46E6-B6E9-C26F69A46DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967999EE-CBC3-4386-B263-3556BE4F6A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2460,6 +2460,42 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2469,15 +2505,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
@@ -2487,15 +2514,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2504,24 +2522,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3949,16 +3949,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -4102,10 +4102,10 @@
       <c r="H13" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="125" t="s">
+      <c r="I13" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="126"/>
+      <c r="J13" s="117"/>
       <c r="K13" s="100" t="s">
         <v>32</v>
       </c>
@@ -4143,11 +4143,11 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D15" s="110" t="s">
+      <c r="D15" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="111"/>
-      <c r="F15" s="112"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="109"/>
       <c r="G15" s="47" t="s">
         <v>113</v>
       </c>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="16" spans="1:14" ht="63">
       <c r="A16" s="10"/>
-      <c r="B16" s="107" t="str">
+      <c r="B16" s="119" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4173,11 +4173,11 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D16" s="110" t="s">
+      <c r="D16" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="111"/>
-      <c r="F16" s="112"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="109"/>
       <c r="G16" s="47" t="s">
         <v>113</v>
       </c>
@@ -4195,16 +4195,16 @@
     </row>
     <row r="17" spans="1:14" ht="163.80000000000001">
       <c r="A17" s="11"/>
-      <c r="B17" s="108"/>
+      <c r="B17" s="120"/>
       <c r="C17" s="47" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D17" s="110" t="s">
+      <c r="D17" s="107" t="s">
         <v>165</v>
       </c>
-      <c r="E17" s="111"/>
-      <c r="F17" s="112"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="109"/>
       <c r="G17" s="47" t="s">
         <v>164</v>
       </c>
@@ -4222,16 +4222,16 @@
     </row>
     <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="108"/>
+      <c r="B18" s="120"/>
       <c r="C18" s="47" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D18" s="110" t="s">
+      <c r="D18" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="111"/>
-      <c r="F18" s="112"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="109"/>
       <c r="G18" s="47" t="s">
         <v>36</v>
       </c>
@@ -4249,16 +4249,16 @@
     </row>
     <row r="19" spans="1:14" ht="151.19999999999999">
       <c r="A19" s="11"/>
-      <c r="B19" s="108"/>
+      <c r="B19" s="120"/>
       <c r="C19" s="47" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="D19" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="111"/>
-      <c r="F19" s="112"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="109"/>
       <c r="G19" s="47" t="s">
         <v>43</v>
       </c>
@@ -4276,16 +4276,16 @@
     </row>
     <row r="20" spans="1:14" ht="252">
       <c r="A20" s="11"/>
-      <c r="B20" s="108"/>
+      <c r="B20" s="120"/>
       <c r="C20" s="47" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D20" s="110" t="s">
+      <c r="D20" s="107" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="111"/>
-      <c r="F20" s="112"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="109"/>
       <c r="G20" s="47" t="s">
         <v>45</v>
       </c>
@@ -4303,16 +4303,16 @@
     </row>
     <row r="21" spans="1:14" ht="126">
       <c r="A21" s="11"/>
-      <c r="B21" s="108"/>
+      <c r="B21" s="120"/>
       <c r="C21" s="47" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D21" s="110" t="s">
+      <c r="D21" s="107" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="111"/>
-      <c r="F21" s="112"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="109"/>
       <c r="G21" s="47" t="s">
         <v>44</v>
       </c>
@@ -4330,16 +4330,16 @@
     </row>
     <row r="22" spans="1:14" ht="63">
       <c r="A22" s="11"/>
-      <c r="B22" s="108"/>
+      <c r="B22" s="120"/>
       <c r="C22" s="47" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D22" s="110" t="s">
+      <c r="D22" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="111"/>
-      <c r="F22" s="112"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
       <c r="G22" s="47" t="s">
         <v>113</v>
       </c>
@@ -4357,16 +4357,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="108"/>
+      <c r="B23" s="120"/>
       <c r="C23" s="47" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D23" s="110" t="s">
+      <c r="D23" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="111"/>
-      <c r="F23" s="112"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="109"/>
       <c r="G23" s="47" t="s">
         <v>37</v>
       </c>
@@ -4384,16 +4384,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="108"/>
+      <c r="B24" s="120"/>
       <c r="C24" s="47" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D24" s="110" t="s">
+      <c r="D24" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="111"/>
-      <c r="F24" s="112"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="109"/>
       <c r="G24" s="47" t="s">
         <v>37</v>
       </c>
@@ -4411,16 +4411,16 @@
     </row>
     <row r="25" spans="1:14" ht="113.4">
       <c r="A25" s="11"/>
-      <c r="B25" s="108"/>
+      <c r="B25" s="120"/>
       <c r="C25" s="47" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D25" s="110" t="s">
+      <c r="D25" s="107" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="111"/>
-      <c r="F25" s="112"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="109"/>
       <c r="G25" s="47" t="s">
         <v>38</v>
       </c>
@@ -4438,16 +4438,16 @@
     </row>
     <row r="26" spans="1:14" ht="88.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="108"/>
+      <c r="B26" s="120"/>
       <c r="C26" s="47" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D26" s="110" t="s">
+      <c r="D26" s="107" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="111"/>
-      <c r="F26" s="112"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="109"/>
       <c r="G26" s="47" t="s">
         <v>39</v>
       </c>
@@ -4465,16 +4465,16 @@
     </row>
     <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="109"/>
+      <c r="B27" s="121"/>
       <c r="C27" s="47" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D27" s="110" t="s">
+      <c r="D27" s="107" t="s">
         <v>128</v>
       </c>
-      <c r="E27" s="111"/>
-      <c r="F27" s="112"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="109"/>
       <c r="G27" s="47" t="s">
         <v>38</v>
       </c>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="28" spans="1:14" ht="37.799999999999997">
       <c r="A28" s="11"/>
-      <c r="B28" s="107" t="str">
+      <c r="B28" s="119" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
@@ -4500,11 +4500,11 @@
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D28" s="110" t="s">
+      <c r="D28" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="111"/>
-      <c r="F28" s="112"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="109"/>
       <c r="G28" s="47" t="s">
         <v>131</v>
       </c>
@@ -4522,16 +4522,16 @@
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="108"/>
+      <c r="B29" s="120"/>
       <c r="C29" s="47" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D29" s="110" t="s">
+      <c r="D29" s="107" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="111"/>
-      <c r="F29" s="112"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="109"/>
       <c r="G29" s="47" t="s">
         <v>89</v>
       </c>
@@ -4549,16 +4549,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="108"/>
+      <c r="B30" s="120"/>
       <c r="C30" s="47" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D30" s="110" t="s">
+      <c r="D30" s="107" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="111"/>
-      <c r="F30" s="112"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="109"/>
       <c r="G30" s="47" t="s">
         <v>89</v>
       </c>
@@ -4576,16 +4576,16 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="108"/>
+      <c r="B31" s="120"/>
       <c r="C31" s="47" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D31" s="110" t="s">
+      <c r="D31" s="107" t="s">
         <v>148</v>
       </c>
-      <c r="E31" s="111"/>
-      <c r="F31" s="112"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="109"/>
       <c r="G31" s="47" t="s">
         <v>89</v>
       </c>
@@ -4603,16 +4603,16 @@
     </row>
     <row r="32" spans="1:14" ht="63">
       <c r="A32" s="11"/>
-      <c r="B32" s="108"/>
+      <c r="B32" s="120"/>
       <c r="C32" s="47" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D32" s="110" t="s">
+      <c r="D32" s="107" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="111"/>
-      <c r="F32" s="112"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="109"/>
       <c r="G32" s="47" t="s">
         <v>132</v>
       </c>
@@ -4630,16 +4630,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="108"/>
+      <c r="B33" s="120"/>
       <c r="C33" s="47" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D33" s="110" t="s">
+      <c r="D33" s="107" t="s">
         <v>137</v>
       </c>
-      <c r="E33" s="111"/>
-      <c r="F33" s="112"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="109"/>
       <c r="G33" s="47" t="s">
         <v>131</v>
       </c>
@@ -4657,16 +4657,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="108"/>
+      <c r="B34" s="120"/>
       <c r="C34" s="47" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D34" s="110" t="s">
+      <c r="D34" s="107" t="s">
         <v>138</v>
       </c>
-      <c r="E34" s="111"/>
-      <c r="F34" s="112"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="109"/>
       <c r="G34" s="47" t="s">
         <v>131</v>
       </c>
@@ -4684,16 +4684,16 @@
     </row>
     <row r="35" spans="1:14" ht="63">
       <c r="A35" s="11"/>
-      <c r="B35" s="108"/>
+      <c r="B35" s="120"/>
       <c r="C35" s="47" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D35" s="110" t="s">
+      <c r="D35" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="111"/>
-      <c r="F35" s="112"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="109"/>
       <c r="G35" s="47" t="s">
         <v>132</v>
       </c>
@@ -4711,16 +4711,16 @@
     </row>
     <row r="36" spans="1:14" ht="25.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="108"/>
+      <c r="B36" s="120"/>
       <c r="C36" s="47" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D36" s="110" t="s">
+      <c r="D36" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="111"/>
-      <c r="F36" s="112"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="109"/>
       <c r="G36" s="47" t="s">
         <v>89</v>
       </c>
@@ -4738,16 +4738,16 @@
     </row>
     <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="108"/>
+      <c r="B37" s="120"/>
       <c r="C37" s="47" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D37" s="110" t="s">
+      <c r="D37" s="107" t="s">
         <v>140</v>
       </c>
-      <c r="E37" s="111"/>
-      <c r="F37" s="112"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="109"/>
       <c r="G37" s="47" t="s">
         <v>131</v>
       </c>
@@ -4765,16 +4765,16 @@
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="108"/>
+      <c r="B38" s="120"/>
       <c r="C38" s="47" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D38" s="110" t="s">
+      <c r="D38" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="111"/>
-      <c r="F38" s="112"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="109"/>
       <c r="G38" s="47" t="s">
         <v>132</v>
       </c>
@@ -4792,16 +4792,16 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="108"/>
+      <c r="B39" s="120"/>
       <c r="C39" s="47" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D39" s="110" t="s">
+      <c r="D39" s="107" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="111"/>
-      <c r="F39" s="112"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="109"/>
       <c r="G39" s="47" t="s">
         <v>132</v>
       </c>
@@ -4819,16 +4819,16 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="109"/>
+      <c r="B40" s="121"/>
       <c r="C40" s="47" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D40" s="110" t="s">
+      <c r="D40" s="107" t="s">
         <v>142</v>
       </c>
-      <c r="E40" s="111"/>
-      <c r="F40" s="112"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="109"/>
       <c r="G40" s="47" t="s">
         <v>131</v>
       </c>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="41" spans="1:14" ht="113.4">
       <c r="A41" s="11"/>
-      <c r="B41" s="119" t="str">
+      <c r="B41" s="125" t="str">
         <f>master!B32</f>
         <v>個人演習</v>
       </c>
@@ -4854,11 +4854,11 @@
         <f>master!C32</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D41" s="116" t="s">
+      <c r="D41" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="117"/>
-      <c r="F41" s="118"/>
+      <c r="E41" s="111"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="66" t="s">
         <v>95</v>
       </c>
@@ -4876,16 +4876,16 @@
     </row>
     <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="120"/>
+      <c r="B42" s="126"/>
       <c r="C42" s="66" t="str">
         <f>master!C33</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D42" s="116" t="s">
+      <c r="D42" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="E42" s="117"/>
-      <c r="F42" s="118"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="112"/>
       <c r="G42" s="66" t="s">
         <v>97</v>
       </c>
@@ -4903,16 +4903,16 @@
     </row>
     <row r="43" spans="1:14" ht="176.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="120"/>
+      <c r="B43" s="126"/>
       <c r="C43" s="66" t="str">
         <f>master!C34</f>
         <v>サービスの検討</v>
       </c>
-      <c r="D43" s="116" t="s">
+      <c r="D43" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="E43" s="117"/>
-      <c r="F43" s="118"/>
+      <c r="E43" s="111"/>
+      <c r="F43" s="112"/>
       <c r="G43" s="66" t="s">
         <v>99</v>
       </c>
@@ -4930,16 +4930,16 @@
     </row>
     <row r="44" spans="1:14" ht="138.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="120"/>
+      <c r="B44" s="126"/>
       <c r="C44" s="66" t="str">
         <f>master!C35</f>
         <v>サービスのブラッシュアップ</v>
       </c>
-      <c r="D44" s="116" t="s">
+      <c r="D44" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="117"/>
-      <c r="F44" s="118"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="112"/>
       <c r="G44" s="66" t="s">
         <v>101</v>
       </c>
@@ -4957,16 +4957,16 @@
     </row>
     <row r="45" spans="1:14" ht="63">
       <c r="A45" s="11"/>
-      <c r="B45" s="120"/>
+      <c r="B45" s="126"/>
       <c r="C45" s="66" t="str">
         <f>master!C36</f>
         <v>サービスの決定</v>
       </c>
-      <c r="D45" s="116" t="s">
+      <c r="D45" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="E45" s="117"/>
-      <c r="F45" s="118"/>
+      <c r="E45" s="111"/>
+      <c r="F45" s="112"/>
       <c r="G45" s="66" t="s">
         <v>98</v>
       </c>
@@ -4984,16 +4984,16 @@
     </row>
     <row r="46" spans="1:14" ht="138.6">
       <c r="A46" s="11"/>
-      <c r="B46" s="120"/>
+      <c r="B46" s="126"/>
       <c r="C46" s="66" t="str">
         <f>master!C37</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D46" s="116" t="s">
+      <c r="D46" s="110" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="117"/>
-      <c r="F46" s="118"/>
+      <c r="E46" s="111"/>
+      <c r="F46" s="112"/>
       <c r="G46" s="66" t="s">
         <v>101</v>
       </c>
@@ -5011,16 +5011,16 @@
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="121"/>
+      <c r="B47" s="127"/>
       <c r="C47" s="66" t="str">
         <f>master!C38</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D47" s="116" t="s">
+      <c r="D47" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="117"/>
-      <c r="F47" s="118"/>
+      <c r="E47" s="111"/>
+      <c r="F47" s="112"/>
       <c r="G47" s="66" t="s">
         <v>107</v>
       </c>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="119" t="str">
+      <c r="B48" s="125" t="str">
         <f>master!B40</f>
         <v>チーム演習</v>
       </c>
@@ -5046,11 +5046,11 @@
         <f>master!C40</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D48" s="116" t="s">
+      <c r="D48" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="E48" s="117"/>
-      <c r="F48" s="118"/>
+      <c r="E48" s="111"/>
+      <c r="F48" s="112"/>
       <c r="G48" s="66" t="s">
         <v>151</v>
       </c>
@@ -5068,16 +5068,16 @@
     </row>
     <row r="49" spans="1:14" ht="201.6">
       <c r="A49" s="11"/>
-      <c r="B49" s="120"/>
+      <c r="B49" s="126"/>
       <c r="C49" s="66" t="str">
         <f>master!C41</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D49" s="116" t="s">
+      <c r="D49" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="117"/>
-      <c r="F49" s="118"/>
+      <c r="E49" s="111"/>
+      <c r="F49" s="112"/>
       <c r="G49" s="66" t="s">
         <v>152</v>
       </c>
@@ -5095,16 +5095,16 @@
     </row>
     <row r="50" spans="1:14" ht="37.799999999999997">
       <c r="A50" s="11"/>
-      <c r="B50" s="120"/>
+      <c r="B50" s="126"/>
       <c r="C50" s="66" t="str">
         <f>master!C42</f>
         <v>【参考】最終発表時の評価基準</v>
       </c>
-      <c r="D50" s="116" t="s">
+      <c r="D50" s="110" t="s">
         <v>145</v>
       </c>
-      <c r="E50" s="117"/>
-      <c r="F50" s="118"/>
+      <c r="E50" s="111"/>
+      <c r="F50" s="112"/>
       <c r="G50" s="66" t="s">
         <v>153</v>
       </c>
@@ -5122,16 +5122,16 @@
     </row>
     <row r="51" spans="1:14" ht="113.4">
       <c r="A51" s="11"/>
-      <c r="B51" s="120"/>
+      <c r="B51" s="126"/>
       <c r="C51" s="66" t="str">
         <f>master!C43</f>
         <v>サービスの提案</v>
       </c>
-      <c r="D51" s="116" t="s">
+      <c r="D51" s="110" t="s">
         <v>161</v>
       </c>
-      <c r="E51" s="117"/>
-      <c r="F51" s="118"/>
+      <c r="E51" s="111"/>
+      <c r="F51" s="112"/>
       <c r="G51" s="66" t="s">
         <v>154</v>
       </c>
@@ -5149,16 +5149,16 @@
     </row>
     <row r="52" spans="1:14" ht="100.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="120"/>
+      <c r="B52" s="126"/>
       <c r="C52" s="66" t="str">
         <f>master!C44</f>
         <v>サービスの決定（チーム）</v>
       </c>
-      <c r="D52" s="116" t="s">
+      <c r="D52" s="110" t="s">
         <v>146</v>
       </c>
-      <c r="E52" s="117"/>
-      <c r="F52" s="118"/>
+      <c r="E52" s="111"/>
+      <c r="F52" s="112"/>
       <c r="G52" s="66" t="s">
         <v>151</v>
       </c>
@@ -5176,16 +5176,16 @@
     </row>
     <row r="53" spans="1:14" ht="113.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="120"/>
+      <c r="B53" s="126"/>
       <c r="C53" s="66" t="str">
         <f>master!C45</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D53" s="116" t="s">
+      <c r="D53" s="110" t="s">
         <v>112</v>
       </c>
-      <c r="E53" s="117"/>
-      <c r="F53" s="118"/>
+      <c r="E53" s="111"/>
+      <c r="F53" s="112"/>
       <c r="G53" s="66" t="s">
         <v>154</v>
       </c>
@@ -5203,16 +5203,16 @@
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="120"/>
+      <c r="B54" s="126"/>
       <c r="C54" s="66" t="str">
         <f>master!C46</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D54" s="116" t="s">
+      <c r="D54" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="E54" s="117"/>
-      <c r="F54" s="118"/>
+      <c r="E54" s="111"/>
+      <c r="F54" s="112"/>
       <c r="G54" s="66" t="s">
         <v>155</v>
       </c>
@@ -5230,16 +5230,16 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="127"/>
       <c r="C55" s="66" t="str">
         <f>master!C47</f>
         <v>提案のリハーサル</v>
       </c>
-      <c r="D55" s="116" t="s">
+      <c r="D55" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="E55" s="117"/>
-      <c r="F55" s="118"/>
+      <c r="E55" s="111"/>
+      <c r="F55" s="112"/>
       <c r="G55" s="66" t="s">
         <v>155</v>
       </c>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="56" spans="1:14" ht="100.8">
       <c r="A56" s="11"/>
-      <c r="B56" s="113" t="str">
+      <c r="B56" s="122" t="str">
         <f>master!B49</f>
         <v>提案会（ブロック代表の決定）</v>
       </c>
@@ -5265,11 +5265,11 @@
         <f>master!C49</f>
         <v>ブロック内発表の説明</v>
       </c>
-      <c r="D56" s="122" t="s">
+      <c r="D56" s="113" t="s">
         <v>114</v>
       </c>
-      <c r="E56" s="123"/>
-      <c r="F56" s="124"/>
+      <c r="E56" s="114"/>
+      <c r="F56" s="115"/>
       <c r="G56" s="73" t="s">
         <v>156</v>
       </c>
@@ -5287,16 +5287,16 @@
     </row>
     <row r="57" spans="1:14" ht="113.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="114"/>
+      <c r="B57" s="123"/>
       <c r="C57" s="73" t="str">
         <f>master!C50</f>
         <v>ブロック内発表の実施</v>
       </c>
-      <c r="D57" s="122" t="s">
+      <c r="D57" s="113" t="s">
         <v>162</v>
       </c>
-      <c r="E57" s="123"/>
-      <c r="F57" s="124"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="115"/>
       <c r="G57" s="73" t="s">
         <v>157</v>
       </c>
@@ -5314,16 +5314,16 @@
     </row>
     <row r="58" spans="1:14" ht="25.2">
       <c r="A58" s="11"/>
-      <c r="B58" s="115"/>
+      <c r="B58" s="124"/>
       <c r="C58" s="73" t="str">
         <f>master!C51</f>
         <v>ブロック代表（選抜チーム）の決定</v>
       </c>
-      <c r="D58" s="122" t="s">
+      <c r="D58" s="113" t="s">
         <v>116</v>
       </c>
-      <c r="E58" s="123"/>
-      <c r="F58" s="124"/>
+      <c r="E58" s="114"/>
+      <c r="F58" s="115"/>
       <c r="G58" s="73" t="s">
         <v>158</v>
       </c>
@@ -5349,11 +5349,11 @@
         <f>master!C52</f>
         <v>全体発表</v>
       </c>
-      <c r="D59" s="122" t="s">
+      <c r="D59" s="113" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="123"/>
-      <c r="F59" s="124"/>
+      <c r="E59" s="114"/>
+      <c r="F59" s="115"/>
       <c r="G59" s="73" t="s">
         <v>157</v>
       </c>
@@ -5371,6 +5371,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B28:B40"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="B48:B55"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D53:F53"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D59:F59"/>
@@ -5387,50 +5431,6 @@
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="D57:F57"/>
     <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B28:B40"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B41:B47"/>
-    <mergeCell ref="B48:B55"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D43:F43"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
